--- a/data/Global_Learning_Resource_Directory.xlsx
+++ b/data/Global_Learning_Resource_Directory.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I445"/>
+  <dimension ref="A1:I538"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="14" min="1" max="1"/>
@@ -21694,6 +21694,4377 @@
       <c r="I445" s="26" t="inlineStr">
         <is>
           <t>Accessible explainers on the psychology behind economic decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="26" t="inlineStr">
+        <is>
+          <t>Mathematics — Foundations &amp; Arithmetic</t>
+        </is>
+      </c>
+      <c r="B446" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C446" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Math Antics</t>
+        </is>
+      </c>
+      <c r="D446" s="26" t="inlineStr">
+        <is>
+          <t>Basic Math Full Playlist (fractions, decimals, percentages)</t>
+        </is>
+      </c>
+      <c r="E446" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pWJzqTYS8no</t>
+        </is>
+      </c>
+      <c r="F446" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G446" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/pWJzqTYS8no" title="Basic Math Full Playlist (fractions, decimals, percentages)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H446" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I446" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Fractions on the Number Line - Math Antics".</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="26" t="inlineStr">
+        <is>
+          <t>Mathematics — Foundations &amp; Arithmetic</t>
+        </is>
+      </c>
+      <c r="B447" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C447" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Numberphile</t>
+        </is>
+      </c>
+      <c r="D447" s="26" t="inlineStr">
+        <is>
+          <t>Numbers &amp; Number Theory Playlist</t>
+        </is>
+      </c>
+      <c r="E447" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0aTUTxOiRgU</t>
+        </is>
+      </c>
+      <c r="F447" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G447" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/0aTUTxOiRgU" title="Numbers &amp; Number Theory Playlist" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H447" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I447" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "291 Holes - Numberphile".</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="26" t="inlineStr">
+        <is>
+          <t>Mathematics — Foundations &amp; Arithmetic</t>
+        </is>
+      </c>
+      <c r="B448" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C448" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Khan Academy</t>
+        </is>
+      </c>
+      <c r="D448" s="26" t="inlineStr">
+        <is>
+          <t>Arithmetic Word Problems &amp; Ratios</t>
+        </is>
+      </c>
+      <c r="E448" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W6HDsxbHfO0</t>
+        </is>
+      </c>
+      <c r="F448" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G448" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/W6HDsxbHfO0" title="Arithmetic Word Problems &amp; Ratios" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H448" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I448" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "🚨 NEW COURSE ALERT: AP Precalculus just joined Khan Academy".</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="26" t="inlineStr">
+        <is>
+          <t>Algebra &amp; Pre-Calculus</t>
+        </is>
+      </c>
+      <c r="B449" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C449" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Organic Chemistry Tutor</t>
+        </is>
+      </c>
+      <c r="D449" s="26" t="inlineStr">
+        <is>
+          <t>Algebra 1 &amp; Algebra 2 Full Review</t>
+        </is>
+      </c>
+      <c r="E449" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PyYEHq4Dc5I</t>
+        </is>
+      </c>
+      <c r="F449" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G449" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/PyYEHq4Dc5I" title="Algebra 1 &amp; Algebra 2 Full Review" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H449" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I449" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "GED Math Practice Test - Study Guide Review Prep".</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="26" t="inlineStr">
+        <is>
+          <t>Algebra &amp; Pre-Calculus</t>
+        </is>
+      </c>
+      <c r="B450" s="26" t="inlineStr">
+        <is>
+          <t>School/College</t>
+        </is>
+      </c>
+      <c r="C450" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Krista King Math</t>
+        </is>
+      </c>
+      <c r="D450" s="26" t="inlineStr">
+        <is>
+          <t>Algebra &amp; Precalculus</t>
+        </is>
+      </c>
+      <c r="E450" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gb6QihvVaNU</t>
+        </is>
+      </c>
+      <c r="F450" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G450" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/gb6QihvVaNU" title="Algebra &amp; Precalculus" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H450" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I450" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Why Completing the Square Works".</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="26" t="inlineStr">
+        <is>
+          <t>Algebra &amp; Pre-Calculus</t>
+        </is>
+      </c>
+      <c r="B451" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C451" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Brian McLogan</t>
+        </is>
+      </c>
+      <c r="D451" s="26" t="inlineStr">
+        <is>
+          <t>Precalculus Full Course</t>
+        </is>
+      </c>
+      <c r="E451" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bV3U0q6h0tk</t>
+        </is>
+      </c>
+      <c r="F451" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G451" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/bV3U0q6h0tk" title="Precalculus Full Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H451" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I451" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How is the Associative Property Actually Useful?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="26" t="inlineStr">
+        <is>
+          <t>Calculus &amp; Advanced Mathematics</t>
+        </is>
+      </c>
+      <c r="B452" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C452" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Professor Leonard</t>
+        </is>
+      </c>
+      <c r="D452" s="26" t="inlineStr">
+        <is>
+          <t>Calculus 1, 2 and 3 — Full Lecture Series</t>
+        </is>
+      </c>
+      <c r="E452" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1vH00iNHIA4</t>
+        </is>
+      </c>
+      <c r="F452" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G452" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/1vH00iNHIA4" title="Calculus 1, 2 and 3 — Full Lecture Series" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H452" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I452" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "I'm BACK - Professor Leonard Update".</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="26" t="inlineStr">
+        <is>
+          <t>Calculus &amp; Advanced Mathematics</t>
+        </is>
+      </c>
+      <c r="B453" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C453" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — MIT OpenCourseWare</t>
+        </is>
+      </c>
+      <c r="D453" s="26" t="inlineStr">
+        <is>
+          <t>18.01 Single Variable Calculus (Lecture Videos)</t>
+        </is>
+      </c>
+      <c r="E453" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0oykYip2vus</t>
+        </is>
+      </c>
+      <c r="F453" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G453" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/0oykYip2vus" title="18.01 Single Variable Calculus (Lecture Videos)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H453" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I453" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Sal Khan discusses MIT OpenCourseWare".</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="26" t="inlineStr">
+        <is>
+          <t>Calculus &amp; Advanced Mathematics</t>
+        </is>
+      </c>
+      <c r="B454" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C454" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Dr. Trefor Bazett</t>
+        </is>
+      </c>
+      <c r="D454" s="26" t="inlineStr">
+        <is>
+          <t>Calculus &amp; Multivariable Calculus</t>
+        </is>
+      </c>
+      <c r="E454" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CrVVsX3el8I</t>
+        </is>
+      </c>
+      <c r="F454" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G454" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/CrVVsX3el8I" title="Calculus &amp; Multivariable Calculus" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H454" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I454" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Math News: Is the Reimann Hypothesis closer to being solved?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="26" t="inlineStr">
+        <is>
+          <t>Linear Algebra</t>
+        </is>
+      </c>
+      <c r="B455" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C455" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Steve Brunton</t>
+        </is>
+      </c>
+      <c r="D455" s="26" t="inlineStr">
+        <is>
+          <t>Linear Algebra &amp; Singular Value Decomposition</t>
+        </is>
+      </c>
+      <c r="E455" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eUhnyZ--kGY</t>
+        </is>
+      </c>
+      <c r="F455" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G455" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/eUhnyZ--kGY" title="Linear Algebra &amp; Singular Value Decomposition" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H455" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I455" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Convex Sets".</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="26" t="inlineStr">
+        <is>
+          <t>Statistics, Probability &amp; Data Literacy</t>
+        </is>
+      </c>
+      <c r="B456" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C456" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — CrashCourse</t>
+        </is>
+      </c>
+      <c r="D456" s="26" t="inlineStr">
+        <is>
+          <t>Crash Course Statistics (45 episodes)</t>
+        </is>
+      </c>
+      <c r="E456" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xYKSKBcifaE</t>
+        </is>
+      </c>
+      <c r="F456" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G456" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/xYKSKBcifaE" title="Crash Course Statistics (45 episodes)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H456" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I456" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Is it Possible to Prepare for an Earthquake?: Crash Course Geology #15".</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="26" t="inlineStr">
+        <is>
+          <t>Statistics, Probability &amp; Data Literacy</t>
+        </is>
+      </c>
+      <c r="B457" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C457" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — ritvikmath</t>
+        </is>
+      </c>
+      <c r="D457" s="26" t="inlineStr">
+        <is>
+          <t>Statistics &amp; Data Science Concepts</t>
+        </is>
+      </c>
+      <c r="E457" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wi3-KO2X-T8</t>
+        </is>
+      </c>
+      <c r="F457" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G457" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/wi3-KO2X-T8" title="Statistics &amp; Data Science Concepts" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H457" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I457" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Regularization : Data Science Basics".</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="26" t="inlineStr">
+        <is>
+          <t>Physics — School &amp; AP</t>
+        </is>
+      </c>
+      <c r="B458" s="26" t="inlineStr">
+        <is>
+          <t>School/College</t>
+        </is>
+      </c>
+      <c r="C458" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Michel van Biezen</t>
+        </is>
+      </c>
+      <c r="D458" s="26" t="inlineStr">
+        <is>
+          <t>Physics — Mechanics, E&amp;M, Optics</t>
+        </is>
+      </c>
+      <c r="E458" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=deRZbv3fkA8</t>
+        </is>
+      </c>
+      <c r="F458" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G458" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/deRZbv3fkA8" title="Physics — Mechanics, E&amp;M, Optics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H458" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I458" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "JEE Main Physics Optics #3 Polarization".</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="26" t="inlineStr">
+        <is>
+          <t>Physics — School &amp; AP</t>
+        </is>
+      </c>
+      <c r="B459" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C459" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Professor Dave Explains</t>
+        </is>
+      </c>
+      <c r="D459" s="26" t="inlineStr">
+        <is>
+          <t>Physics Explained</t>
+        </is>
+      </c>
+      <c r="E459" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SXm_Wd_DBIY</t>
+        </is>
+      </c>
+      <c r="F459" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G459" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/SXm_Wd_DBIY" title="Physics Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H459" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I459" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Present Passive System (I-II Conjugation)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="26" t="inlineStr">
+        <is>
+          <t>Physics — University &amp; Theoretical</t>
+        </is>
+      </c>
+      <c r="B460" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C460" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Veritasium</t>
+        </is>
+      </c>
+      <c r="D460" s="26" t="inlineStr">
+        <is>
+          <t>Physics Investigations &amp; Misconceptions</t>
+        </is>
+      </c>
+      <c r="E460" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=J1WoNuemKOg</t>
+        </is>
+      </c>
+      <c r="F460" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G460" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/J1WoNuemKOg" title="Physics Investigations &amp; Misconceptions" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H460" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I460" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Total Solar Eclipse From Space".</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy, Physiology &amp; Medicine</t>
+        </is>
+      </c>
+      <c r="B461" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C461" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Ninja Nerd</t>
+        </is>
+      </c>
+      <c r="D461" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy &amp; Physiology Full Lectures</t>
+        </is>
+      </c>
+      <c r="E461" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ewt9gqWlf9w</t>
+        </is>
+      </c>
+      <c r="F461" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G461" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/Ewt9gqWlf9w" title="Anatomy &amp; Physiology Full Lectures" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H461" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I461" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Urinary Tract Infection (UTI) | Podcast".</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy, Physiology &amp; Medicine</t>
+        </is>
+      </c>
+      <c r="B462" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C462" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Armando Hasudungan</t>
+        </is>
+      </c>
+      <c r="D462" s="26" t="inlineStr">
+        <is>
+          <t>Hand-Drawn Medicine &amp; Physiology</t>
+        </is>
+      </c>
+      <c r="E462" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n4JBo_Mjkx8</t>
+        </is>
+      </c>
+      <c r="F462" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G462" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/n4JBo_Mjkx8" title="Hand-Drawn Medicine &amp; Physiology" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H462" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I462" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Cardiovascular Insights: Kussmaul's Sign #kussmaulssign #cardiology  #cardiovascularInsights #meded".</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="26" t="inlineStr">
+        <is>
+          <t>Astronomy, Space &amp; Cosmology</t>
+        </is>
+      </c>
+      <c r="B463" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C463" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — PBS Space Time</t>
+        </is>
+      </c>
+      <c r="D463" s="26" t="inlineStr">
+        <is>
+          <t>Cosmology &amp; Astrophysics</t>
+        </is>
+      </c>
+      <c r="E463" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Yid9cO7peXg</t>
+        </is>
+      </c>
+      <c r="F463" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G463" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/Yid9cO7peXg" title="Cosmology &amp; Astrophysics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H463" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I463" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "There's Something Massive Hiding Behind the Galaxy's Strangest Star".</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="26" t="inlineStr">
+        <is>
+          <t>Astronomy, Space &amp; Cosmology</t>
+        </is>
+      </c>
+      <c r="B464" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C464" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Anton Petrov</t>
+        </is>
+      </c>
+      <c r="D464" s="26" t="inlineStr">
+        <is>
+          <t>Daily Space &amp; Science News</t>
+        </is>
+      </c>
+      <c r="E464" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SSccNV39mCU</t>
+        </is>
+      </c>
+      <c r="F464" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G464" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/SSccNV39mCU" title="Daily Space &amp; Science News" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H464" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I464" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Astronomers Imaged Asteroid 44 Nysa and Found Something Truly Unexpected".</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="26" t="inlineStr">
+        <is>
+          <t>Earth, Environmental &amp; Climate Science</t>
+        </is>
+      </c>
+      <c r="B465" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C465" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — MinuteEarth</t>
+        </is>
+      </c>
+      <c r="D465" s="26" t="inlineStr">
+        <is>
+          <t>Earth Systems Short Explainers</t>
+        </is>
+      </c>
+      <c r="E465" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OqWEFV87urg</t>
+        </is>
+      </c>
+      <c r="F465" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G465" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/OqWEFV87urg" title="Earth Systems Short Explainers" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H465" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I465" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Why do bees dance?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="26" t="inlineStr">
+        <is>
+          <t>Computer Science Fundamentals</t>
+        </is>
+      </c>
+      <c r="B466" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C466" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — CS50 (Harvard)</t>
+        </is>
+      </c>
+      <c r="D466" s="26" t="inlineStr">
+        <is>
+          <t>CS50x — Introduction to Computer Science</t>
+        </is>
+      </c>
+      <c r="E466" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0IjFxHxs88c</t>
+        </is>
+      </c>
+      <c r="F466" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G466" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/0IjFxHxs88c" title="CS50x — Introduction to Computer Science" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H466" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I466" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "CS50x en Español - El Fin".</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="26" t="inlineStr">
+        <is>
+          <t>Computer Science Fundamentals</t>
+        </is>
+      </c>
+      <c r="B467" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C467" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Computerphile</t>
+        </is>
+      </c>
+      <c r="D467" s="26" t="inlineStr">
+        <is>
+          <t>Core CS Concepts with Researchers</t>
+        </is>
+      </c>
+      <c r="E467" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pg7fntKLNak</t>
+        </is>
+      </c>
+      <c r="F467" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G467" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/pg7fntKLNak" title="Core CS Concepts with Researchers" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H467" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I467" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Quantum Simulation &amp; Nature - Computerphile".</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="26" t="inlineStr">
+        <is>
+          <t>Computer Science Fundamentals</t>
+        </is>
+      </c>
+      <c r="B468" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C468" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Ben Eater</t>
+        </is>
+      </c>
+      <c r="D468" s="26" t="inlineStr">
+        <is>
+          <t>Building an 8-Bit Computer from Scratch</t>
+        </is>
+      </c>
+      <c r="E468" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3XDH-fZKnQk</t>
+        </is>
+      </c>
+      <c r="F468" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G468" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/3XDH-fZKnQk" title="Building an 8-Bit Computer from Scratch" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H468" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I468" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Let's build a digital clock!".</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="26" t="inlineStr">
+        <is>
+          <t>Python Programming</t>
+        </is>
+      </c>
+      <c r="B469" s="26" t="inlineStr">
+        <is>
+          <t>Beginner/Intermediate</t>
+        </is>
+      </c>
+      <c r="C469" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Corey Schafer</t>
+        </is>
+      </c>
+      <c r="D469" s="26" t="inlineStr">
+        <is>
+          <t>Python Tutorials — Full Playlist</t>
+        </is>
+      </c>
+      <c r="E469" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tHh0UaL_V4w</t>
+        </is>
+      </c>
+      <c r="F469" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G469" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/tHh0UaL_V4w" title="Python Tutorials — Full Playlist" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H469" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I469" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "I Use AI Every Day: What I Like, What I Hate, and Where I Think We're Heading".</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="26" t="inlineStr">
+        <is>
+          <t>Python Programming</t>
+        </is>
+      </c>
+      <c r="B470" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C470" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — sentdex</t>
+        </is>
+      </c>
+      <c r="D470" s="26" t="inlineStr">
+        <is>
+          <t>Python for Data, Automation &amp; ML</t>
+        </is>
+      </c>
+      <c r="E470" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=H50xoAzNfB0</t>
+        </is>
+      </c>
+      <c r="F470" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G470" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/H50xoAzNfB0" title="Python for Data, Automation &amp; ML" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H470" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I470" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The Right Harness is All You Need - For local Frontier AI".</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="26" t="inlineStr">
+        <is>
+          <t>Python Programming</t>
+        </is>
+      </c>
+      <c r="B471" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C471" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Bro Code</t>
+        </is>
+      </c>
+      <c r="D471" s="26" t="inlineStr">
+        <is>
+          <t>Python Full Course</t>
+        </is>
+      </c>
+      <c r="E471" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fPopFeqw5sk</t>
+        </is>
+      </c>
+      <c r="F471" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G471" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/fPopFeqw5sk" title="Python Full Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H471" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I471" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Learn NumPy data types in 8 minutes! 💱".</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="26" t="inlineStr">
+        <is>
+          <t>Web Development — HTML, CSS &amp; JavaScript</t>
+        </is>
+      </c>
+      <c r="B472" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C472" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Traversy Media</t>
+        </is>
+      </c>
+      <c r="D472" s="26" t="inlineStr">
+        <is>
+          <t>Web Development Crash Courses</t>
+        </is>
+      </c>
+      <c r="E472" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=L4g6GGLzAyo</t>
+        </is>
+      </c>
+      <c r="F472" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G472" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/L4g6GGLzAyo" title="Web Development Crash Courses" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H472" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I472" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "A Better Way to Build Software with AI (Full Tutorial &amp; Workflow)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="26" t="inlineStr">
+        <is>
+          <t>Web Development — HTML, CSS &amp; JavaScript</t>
+        </is>
+      </c>
+      <c r="B473" s="26" t="inlineStr">
+        <is>
+          <t>Beginner/Intermediate</t>
+        </is>
+      </c>
+      <c r="C473" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Kevin Powell</t>
+        </is>
+      </c>
+      <c r="D473" s="26" t="inlineStr">
+        <is>
+          <t>CSS Mastery</t>
+        </is>
+      </c>
+      <c r="E473" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wazlBxxTohA</t>
+        </is>
+      </c>
+      <c r="F473" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G473" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/wazlBxxTohA" title="CSS Mastery" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H473" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I473" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Make a hover state stick forever with this simple trick".</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="26" t="inlineStr">
+        <is>
+          <t>Web Development — HTML, CSS &amp; JavaScript</t>
+        </is>
+      </c>
+      <c r="B474" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C474" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — JavaScript Mastery</t>
+        </is>
+      </c>
+      <c r="D474" s="26" t="inlineStr">
+        <is>
+          <t>Full-Stack Project Builds</t>
+        </is>
+      </c>
+      <c r="E474" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=R-UbDa1oRto</t>
+        </is>
+      </c>
+      <c r="F474" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G474" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/R-UbDa1oRto" title="Full-Stack Project Builds" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H474" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I474" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Why Developers Love React Native".</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="26" t="inlineStr">
+        <is>
+          <t>Frontend Frameworks (React, Next.js, Vue)</t>
+        </is>
+      </c>
+      <c r="B475" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C475" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Jack Herrington</t>
+        </is>
+      </c>
+      <c r="D475" s="26" t="inlineStr">
+        <is>
+          <t>Advanced React Patterns</t>
+        </is>
+      </c>
+      <c r="E475" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2aKGR4RECj0</t>
+        </is>
+      </c>
+      <c r="F475" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G475" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/2aKGR4RECj0" title="Advanced React Patterns" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H475" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I475" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "TanStack is Doing What?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="26" t="inlineStr">
+        <is>
+          <t>Backend, APIs &amp; System Design</t>
+        </is>
+      </c>
+      <c r="B476" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C476" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — ByteByteGo</t>
+        </is>
+      </c>
+      <c r="D476" s="26" t="inlineStr">
+        <is>
+          <t>System Design Fundamentals</t>
+        </is>
+      </c>
+      <c r="E476" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WvSVSbGo0wI</t>
+        </is>
+      </c>
+      <c r="F476" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G476" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/WvSVSbGo0wI" title="System Design Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H476" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I476" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "HTTP vs HTTPS Explained".</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="26" t="inlineStr">
+        <is>
+          <t>Java Programming</t>
+        </is>
+      </c>
+      <c r="B477" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C477" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Coding with John</t>
+        </is>
+      </c>
+      <c r="D477" s="26" t="inlineStr">
+        <is>
+          <t>Java Concepts Explained</t>
+        </is>
+      </c>
+      <c r="E477" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yg_UPwSD3-U</t>
+        </is>
+      </c>
+      <c r="F477" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G477" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/yg_UPwSD3-U" title="Java Concepts Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H477" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I477" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Volatile Keyword in Java Tutorial - The Fix for Impossible Bugs".</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="26" t="inlineStr">
+        <is>
+          <t>C, C++ &amp; Systems Programming</t>
+        </is>
+      </c>
+      <c r="B478" s="26" t="inlineStr">
+        <is>
+          <t>Intermediate/Advanced</t>
+        </is>
+      </c>
+      <c r="C478" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Cherno</t>
+        </is>
+      </c>
+      <c r="D478" s="26" t="inlineStr">
+        <is>
+          <t>C++ Series</t>
+        </is>
+      </c>
+      <c r="E478" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s0oN6Tx5Xxo</t>
+        </is>
+      </c>
+      <c r="F478" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G478" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/s0oN6Tx5Xxo" title="C++ Series" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H478" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I478" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "ls AI Code Actually BAD?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="26" t="inlineStr">
+        <is>
+          <t>C, C++ &amp; Systems Programming</t>
+        </is>
+      </c>
+      <c r="B479" s="26" t="inlineStr">
+        <is>
+          <t>Beginner/Intermediate</t>
+        </is>
+      </c>
+      <c r="C479" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — mycodeschool</t>
+        </is>
+      </c>
+      <c r="D479" s="26" t="inlineStr">
+        <is>
+          <t>C, C++ and Data Structures</t>
+        </is>
+      </c>
+      <c r="E479" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k1wraWzqtvQ</t>
+        </is>
+      </c>
+      <c r="F479" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G479" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/k1wraWzqtvQ" title="C, C++ and Data Structures" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H479" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I479" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Graph Representation part 03 - Adjacency List".</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="26" t="inlineStr">
+        <is>
+          <t>Other Languages (C#, Rust, Go, Kotlin, PHP)</t>
+        </is>
+      </c>
+      <c r="B480" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C480" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — IAmTimCorey</t>
+        </is>
+      </c>
+      <c r="D480" s="26" t="inlineStr">
+        <is>
+          <t>C# and .NET Development</t>
+        </is>
+      </c>
+      <c r="E480" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1edzGdmMRwI</t>
+        </is>
+      </c>
+      <c r="F480" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G480" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/1edzGdmMRwI" title="C# and .NET Development" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H480" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I480" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "322. How to Onboard a New Developer the Right Way".</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="26" t="inlineStr">
+        <is>
+          <t>Other Languages (C#, Rust, Go, Kotlin, PHP)</t>
+        </is>
+      </c>
+      <c r="B481" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C481" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Jon Gjengset</t>
+        </is>
+      </c>
+      <c r="D481" s="26" t="inlineStr">
+        <is>
+          <t>Rust Deep Dives (Crust of Rust)</t>
+        </is>
+      </c>
+      <c r="E481" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bAINppA0BSU</t>
+        </is>
+      </c>
+      <c r="F481" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G481" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/bAINppA0BSU" title="Rust Deep Dives (Crust of Rust)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H481" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I481" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Open Source Maintenance, 2026-07-18".</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="26" t="inlineStr">
+        <is>
+          <t>Data Structures &amp; Algorithms</t>
+        </is>
+      </c>
+      <c r="B482" s="26" t="inlineStr">
+        <is>
+          <t>Intermediate/Advanced</t>
+        </is>
+      </c>
+      <c r="C482" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Abdul Bari</t>
+        </is>
+      </c>
+      <c r="D482" s="26" t="inlineStr">
+        <is>
+          <t>Algorithms — Full Course</t>
+        </is>
+      </c>
+      <c r="E482" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rOocMVYI6Zs</t>
+        </is>
+      </c>
+      <c r="F482" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G482" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/rOocMVYI6Zs" title="Algorithms — Full Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H482" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I482" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Bresenham's Circle Drawing Algorithm - Computer Graphics".</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="26" t="inlineStr">
+        <is>
+          <t>Data Structures &amp; Algorithms</t>
+        </is>
+      </c>
+      <c r="B483" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C483" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Striver / take U forward</t>
+        </is>
+      </c>
+      <c r="D483" s="26" t="inlineStr">
+        <is>
+          <t>DSA Sheet Full Series</t>
+        </is>
+      </c>
+      <c r="E483" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LX00L2gDoow</t>
+        </is>
+      </c>
+      <c r="F483" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G483" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/LX00L2gDoow" title="DSA Sheet Full Series" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H483" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I483" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "No Internship in Your Resume ? |  Placement Series Ep. 2".</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="26" t="inlineStr">
+        <is>
+          <t>Databases &amp; SQL</t>
+        </is>
+      </c>
+      <c r="B484" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C484" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Programming with Mosh</t>
+        </is>
+      </c>
+      <c r="D484" s="26" t="inlineStr">
+        <is>
+          <t>MySQL Complete Course</t>
+        </is>
+      </c>
+      <c r="E484" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QuzttTTLyMk</t>
+        </is>
+      </c>
+      <c r="F484" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G484" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/QuzttTTLyMk" title="MySQL Complete Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H484" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I484" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Claude Code Tutorial Dropped #claude #claudecode".</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="26" t="inlineStr">
+        <is>
+          <t>Databases &amp; SQL</t>
+        </is>
+      </c>
+      <c r="B485" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C485" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Neso Academy</t>
+        </is>
+      </c>
+      <c r="D485" s="26" t="inlineStr">
+        <is>
+          <t>DBMS Full Course</t>
+        </is>
+      </c>
+      <c r="E485" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2cNuLDUAcRg</t>
+        </is>
+      </c>
+      <c r="F485" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G485" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/2cNuLDUAcRg" title="DBMS Full Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H485" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I485" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Half Subtractor using VHDL".</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="26" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="B486" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C486" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Stanford Online</t>
+        </is>
+      </c>
+      <c r="D486" s="26" t="inlineStr">
+        <is>
+          <t>CS229 — Machine Learning (full lectures)</t>
+        </is>
+      </c>
+      <c r="E486" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZXMThMHFD_w</t>
+        </is>
+      </c>
+      <c r="F486" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G486" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/ZXMThMHFD_w" title="CS229 — Machine Learning (full lectures)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H486" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I486" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Stanford AA203 Optimal and Learning-Based Control | Spring 2026 | Lecture 19: Model-Based RL".</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="26" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Neural Networks</t>
+        </is>
+      </c>
+      <c r="B487" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C487" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Andrej Karpathy</t>
+        </is>
+      </c>
+      <c r="D487" s="26" t="inlineStr">
+        <is>
+          <t>Neural Networks: Zero to Hero</t>
+        </is>
+      </c>
+      <c r="E487" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EWvNQjAaOHw</t>
+        </is>
+      </c>
+      <c r="F487" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G487" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/EWvNQjAaOHw" title="Neural Networks: Zero to Hero" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H487" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I487" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How I use LLMs".</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="26" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Neural Networks</t>
+        </is>
+      </c>
+      <c r="B488" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C488" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Umar Jamil</t>
+        </is>
+      </c>
+      <c r="D488" s="26" t="inlineStr">
+        <is>
+          <t>Transformers, LoRA, RLHF from Scratch</t>
+        </is>
+      </c>
+      <c r="E488" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BA6F8uYFPvM</t>
+        </is>
+      </c>
+      <c r="F488" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G488" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/BA6F8uYFPvM" title="Transformers, LoRA, RLHF from Scratch" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H488" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I488" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Umar Jamil Live Stream".</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="26" t="inlineStr">
+        <is>
+          <t>Large Language Models &amp; Generative AI</t>
+        </is>
+      </c>
+      <c r="B489" s="26" t="inlineStr">
+        <is>
+          <t>Beginner/Intermediate</t>
+        </is>
+      </c>
+      <c r="C489" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — DeepLearning.AI</t>
+        </is>
+      </c>
+      <c r="D489" s="26" t="inlineStr">
+        <is>
+          <t>Short Courses: Prompting, RAG, Agents, LangChain</t>
+        </is>
+      </c>
+      <c r="E489" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xUXJuPC7gz0</t>
+        </is>
+      </c>
+      <c r="F489" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G489" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/xUXJuPC7gz0" title="Short Courses: Prompting, RAG, Agents, LangChain" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H489" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I489" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Take back control of your AI coding workflow".</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="26" t="inlineStr">
+        <is>
+          <t>Large Language Models &amp; Generative AI</t>
+        </is>
+      </c>
+      <c r="B490" s="26" t="inlineStr">
+        <is>
+          <t>Beginner/Intermediate</t>
+        </is>
+      </c>
+      <c r="C490" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — 3Blue1Brown</t>
+        </is>
+      </c>
+      <c r="D490" s="26" t="inlineStr">
+        <is>
+          <t>Transformers &amp; Attention Visualised</t>
+        </is>
+      </c>
+      <c r="E490" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6XPlmCDNLNc</t>
+        </is>
+      </c>
+      <c r="F490" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G490" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/6XPlmCDNLNc" title="Transformers &amp; Attention Visualised" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H490" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I490" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The 64 sugar cubes puzzle".</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="26" t="inlineStr">
+        <is>
+          <t>Computer Vision</t>
+        </is>
+      </c>
+      <c r="B491" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C491" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Murtaza's Workshop</t>
+        </is>
+      </c>
+      <c r="D491" s="26" t="inlineStr">
+        <is>
+          <t>OpenCV &amp; Computer Vision Projects</t>
+        </is>
+      </c>
+      <c r="E491" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E_zUoHGcxRE</t>
+        </is>
+      </c>
+      <c r="F491" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G491" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/E_zUoHGcxRE" title="OpenCV &amp; Computer Vision Projects" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H491" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I491" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Learn Modern Computer Vision in 2026: From Basics to Advanced".</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="26" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B492" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C492" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Ken Jee</t>
+        </is>
+      </c>
+      <c r="D492" s="26" t="inlineStr">
+        <is>
+          <t>Data Science Career &amp; Projects</t>
+        </is>
+      </c>
+      <c r="E492" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3CRBW-0PuqA</t>
+        </is>
+      </c>
+      <c r="F492" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G492" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/3CRBW-0PuqA" title="Data Science Career &amp; Projects" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H492" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I492" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: ""Radicalized" About AI.".</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="26" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B493" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C493" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Data School</t>
+        </is>
+      </c>
+      <c r="D493" s="26" t="inlineStr">
+        <is>
+          <t>pandas Deep Dives</t>
+        </is>
+      </c>
+      <c r="E493" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DJZVAcwc4DI</t>
+        </is>
+      </c>
+      <c r="F493" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G493" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/DJZVAcwc4DI" title="pandas Deep Dives" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H493" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I493" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "My new book - on sale NEXT WEEK! 🎉".</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="26" t="inlineStr">
+        <is>
+          <t>Excel, Spreadsheets &amp; Business Tools</t>
+        </is>
+      </c>
+      <c r="B494" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C494" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Chandoo</t>
+        </is>
+      </c>
+      <c r="D494" s="26" t="inlineStr">
+        <is>
+          <t>Excel Dashboards &amp; Data Analysis</t>
+        </is>
+      </c>
+      <c r="E494" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Q3oqqYQz2gM</t>
+        </is>
+      </c>
+      <c r="F494" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G494" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/Q3oqqYQz2gM" title="Excel Dashboards &amp; Data Analysis" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H494" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I494" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Excel Heatmaps - 3 Ways to Make Them [Must have for Dashboards]".</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="26" t="inlineStr">
+        <is>
+          <t>Cybersecurity &amp; Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="B495" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C495" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — John Hammond</t>
+        </is>
+      </c>
+      <c r="D495" s="26" t="inlineStr">
+        <is>
+          <t>CTF Walkthroughs &amp; Malware Analysis</t>
+        </is>
+      </c>
+      <c r="E495" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SjT-_Rw9Gqc</t>
+        </is>
+      </c>
+      <c r="F495" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G495" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/SjT-_Rw9Gqc" title="CTF Walkthroughs &amp; Malware Analysis" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H495" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I495" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "AI Malware Gets Weird".</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="26" t="inlineStr">
+        <is>
+          <t>Cybersecurity &amp; Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="B496" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C496" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Professor Messer</t>
+        </is>
+      </c>
+      <c r="D496" s="26" t="inlineStr">
+        <is>
+          <t>Security+ / Network+ Certification Courses</t>
+        </is>
+      </c>
+      <c r="E496" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JszMBuIovMw</t>
+        </is>
+      </c>
+      <c r="F496" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G496" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/JszMBuIovMw" title="Security+ / Network+ Certification Courses" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H496" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I496" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Professor Messer's Security+ SY0-701 Study Group - September 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="26" t="inlineStr">
+        <is>
+          <t>Networking &amp; IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="B497" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C497" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — NetworkChuck</t>
+        </is>
+      </c>
+      <c r="D497" s="26" t="inlineStr">
+        <is>
+          <t>Networking Fundamentals &amp; CCNA</t>
+        </is>
+      </c>
+      <c r="E497" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=a3RI4DjFBzw</t>
+        </is>
+      </c>
+      <c r="F497" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G497" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/a3RI4DjFBzw" title="Networking Fundamentals &amp; CCNA" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H497" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I497" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "your home router STILL SUCKS!! (use OPNsense instead)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="26" t="inlineStr">
+        <is>
+          <t>DevOps, Cloud &amp; Containers</t>
+        </is>
+      </c>
+      <c r="B498" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C498" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — TechWorld with Nana</t>
+        </is>
+      </c>
+      <c r="D498" s="26" t="inlineStr">
+        <is>
+          <t>DevOps Bootcamp — Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="E498" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4TXpQnqLvLE</t>
+        </is>
+      </c>
+      <c r="F498" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G498" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/4TXpQnqLvLE" title="DevOps Bootcamp — Docker, Kubernetes, CI/CD" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H498" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I498" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How to Get Hired in DevOps WITHOUT a Tech Degree 💼🔥".</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="26" t="inlineStr">
+        <is>
+          <t>DevOps, Cloud &amp; Containers</t>
+        </is>
+      </c>
+      <c r="B499" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C499" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Google Cloud Tech</t>
+        </is>
+      </c>
+      <c r="D499" s="26" t="inlineStr">
+        <is>
+          <t>Official GCP Tutorials</t>
+        </is>
+      </c>
+      <c r="E499" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BFtkDiJYYHk</t>
+        </is>
+      </c>
+      <c r="F499" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G499" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/BFtkDiJYYHk" title="Official GCP Tutorials" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H499" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I499" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How to build AI agents with Gemini Enterprise &amp; Workspace".</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="26" t="inlineStr">
+        <is>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="B500" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C500" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Philipp Lackner</t>
+        </is>
+      </c>
+      <c r="D500" s="26" t="inlineStr">
+        <is>
+          <t>Android Development with Kotlin &amp; Jetpack Compose</t>
+        </is>
+      </c>
+      <c r="E500" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=svQAKu30C18</t>
+        </is>
+      </c>
+      <c r="F500" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G500" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/svQAKu30C18" title="Android Development with Kotlin &amp; Jetpack Compose" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H500" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I500" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Vertical vs. Horizontal Slicing - The ONLY Right Way to Split Down Your App".</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="26" t="inlineStr">
+        <is>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="B501" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C501" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Sean Allen</t>
+        </is>
+      </c>
+      <c r="D501" s="26" t="inlineStr">
+        <is>
+          <t>iOS &amp; Swift Development</t>
+        </is>
+      </c>
+      <c r="E501" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Q3tPGesg_e8</t>
+        </is>
+      </c>
+      <c r="F501" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G501" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/Q3tPGesg_e8" title="iOS &amp; Swift Development" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H501" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I501" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Shipaton ($700K in prizes), iOS 27 Breaking Changes, New Foundation Models Utilities &amp; More".</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="26" t="inlineStr">
+        <is>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="B502" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C502" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Academind</t>
+        </is>
+      </c>
+      <c r="D502" s="26" t="inlineStr">
+        <is>
+          <t>React Native Complete Guide</t>
+        </is>
+      </c>
+      <c r="E502" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=G-v1hkQ8Sf8</t>
+        </is>
+      </c>
+      <c r="F502" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G502" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/G-v1hkQ8Sf8" title="React Native Complete Guide" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H502" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I502" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Self-hosted Cloudflare?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="26" t="inlineStr">
+        <is>
+          <t>Game Development</t>
+        </is>
+      </c>
+      <c r="B503" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C503" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Sebastian Lague</t>
+        </is>
+      </c>
+      <c r="D503" s="26" t="inlineStr">
+        <is>
+          <t>Coding Adventures (procedural generation, AI)</t>
+        </is>
+      </c>
+      <c r="E503" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_JGMgpyCTsY</t>
+        </is>
+      </c>
+      <c r="F503" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G503" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/_JGMgpyCTsY" title="Coding Adventures (procedural generation, AI)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H503" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I503" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "I Tried Coding my own Graphics Library".</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="26" t="inlineStr">
+        <is>
+          <t>Game Development</t>
+        </is>
+      </c>
+      <c r="B504" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C504" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Unreal Engine</t>
+        </is>
+      </c>
+      <c r="D504" s="26" t="inlineStr">
+        <is>
+          <t>Official Unreal Learning Content</t>
+        </is>
+      </c>
+      <c r="E504" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VxX1aah6TZM</t>
+        </is>
+      </c>
+      <c r="F504" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G504" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/VxX1aah6TZM" title="Official Unreal Learning Content" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H504" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I504" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "UI Performance &amp; Invalidation Debugging | Unreal Fest Chicago 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="26" t="inlineStr">
+        <is>
+          <t>Robotics, Arduino &amp; Embedded Systems</t>
+        </is>
+      </c>
+      <c r="B505" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C505" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — DroneBot Workshop</t>
+        </is>
+      </c>
+      <c r="D505" s="26" t="inlineStr">
+        <is>
+          <t>Arduino, ESP32 &amp; Robotics Projects</t>
+        </is>
+      </c>
+      <c r="E505" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-P2dN1GSKz0</t>
+        </is>
+      </c>
+      <c r="F505" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G505" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/-P2dN1GSKz0" title="Arduino, ESP32 &amp; Robotics Projects" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H505" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I505" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "PiZZa - Turn a Raspberry Pi Zero into a High-Performance Microcontroller".</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="26" t="inlineStr">
+        <is>
+          <t>Electronics &amp; Circuit Theory</t>
+        </is>
+      </c>
+      <c r="B506" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C506" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — EEVblog</t>
+        </is>
+      </c>
+      <c r="D506" s="26" t="inlineStr">
+        <is>
+          <t>Test Equipment &amp; Electronics Engineering</t>
+        </is>
+      </c>
+      <c r="E506" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nNTaLhJzw14</t>
+        </is>
+      </c>
+      <c r="F506" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G506" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/nNTaLhJzw14" title="Test Equipment &amp; Electronics Engineering" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H506" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I506" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "EEVblog Now Available on Spotify!".</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="26" t="inlineStr">
+        <is>
+          <t>Mechanical, Civil &amp; General Engineering</t>
+        </is>
+      </c>
+      <c r="B507" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C507" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Real Engineering</t>
+        </is>
+      </c>
+      <c r="D507" s="26" t="inlineStr">
+        <is>
+          <t>Applied Engineering Case Studies</t>
+        </is>
+      </c>
+      <c r="E507" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UiPJbxryrkU</t>
+        </is>
+      </c>
+      <c r="F507" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G507" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/UiPJbxryrkU" title="Applied Engineering Case Studies" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H507" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I507" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Why Sagrada Familia Took 144 Years to Complete".</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="26" t="inlineStr">
+        <is>
+          <t>Finance, Accounting &amp; Investing</t>
+        </is>
+      </c>
+      <c r="B508" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C508" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Aswath Damodaran</t>
+        </is>
+      </c>
+      <c r="D508" s="26" t="inlineStr">
+        <is>
+          <t>Valuation &amp; Corporate Finance (NYU lectures)</t>
+        </is>
+      </c>
+      <c r="E508" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dNEWqinHrW8</t>
+        </is>
+      </c>
+      <c r="F508" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G508" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/dNEWqinHrW8" title="Valuation &amp; Corporate Finance (NYU lectures)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H508" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I508" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Lessons from Leo: The Dark Side of Investment Conviction!".</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="26" t="inlineStr">
+        <is>
+          <t>Business, Startups &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="B509" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C509" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Stanford eCorner</t>
+        </is>
+      </c>
+      <c r="D509" s="26" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Thought Leaders</t>
+        </is>
+      </c>
+      <c r="E509" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hUHhg-_pu6M</t>
+        </is>
+      </c>
+      <c r="F509" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G509" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/hUHhg-_pu6M" title="Entrepreneurial Thought Leaders" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H509" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I509" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Do What You Love".</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="26" t="inlineStr">
+        <is>
+          <t>Business, Startups &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="B510" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C510" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — a16z</t>
+        </is>
+      </c>
+      <c r="D510" s="26" t="inlineStr">
+        <is>
+          <t>Technology &amp; Market Analysis</t>
+        </is>
+      </c>
+      <c r="E510" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=P5iICDVn5gc</t>
+        </is>
+      </c>
+      <c r="F510" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G510" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/P5iICDVn5gc" title="Technology &amp; Market Analysis" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H510" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I510" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Inside Stripe's AI Strategy with Will Gaybrick".</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="26" t="inlineStr">
+        <is>
+          <t>Business, Startups &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="B511" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C511" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Ali Abdaal</t>
+        </is>
+      </c>
+      <c r="D511" s="26" t="inlineStr">
+        <is>
+          <t>Building an Online Business</t>
+        </is>
+      </c>
+      <c r="E511" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nH-sP5Afyxk</t>
+        </is>
+      </c>
+      <c r="F511" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G511" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/nH-sP5Afyxk" title="Building an Online Business" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H511" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I511" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Our new AI employee can give you $100 of free work - link in description!".</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="26" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Growth</t>
+        </is>
+      </c>
+      <c r="B512" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C512" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Neil Patel</t>
+        </is>
+      </c>
+      <c r="D512" s="26" t="inlineStr">
+        <is>
+          <t>Digital Marketing Tactics</t>
+        </is>
+      </c>
+      <c r="E512" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bx_8y4WkmCA</t>
+        </is>
+      </c>
+      <c r="F512" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G512" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/bx_8y4WkmCA" title="Digital Marketing Tactics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H512" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I512" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "AI Just Flipped Your Traffic Game #shorts".</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="26" t="inlineStr">
+        <is>
+          <t>Psychology &amp; Behavioural Science</t>
+        </is>
+      </c>
+      <c r="B513" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C513" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Psych2Go</t>
+        </is>
+      </c>
+      <c r="D513" s="26" t="inlineStr">
+        <is>
+          <t>Psychology Concepts Animated</t>
+        </is>
+      </c>
+      <c r="E513" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4oA0vHbmrdw</t>
+        </is>
+      </c>
+      <c r="F513" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G513" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/4oA0vHbmrdw" title="Psychology Concepts Animated" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H513" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I513" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "You Want to Talk... But You Can't".</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="26" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Critical Thinking</t>
+        </is>
+      </c>
+      <c r="B514" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C514" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The School of Life</t>
+        </is>
+      </c>
+      <c r="D514" s="26" t="inlineStr">
+        <is>
+          <t>Applied Philosophy &amp; Emotional Reasoning</t>
+        </is>
+      </c>
+      <c r="E514" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eF2ZSd0fD3A</t>
+        </is>
+      </c>
+      <c r="F514" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G514" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/eF2ZSd0fD3A" title="Applied Philosophy &amp; Emotional Reasoning" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H514" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I514" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The Fear of Ending our Relationships".</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="26" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="B515" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C515" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — OverSimplified</t>
+        </is>
+      </c>
+      <c r="D515" s="26" t="inlineStr">
+        <is>
+          <t>Major Wars &amp; Events Explained</t>
+        </is>
+      </c>
+      <c r="E515" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1BVJzaXv3rk</t>
+        </is>
+      </c>
+      <c r="F515" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G515" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/1BVJzaXv3rk" title="Major Wars &amp; Events Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H515" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I515" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The Second Punic War  - OverSimplified (Part 3)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="26" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="B516" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C516" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Historia Civilis</t>
+        </is>
+      </c>
+      <c r="D516" s="26" t="inlineStr">
+        <is>
+          <t>Roman &amp; Classical History</t>
+        </is>
+      </c>
+      <c r="E516" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=872JcpP3FEM</t>
+        </is>
+      </c>
+      <c r="F516" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G516" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/872JcpP3FEM" title="Roman &amp; Classical History" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H516" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I516" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The City.".</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="26" t="inlineStr">
+        <is>
+          <t>Geography &amp; Geopolitics</t>
+        </is>
+      </c>
+      <c r="B517" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C517" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — CGP Grey</t>
+        </is>
+      </c>
+      <c r="D517" s="26" t="inlineStr">
+        <is>
+          <t>Systems, Borders &amp; Politics Explained</t>
+        </is>
+      </c>
+      <c r="E517" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HSRmfNDk87s</t>
+        </is>
+      </c>
+      <c r="F517" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G517" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/HSRmfNDk87s" title="Systems, Borders &amp; Politics Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H517" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I517" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Why Runways Have to Be Repainted".</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="26" t="inlineStr">
+        <is>
+          <t>English Language &amp; Grammar (ESL)</t>
+        </is>
+      </c>
+      <c r="B518" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C518" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — BBC Learning English</t>
+        </is>
+      </c>
+      <c r="D518" s="26" t="inlineStr">
+        <is>
+          <t>English Grammar &amp; Vocabulary Courses</t>
+        </is>
+      </c>
+      <c r="E518" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tRM2teDhiPM</t>
+        </is>
+      </c>
+      <c r="F518" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G518" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/tRM2teDhiPM" title="English Grammar &amp; Vocabulary Courses" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H518" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I518" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "What cheers you up when you're in a bad mood? #realeasyenglish  #podcast  #bbclearningenglish".</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="26" t="inlineStr">
+        <is>
+          <t>English Language &amp; Grammar (ESL)</t>
+        </is>
+      </c>
+      <c r="B519" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C519" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — mmmEnglish</t>
+        </is>
+      </c>
+      <c r="D519" s="26" t="inlineStr">
+        <is>
+          <t>Grammar, Fluency &amp; Speaking Practice</t>
+        </is>
+      </c>
+      <c r="E519" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xgSIO5QV2C8</t>
+        </is>
+      </c>
+      <c r="F519" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G519" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/xgSIO5QV2C8" title="Grammar, Fluency &amp; Speaking Practice" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H519" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I519" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "IELTS Speaking Test (Part 2) practice".</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="26" t="inlineStr">
+        <is>
+          <t>IELTS Preparation</t>
+        </is>
+      </c>
+      <c r="B520" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C520" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — E2 IELTS</t>
+        </is>
+      </c>
+      <c r="D520" s="26" t="inlineStr">
+        <is>
+          <t>IELTS Full Preparation — All Four Skills</t>
+        </is>
+      </c>
+      <c r="E520" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FMzYOyd90UU</t>
+        </is>
+      </c>
+      <c r="F520" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G520" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/FMzYOyd90UU" title="IELTS Full Preparation — All Four Skills" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H520" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I520" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "IELTS Listening: All 6 Question Types for Band 8 (2026)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="26" t="inlineStr">
+        <is>
+          <t>IELTS Preparation</t>
+        </is>
+      </c>
+      <c r="B521" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C521" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — British Council</t>
+        </is>
+      </c>
+      <c r="D521" s="26" t="inlineStr">
+        <is>
+          <t>Official IELTS Preparation Videos</t>
+        </is>
+      </c>
+      <c r="E521" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IbTB4REtrmI</t>
+        </is>
+      </c>
+      <c r="F521" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G521" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/IbTB4REtrmI" title="Official IELTS Preparation Videos" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H521" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I521" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Do you code-switch or do you code-switch?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="26" t="inlineStr">
+        <is>
+          <t>SAT &amp; Digital SAT</t>
+        </is>
+      </c>
+      <c r="B522" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C522" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — SupertutorTV</t>
+        </is>
+      </c>
+      <c r="D522" s="26" t="inlineStr">
+        <is>
+          <t>Digital SAT Strategy &amp; Full Walkthroughs</t>
+        </is>
+      </c>
+      <c r="E522" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WBt--0FgQHg</t>
+        </is>
+      </c>
+      <c r="F522" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G522" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/WBt--0FgQHg" title="Digital SAT Strategy &amp; Full Walkthroughs" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H522" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I522" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Looking for a 1550+ SAT Score?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="26" t="inlineStr">
+        <is>
+          <t>GRE, GMAT &amp; Graduate Admissions Tests</t>
+        </is>
+      </c>
+      <c r="B523" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C523" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Magoosh</t>
+        </is>
+      </c>
+      <c r="D523" s="26" t="inlineStr">
+        <is>
+          <t>GRE &amp; GMAT Lessons</t>
+        </is>
+      </c>
+      <c r="E523" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lH6FFVl0pY8</t>
+        </is>
+      </c>
+      <c r="F523" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G523" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/lH6FFVl0pY8" title="GRE &amp; GMAT Lessons" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H523" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I523" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Study with me with this ACT reading passage. Let me know your answer in the comments! #shorts".</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="26" t="inlineStr">
+        <is>
+          <t>AI Safety, Ethics &amp; Policy</t>
+        </is>
+      </c>
+      <c r="B524" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C524" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Robert Miles AI Safety</t>
+        </is>
+      </c>
+      <c r="D524" s="26" t="inlineStr">
+        <is>
+          <t>AI Alignment Explained</t>
+        </is>
+      </c>
+      <c r="E524" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=guUpt1RCWkY</t>
+        </is>
+      </c>
+      <c r="F524" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G524" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/guUpt1RCWkY" title="AI Alignment Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H524" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I524" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Yyup...".</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="26" t="inlineStr">
+        <is>
+          <t>Blockchain, Web3 &amp; Quantum Computing</t>
+        </is>
+      </c>
+      <c r="B525" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C525" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Qiskit</t>
+        </is>
+      </c>
+      <c r="D525" s="26" t="inlineStr">
+        <is>
+          <t>Quantum Computing Course &amp; Summer School</t>
+        </is>
+      </c>
+      <c r="E525" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LeAI2PCmyb4</t>
+        </is>
+      </c>
+      <c r="F525" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G525" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/LeAI2PCmyb4" title="Quantum Computing Course &amp; Summer School" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H525" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I525" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Whats the least quantum thing about you? Ask a quantum intern.".</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="26" t="inlineStr">
+        <is>
+          <t>Design — UI/UX &amp; Graphic Design</t>
+        </is>
+      </c>
+      <c r="B526" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C526" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Futur</t>
+        </is>
+      </c>
+      <c r="D526" s="26" t="inlineStr">
+        <is>
+          <t>Design Business, Branding &amp; Typography</t>
+        </is>
+      </c>
+      <c r="E526" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BeYH1Y_vheI</t>
+        </is>
+      </c>
+      <c r="F526" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G526" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/BeYH1Y_vheI" title="Design Business, Branding &amp; Typography" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H526" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I526" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "You weren’t born normal. You learned to fit in.".</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="26" t="inlineStr">
+        <is>
+          <t>Design — UI/UX &amp; Graphic Design</t>
+        </is>
+      </c>
+      <c r="B527" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C527" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Figma</t>
+        </is>
+      </c>
+      <c r="D527" s="26" t="inlineStr">
+        <is>
+          <t>Official Figma Tutorials</t>
+        </is>
+      </c>
+      <c r="E527" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hfyEr4qGkhk</t>
+        </is>
+      </c>
+      <c r="F527" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G527" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/hfyEr4qGkhk" title="Official Figma Tutorials" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H527" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I527" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Really cooked with these comebacks ngl".</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="26" t="inlineStr">
+        <is>
+          <t>Art, Drawing &amp; 3D</t>
+        </is>
+      </c>
+      <c r="B528" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C528" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Blender Guru</t>
+        </is>
+      </c>
+      <c r="D528" s="26" t="inlineStr">
+        <is>
+          <t>Blender Donut Tutorial &amp; 3D Fundamentals</t>
+        </is>
+      </c>
+      <c r="E528" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JQyDVF5duzo</t>
+        </is>
+      </c>
+      <c r="F528" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G528" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/JQyDVF5duzo" title="Blender Donut Tutorial &amp; 3D Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H528" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I528" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The hardest thing to make in Blender".</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="26" t="inlineStr">
+        <is>
+          <t>Photography, Video &amp; Content Creation</t>
+        </is>
+      </c>
+      <c r="B529" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C529" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Sean Tucker</t>
+        </is>
+      </c>
+      <c r="D529" s="26" t="inlineStr">
+        <is>
+          <t>Photographic Philosophy &amp; Composition</t>
+        </is>
+      </c>
+      <c r="E529" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6s9tlYQM5wo</t>
+        </is>
+      </c>
+      <c r="F529" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G529" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/6s9tlYQM5wo" title="Photographic Philosophy &amp; Composition" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H529" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I529" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Why Street Photographers Don't Ask Permission".</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="26" t="inlineStr">
+        <is>
+          <t>Music Theory &amp; Instruments</t>
+        </is>
+      </c>
+      <c r="B530" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C530" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Rick Beato</t>
+        </is>
+      </c>
+      <c r="D530" s="26" t="inlineStr">
+        <is>
+          <t>Music Theory &amp; Ear Training</t>
+        </is>
+      </c>
+      <c r="E530" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KY3cOCWXpwg</t>
+        </is>
+      </c>
+      <c r="F530" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G530" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/KY3cOCWXpwg" title="Music Theory &amp; Ear Training" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H530" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I530" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Sean Ono Lennon on AI music #ai #music #shorts".</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="26" t="inlineStr">
+        <is>
+          <t>Music Theory &amp; Instruments</t>
+        </is>
+      </c>
+      <c r="B531" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C531" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Andrew Huang</t>
+        </is>
+      </c>
+      <c r="D531" s="26" t="inlineStr">
+        <is>
+          <t>Music Production &amp; Sound Design</t>
+        </is>
+      </c>
+      <c r="E531" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ptZ6KkIySlk</t>
+        </is>
+      </c>
+      <c r="F531" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G531" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/ptZ6KkIySlk" title="Music Production &amp; Sound Design" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H531" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I531" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "That time starpowerdrummer gave the game away".</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="26" t="inlineStr">
+        <is>
+          <t>Languages (Spanish, French, German, Japanese, Arabic)</t>
+        </is>
+      </c>
+      <c r="B532" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C532" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Easy German</t>
+        </is>
+      </c>
+      <c r="D532" s="26" t="inlineStr">
+        <is>
+          <t>German Conversation &amp; Grammar</t>
+        </is>
+      </c>
+      <c r="E532" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uBDIHuMJSe0</t>
+        </is>
+      </c>
+      <c r="F532" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G532" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/uBDIHuMJSe0" title="German Conversation &amp; Grammar" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H532" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I532" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Nachteile des Lebens in Hamburg #shorts #easygerman".</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="26" t="inlineStr">
+        <is>
+          <t>Public Speaking &amp; Communication</t>
+        </is>
+      </c>
+      <c r="B533" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C533" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Harvard Business Review</t>
+        </is>
+      </c>
+      <c r="D533" s="26" t="inlineStr">
+        <is>
+          <t>Persuasion &amp; Executive Presence</t>
+        </is>
+      </c>
+      <c r="E533" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=By3QJjokIcs</t>
+        </is>
+      </c>
+      <c r="F533" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G533" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/By3QJjokIcs" title="Persuasion &amp; Executive Presence" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H533" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I533" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "https://hbr.org/podcast/2026/07/how-leaders-can-use-ai-to-solve-real-business-problems".</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="26" t="inlineStr">
+        <is>
+          <t>Productivity, Study Skills &amp; Learning How to Learn</t>
+        </is>
+      </c>
+      <c r="B534" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C534" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Thomas Frank</t>
+        </is>
+      </c>
+      <c r="D534" s="26" t="inlineStr">
+        <is>
+          <t>Study Systems &amp; Notion Workflows</t>
+        </is>
+      </c>
+      <c r="E534" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vhqq4U3mnNQ</t>
+        </is>
+      </c>
+      <c r="F534" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G534" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/vhqq4U3mnNQ" title="Study Systems &amp; Notion Workflows" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H534" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I534" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "I never dread this workout".</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="26" t="inlineStr">
+        <is>
+          <t>Career, Interviews &amp; Professional Skills</t>
+        </is>
+      </c>
+      <c r="B535" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C535" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — NeetCode</t>
+        </is>
+      </c>
+      <c r="D535" s="26" t="inlineStr">
+        <is>
+          <t>Coding Interview Preparation</t>
+        </is>
+      </c>
+      <c r="E535" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bozpwivcZvs</t>
+        </is>
+      </c>
+      <c r="F535" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G535" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/bozpwivcZvs" title="Coding Interview Preparation" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H535" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I535" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "What happens when AI builds itself?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="26" t="inlineStr">
+        <is>
+          <t>Career, Interviews &amp; Professional Skills</t>
+        </is>
+      </c>
+      <c r="B536" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C536" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Jeff Su</t>
+        </is>
+      </c>
+      <c r="D536" s="26" t="inlineStr">
+        <is>
+          <t>Workplace &amp; Career Communication Skills</t>
+        </is>
+      </c>
+      <c r="E536" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cEEw1AbeysI</t>
+        </is>
+      </c>
+      <c r="F536" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G536" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/cEEw1AbeysI" title="Workplace &amp; Career Communication Skills" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H536" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I536" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Never Repeat Yourself to AI Again".</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="26" t="inlineStr">
+        <is>
+          <t>Health, Fitness &amp; Wellbeing</t>
+        </is>
+      </c>
+      <c r="B537" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C537" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Yoga With Adriene</t>
+        </is>
+      </c>
+      <c r="D537" s="26" t="inlineStr">
+        <is>
+          <t>Yoga for All Levels</t>
+        </is>
+      </c>
+      <c r="E537" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7ZQr_Um3Wlk</t>
+        </is>
+      </c>
+      <c r="F537" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G537" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/7ZQr_Um3Wlk" title="Yoga for All Levels" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H537" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I537" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Yoga For Tight Hamstrings &amp; Lower Back | Yoga With Adriene".</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="26" t="inlineStr">
+        <is>
+          <t>Life Skills, Cooking &amp; Practical Knowledge</t>
+        </is>
+      </c>
+      <c r="B538" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C538" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Joshua Weissman</t>
+        </is>
+      </c>
+      <c r="D538" s="26" t="inlineStr">
+        <is>
+          <t>Cooking Fundamentals &amp; Recipes</t>
+        </is>
+      </c>
+      <c r="E538" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iLe2PLFdIgY</t>
+        </is>
+      </c>
+      <c r="F538" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G538" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/iLe2PLFdIgY" title="Cooking Fundamentals &amp; Recipes" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H538" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I538" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Top 3 Brownie Hacks".</t>
         </is>
       </c>
     </row>

--- a/data/Global_Learning_Resource_Directory.xlsx
+++ b/data/Global_Learning_Resource_Directory.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I538"/>
+  <dimension ref="A1:I609"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="14" min="1" max="1"/>
@@ -26065,6 +26065,3343 @@
       <c r="I538" s="26" t="inlineStr">
         <is>
           <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Top 3 Brownie Hacks".</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="26" t="inlineStr">
+        <is>
+          <t>Algebra &amp; Pre-Calculus</t>
+        </is>
+      </c>
+      <c r="B539" s="26" t="inlineStr">
+        <is>
+          <t>School/College</t>
+        </is>
+      </c>
+      <c r="C539" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — PatrickJMT</t>
+        </is>
+      </c>
+      <c r="D539" s="26" t="inlineStr">
+        <is>
+          <t>Algebra &amp; Precalculus Playlists</t>
+        </is>
+      </c>
+      <c r="E539" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n9VlNs8jmKg</t>
+        </is>
+      </c>
+      <c r="F539" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G539" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/n9VlNs8jmKg" title="Algebra &amp; Precalculus Playlists" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H539" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I539" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Izzy of ‘Automatic’ at ‘The Mohawk’ Austin TX Oct 5th 2025".</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="26" t="inlineStr">
+        <is>
+          <t>Algebra &amp; Pre-Calculus</t>
+        </is>
+      </c>
+      <c r="B540" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C540" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — NancyPi</t>
+        </is>
+      </c>
+      <c r="D540" s="26" t="inlineStr">
+        <is>
+          <t>Algebra Essentials</t>
+        </is>
+      </c>
+      <c r="E540" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hc3hk294leY</t>
+        </is>
+      </c>
+      <c r="F540" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G540" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/hc3hk294leY" title="Algebra Essentials" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H540" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I540" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The Trick for Doing Trig (NancyPi)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="26" t="inlineStr">
+        <is>
+          <t>Algebra &amp; Pre-Calculus</t>
+        </is>
+      </c>
+      <c r="B541" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C541" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Mathologer</t>
+        </is>
+      </c>
+      <c r="D541" s="26" t="inlineStr">
+        <is>
+          <t>Algebraic Identities &amp; Proofs Visualised</t>
+        </is>
+      </c>
+      <c r="E541" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rUiulWItECQ</t>
+        </is>
+      </c>
+      <c r="F541" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G541" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/rUiulWItECQ" title="Algebraic Identities &amp; Proofs Visualised" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H541" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I541" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Parity of permutations, impossible puzzles and the magical determinant".</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="26" t="inlineStr">
+        <is>
+          <t>Calculus &amp; Advanced Mathematics</t>
+        </is>
+      </c>
+      <c r="B542" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C542" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — blackpenredpen</t>
+        </is>
+      </c>
+      <c r="D542" s="26" t="inlineStr">
+        <is>
+          <t>Integration Techniques &amp; Calculus 2</t>
+        </is>
+      </c>
+      <c r="E542" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dDr73Q0MsBA</t>
+        </is>
+      </c>
+      <c r="F542" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G542" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/dDr73Q0MsBA" title="Integration Techniques &amp; Calculus 2" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H542" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I542" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Limit of x^(y^z) as (x, y, z) goes to (0, 0, 0)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="26" t="inlineStr">
+        <is>
+          <t>Calculus &amp; Advanced Mathematics</t>
+        </is>
+      </c>
+      <c r="B543" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C543" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Zach Star</t>
+        </is>
+      </c>
+      <c r="D543" s="26" t="inlineStr">
+        <is>
+          <t>Where Advanced Math Is Actually Used</t>
+        </is>
+      </c>
+      <c r="E543" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BkWEhMWbPVs</t>
+        </is>
+      </c>
+      <c r="F543" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G543" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/BkWEhMWbPVs" title="Where Advanced Math Is Actually Used" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H543" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I543" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The algorithm from The Social Network".</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="26" t="inlineStr">
+        <is>
+          <t>Statistics, Probability &amp; Data Literacy</t>
+        </is>
+      </c>
+      <c r="B544" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C544" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — MarinStatsLectures</t>
+        </is>
+      </c>
+      <c r="D544" s="26" t="inlineStr">
+        <is>
+          <t>Statistics with R</t>
+        </is>
+      </c>
+      <c r="E544" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=URPVAvkM-HM</t>
+        </is>
+      </c>
+      <c r="F544" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G544" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/URPVAvkM-HM" title="Statistics with R" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H544" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I544" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "9.12 Poisson Regression: Why are model coefficients the log rate ratio?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="26" t="inlineStr">
+        <is>
+          <t>Physics — School &amp; AP</t>
+        </is>
+      </c>
+      <c r="B545" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C545" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Physics Wallah</t>
+        </is>
+      </c>
+      <c r="D545" s="26" t="inlineStr">
+        <is>
+          <t>Physics for Class 11-12 / JEE-NEET</t>
+        </is>
+      </c>
+      <c r="E545" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E-JyBHAF4GY</t>
+        </is>
+      </c>
+      <c r="F545" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G545" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/E-JyBHAF4GY" title="Physics for Class 11-12 / JEE-NEET" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H545" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I545" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "PW Launching CHESSMATE Ft. Vidit Gujrathi | NEW ERA IN CHESS - 🔴 LIVE".</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="26" t="inlineStr">
+        <is>
+          <t>Physics — University &amp; Theoretical</t>
+        </is>
+      </c>
+      <c r="B546" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C546" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Sixty Symbols</t>
+        </is>
+      </c>
+      <c r="D546" s="26" t="inlineStr">
+        <is>
+          <t>Physics with Nottingham Researchers</t>
+        </is>
+      </c>
+      <c r="E546" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6lX7VLnX2UE</t>
+        </is>
+      </c>
+      <c r="F546" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G546" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/6lX7VLnX2UE" title="Physics with Nottingham Researchers" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H546" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I546" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Burstiness - Sixty Symbols".</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="26" t="inlineStr">
+        <is>
+          <t>Biology &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B547" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C547" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Amoeba Sisters</t>
+        </is>
+      </c>
+      <c r="D547" s="26" t="inlineStr">
+        <is>
+          <t>Biology Concepts (cell, genetics, evolution)</t>
+        </is>
+      </c>
+      <c r="E547" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ShEzlXZPpPM</t>
+        </is>
+      </c>
+      <c r="F547" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G547" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/ShEzlXZPpPM" title="Biology Concepts (cell, genetics, evolution)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H547" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I547" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Mitosis (UPDATED 2026)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="26" t="inlineStr">
+        <is>
+          <t>Biology &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B548" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C548" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Bozeman Science</t>
+        </is>
+      </c>
+      <c r="D548" s="26" t="inlineStr">
+        <is>
+          <t>AP Biology Full Playlist</t>
+        </is>
+      </c>
+      <c r="E548" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6y8JOdjIU7M</t>
+        </is>
+      </c>
+      <c r="F548" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G548" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/6y8JOdjIU7M" title="AP Biology Full Playlist" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H548" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I548" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Artificial Intelligence in Education: A "Conversation"".</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy, Physiology &amp; Medicine</t>
+        </is>
+      </c>
+      <c r="B549" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C549" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Osmosis</t>
+        </is>
+      </c>
+      <c r="D549" s="26" t="inlineStr">
+        <is>
+          <t>Clinical &amp; Pathology Explainers</t>
+        </is>
+      </c>
+      <c r="E549" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QQWxvQVwXQc</t>
+        </is>
+      </c>
+      <c r="F549" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G549" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/QQWxvQVwXQc" title="Clinical &amp; Pathology Explainers" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H549" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I549" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Shock - Cardiogenic: Nursing".</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="26" t="inlineStr">
+        <is>
+          <t>Astronomy, Space &amp; Cosmology</t>
+        </is>
+      </c>
+      <c r="B550" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C550" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Kurzgesagt</t>
+        </is>
+      </c>
+      <c r="D550" s="26" t="inlineStr">
+        <is>
+          <t>Space, Cosmology &amp; Big Questions</t>
+        </is>
+      </c>
+      <c r="E550" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=U5-dE2nCzjM</t>
+        </is>
+      </c>
+      <c r="F550" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G550" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/U5-dE2nCzjM" title="Space, Cosmology &amp; Big Questions" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H550" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I550" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "What the Flu Does to Your Body".</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="26" t="inlineStr">
+        <is>
+          <t>Astronomy, Space &amp; Cosmology</t>
+        </is>
+      </c>
+      <c r="B551" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C551" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Dr. Becky</t>
+        </is>
+      </c>
+      <c r="D551" s="26" t="inlineStr">
+        <is>
+          <t>Astrophysics Research Explained</t>
+        </is>
+      </c>
+      <c r="E551" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W-jTv05JuEE</t>
+        </is>
+      </c>
+      <c r="F551" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G551" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/W-jTv05JuEE" title="Astrophysics Research Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H551" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I551" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Can Roman finally end the crisis in cosmology?! #shorts".</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="26" t="inlineStr">
+        <is>
+          <t>Astronomy, Space &amp; Cosmology</t>
+        </is>
+      </c>
+      <c r="B552" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C552" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — NASA</t>
+        </is>
+      </c>
+      <c r="D552" s="26" t="inlineStr">
+        <is>
+          <t>Mission Footage &amp; Explainers</t>
+        </is>
+      </c>
+      <c r="E552" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I_GUQdY01b0</t>
+        </is>
+      </c>
+      <c r="F552" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G552" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/I_GUQdY01b0" title="Mission Footage &amp; Explainers" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H552" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I552" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Special Event Announcement (Aug. 14, 2026)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="26" t="inlineStr">
+        <is>
+          <t>Earth, Environmental &amp; Climate Science</t>
+        </is>
+      </c>
+      <c r="B553" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C553" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Practical Engineering</t>
+        </is>
+      </c>
+      <c r="D553" s="26" t="inlineStr">
+        <is>
+          <t>Water, Soil &amp; Infrastructure Systems</t>
+        </is>
+      </c>
+      <c r="E553" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=stQfGfUSLQg</t>
+        </is>
+      </c>
+      <c r="F553" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G553" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/stQfGfUSLQg" title="Water, Soil &amp; Infrastructure Systems" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H553" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I553" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The Grid That Doubles the Strength of the Ground".</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="26" t="inlineStr">
+        <is>
+          <t>Python Programming</t>
+        </is>
+      </c>
+      <c r="B554" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C554" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — ArjanCodes</t>
+        </is>
+      </c>
+      <c r="D554" s="26" t="inlineStr">
+        <is>
+          <t>Software Design in Python</t>
+        </is>
+      </c>
+      <c r="E554" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ssLO99uwPWI</t>
+        </is>
+      </c>
+      <c r="F554" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G554" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/ssLO99uwPWI" title="Software Design in Python" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H554" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I554" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "15 Python Libraries That Deserve More Attention".</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="26" t="inlineStr">
+        <is>
+          <t>Python Programming</t>
+        </is>
+      </c>
+      <c r="B555" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C555" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Telusko</t>
+        </is>
+      </c>
+      <c r="D555" s="26" t="inlineStr">
+        <is>
+          <t>Python Programming Series</t>
+        </is>
+      </c>
+      <c r="E555" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=h-aSOm4Gkr0</t>
+        </is>
+      </c>
+      <c r="F555" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G555" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/h-aSOm4Gkr0" title="Python Programming Series" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H555" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I555" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "OpenAI Codex Complete Tutorial".</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="26" t="inlineStr">
+        <is>
+          <t>Web Development — HTML, CSS &amp; JavaScript</t>
+        </is>
+      </c>
+      <c r="B556" s="26" t="inlineStr">
+        <is>
+          <t>Beginner/Intermediate</t>
+        </is>
+      </c>
+      <c r="C556" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Web Dev Simplified</t>
+        </is>
+      </c>
+      <c r="D556" s="26" t="inlineStr">
+        <is>
+          <t>JavaScript &amp; CSS Concepts</t>
+        </is>
+      </c>
+      <c r="E556" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BH9ZgUYjiic</t>
+        </is>
+      </c>
+      <c r="F556" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G556" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/BH9ZgUYjiic" title="JavaScript &amp; CSS Concepts" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H556" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I556" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "I Wish This Was Better".</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="26" t="inlineStr">
+        <is>
+          <t>Web Development — HTML, CSS &amp; JavaScript</t>
+        </is>
+      </c>
+      <c r="B557" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C557" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Fireship</t>
+        </is>
+      </c>
+      <c r="D557" s="26" t="inlineStr">
+        <is>
+          <t>Web Tech in 100 Seconds + Deep Dives</t>
+        </is>
+      </c>
+      <c r="E557" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E7la7-dtfVM</t>
+        </is>
+      </c>
+      <c r="F557" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G557" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/E7la7-dtfVM" title="Web Tech in 100 Seconds + Deep Dives" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H557" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I557" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "This new startup can query anywhere you've been...".</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="26" t="inlineStr">
+        <is>
+          <t>Frontend Frameworks (React, Next.js, Vue)</t>
+        </is>
+      </c>
+      <c r="B558" s="26" t="inlineStr">
+        <is>
+          <t>Beginner/Intermediate</t>
+        </is>
+      </c>
+      <c r="C558" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Net Ninja</t>
+        </is>
+      </c>
+      <c r="D558" s="26" t="inlineStr">
+        <is>
+          <t>React, Vue &amp; Next.js Playlists</t>
+        </is>
+      </c>
+      <c r="E558" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5ePwfYBhgko</t>
+        </is>
+      </c>
+      <c r="F558" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G558" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/5ePwfYBhgko" title="React, Vue &amp; Next.js Playlists" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H558" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I558" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Firebase AI Logic #1 - Introduction &amp; Setup".</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="26" t="inlineStr">
+        <is>
+          <t>Frontend Frameworks (React, Next.js, Vue)</t>
+        </is>
+      </c>
+      <c r="B559" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C559" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Codevolution</t>
+        </is>
+      </c>
+      <c r="D559" s="26" t="inlineStr">
+        <is>
+          <t>React Full Course</t>
+        </is>
+      </c>
+      <c r="E559" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8X_XCuU0qx0</t>
+        </is>
+      </c>
+      <c r="F559" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G559" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/8X_XCuU0qx0" title="React Full Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H559" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I559" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How to get the most out of your $20 Claude Pro plan".</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="26" t="inlineStr">
+        <is>
+          <t>Java Programming</t>
+        </is>
+      </c>
+      <c r="B560" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C560" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — freeCodeCamp</t>
+        </is>
+      </c>
+      <c r="D560" s="26" t="inlineStr">
+        <is>
+          <t>Java Full Course</t>
+        </is>
+      </c>
+      <c r="E560" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iqRcGCah0Kw</t>
+        </is>
+      </c>
+      <c r="F560" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G560" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/iqRcGCah0Kw" title="Java Full Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H560" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I560" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "System Design for AI Agents – Building a Multi-Agent PR Reviewer".</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="26" t="inlineStr">
+        <is>
+          <t>Other Languages (C#, Rust, Go, Kotlin, PHP)</t>
+        </is>
+      </c>
+      <c r="B561" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C561" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Let's Get Rusty</t>
+        </is>
+      </c>
+      <c r="D561" s="26" t="inlineStr">
+        <is>
+          <t>Rust Programming Full Course</t>
+        </is>
+      </c>
+      <c r="E561" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vFp4IbC2aZ0</t>
+        </is>
+      </c>
+      <c r="F561" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G561" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/vFp4IbC2aZ0" title="Rust Programming Full Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H561" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I561" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How to decrease your Rust compile times by 50%".</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="26" t="inlineStr">
+        <is>
+          <t>Databases &amp; SQL</t>
+        </is>
+      </c>
+      <c r="B562" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C562" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Alex The Analyst</t>
+        </is>
+      </c>
+      <c r="D562" s="26" t="inlineStr">
+        <is>
+          <t>SQL for Data Analytics</t>
+        </is>
+      </c>
+      <c r="E562" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hWBDhdvAtQE</t>
+        </is>
+      </c>
+      <c r="F562" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G562" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/hWBDhdvAtQE" title="SQL for Data Analytics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H562" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I562" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "LinkedIn's War on AI Slop | Claude's going for Privacy | Tech Jobs Report".</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="26" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="B563" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C563" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — codebasics</t>
+        </is>
+      </c>
+      <c r="D563" s="26" t="inlineStr">
+        <is>
+          <t>Machine Learning with Python</t>
+        </is>
+      </c>
+      <c r="E563" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Hb1NuOIQ-wQ</t>
+        </is>
+      </c>
+      <c r="F563" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G563" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/Hb1NuOIQ-wQ" title="Machine Learning with Python" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H563" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I563" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "This Is Where Machine Learning Begins".</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="26" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Neural Networks</t>
+        </is>
+      </c>
+      <c r="B564" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C564" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Two Minute Papers</t>
+        </is>
+      </c>
+      <c r="D564" s="26" t="inlineStr">
+        <is>
+          <t>Research Highlights</t>
+        </is>
+      </c>
+      <c r="E564" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QnGNF8k_uoc</t>
+        </is>
+      </c>
+      <c r="F564" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G564" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/QnGNF8k_uoc" title="Research Highlights" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H564" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I564" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Claude AI Failed 650 Times…Then Beat The Human Record".</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="26" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B565" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C565" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Luke Barousse</t>
+        </is>
+      </c>
+      <c r="D565" s="26" t="inlineStr">
+        <is>
+          <t>Data Analytics with Python &amp; SQL</t>
+        </is>
+      </c>
+      <c r="E565" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ol9_NnC9-cc</t>
+        </is>
+      </c>
+      <c r="F565" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G565" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/ol9_NnC9-cc" title="Data Analytics with Python &amp; SQL" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H565" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I565" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Data Engineer Bootcamp (FREE 27+ Hour Course) - SQL, Python, Cloud, Bash, AI, Git &amp; GitHub".</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="26" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B566" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C566" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Keith Galli</t>
+        </is>
+      </c>
+      <c r="D566" s="26" t="inlineStr">
+        <is>
+          <t>Python Data Analysis (pandas, NumPy)</t>
+        </is>
+      </c>
+      <c r="E566" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3pLAjNH1uh0</t>
+        </is>
+      </c>
+      <c r="F566" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G566" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/3pLAjNH1uh0" title="Python Data Analysis (pandas, NumPy)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H566" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I566" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Comprehensive Analytics Reporting Tutorial with Python &amp; Quarto!".</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="26" t="inlineStr">
+        <is>
+          <t>Excel, Spreadsheets &amp; Business Tools</t>
+        </is>
+      </c>
+      <c r="B567" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C567" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Leila Gharani</t>
+        </is>
+      </c>
+      <c r="D567" s="26" t="inlineStr">
+        <is>
+          <t>Excel Advanced Formulas &amp; Dashboards</t>
+        </is>
+      </c>
+      <c r="E567" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s63hXFx9AHw</t>
+        </is>
+      </c>
+      <c r="F567" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G567" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/s63hXFx9AHw" title="Excel Advanced Formulas &amp; Dashboards" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H567" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I567" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The Excel function nobody reaches for... 🤯".</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="26" t="inlineStr">
+        <is>
+          <t>Cybersecurity &amp; Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="B568" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C568" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — David Bombal</t>
+        </is>
+      </c>
+      <c r="D568" s="26" t="inlineStr">
+        <is>
+          <t>Networking, Security &amp; Certification Prep</t>
+        </is>
+      </c>
+      <c r="E568" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=auO6PNiGuAg</t>
+        </is>
+      </c>
+      <c r="F568" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G568" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/auO6PNiGuAg" title="Networking, Security &amp; Certification Prep" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H568" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I568" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Microsoft Gave BitLocker Keys to FBI".</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="26" t="inlineStr">
+        <is>
+          <t>DevOps, Cloud &amp; Containers</t>
+        </is>
+      </c>
+      <c r="B569" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C569" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — KodeKloud</t>
+        </is>
+      </c>
+      <c r="D569" s="26" t="inlineStr">
+        <is>
+          <t>Kubernetes &amp; Certification Prep</t>
+        </is>
+      </c>
+      <c r="E569" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jKipg6vA3mE</t>
+        </is>
+      </c>
+      <c r="F569" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G569" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/jKipg6vA3mE" title="Kubernetes &amp; Certification Prep" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H569" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I569" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Crossplane vs Terraform: What's the Real Difference?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="26" t="inlineStr">
+        <is>
+          <t>Linux &amp; Operating Systems</t>
+        </is>
+      </c>
+      <c r="B570" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C570" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Learn Linux TV</t>
+        </is>
+      </c>
+      <c r="D570" s="26" t="inlineStr">
+        <is>
+          <t>Linux Essentials &amp; Server Administration</t>
+        </is>
+      </c>
+      <c r="E570" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6ay6jXBYEEk</t>
+        </is>
+      </c>
+      <c r="F570" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G570" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/6ay6jXBYEEk" title="Linux Essentials &amp; Server Administration" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H570" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I570" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "SteamOS on a Desktop PC Is Finally Here—and It’s Fantastic".</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="26" t="inlineStr">
+        <is>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="B571" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C571" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Flutter</t>
+        </is>
+      </c>
+      <c r="D571" s="26" t="inlineStr">
+        <is>
+          <t>Official Flutter Tutorials &amp; Widget of the Week</t>
+        </is>
+      </c>
+      <c r="E571" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ig-zOsnU5F4</t>
+        </is>
+      </c>
+      <c r="F571" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G571" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/Ig-zOsnU5F4" title="Official Flutter Tutorials &amp; Widget of the Week" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H571" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I571" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "A2UI 0.9.0 and GenUI".</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="26" t="inlineStr">
+        <is>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="B572" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C572" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — CodeWithChris</t>
+        </is>
+      </c>
+      <c r="D572" s="26" t="inlineStr">
+        <is>
+          <t>iOS Development for Beginners</t>
+        </is>
+      </c>
+      <c r="E572" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zc-_AxRowRY</t>
+        </is>
+      </c>
+      <c r="F572" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G572" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/zc-_AxRowRY" title="iOS Development for Beginners" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H572" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I572" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Codex CLI Tutorial: Install, Build &amp; Ship Apps with AI (Full Guide)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="26" t="inlineStr">
+        <is>
+          <t>Game Development</t>
+        </is>
+      </c>
+      <c r="B573" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C573" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Brackeys</t>
+        </is>
+      </c>
+      <c r="D573" s="26" t="inlineStr">
+        <is>
+          <t>Unity Game Development Tutorials</t>
+        </is>
+      </c>
+      <c r="E573" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=htRjt505sPg</t>
+        </is>
+      </c>
+      <c r="F573" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G573" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/htRjt505sPg" title="Unity Game Development Tutorials" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H573" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I573" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How to make VFX in Godot".</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="26" t="inlineStr">
+        <is>
+          <t>Game Development</t>
+        </is>
+      </c>
+      <c r="B574" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C574" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — GDQuest</t>
+        </is>
+      </c>
+      <c r="D574" s="26" t="inlineStr">
+        <is>
+          <t>Godot Engine Tutorials</t>
+        </is>
+      </c>
+      <c r="E574" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B_2goc0ZWyo</t>
+        </is>
+      </c>
+      <c r="F574" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G574" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/B_2goc0ZWyo" title="Godot Engine Tutorials" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H574" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I574" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "From Line to Lit! in 6 VFX  #knowledgenuggets #gamedev".</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="26" t="inlineStr">
+        <is>
+          <t>Robotics, Arduino &amp; Embedded Systems</t>
+        </is>
+      </c>
+      <c r="B575" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C575" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Paul McWhorter</t>
+        </is>
+      </c>
+      <c r="D575" s="26" t="inlineStr">
+        <is>
+          <t>Arduino Tutorials for Beginners (full series)</t>
+        </is>
+      </c>
+      <c r="E575" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CHcqFEvnDFM</t>
+        </is>
+      </c>
+      <c r="F575" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G575" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/CHcqFEvnDFM" title="Arduino Tutorials for Beginners (full series)" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H575" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I575" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "AI on the Edge LESSON 42: Create Composite Images Using Masks in OpenCV and MediaPipe".</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="26" t="inlineStr">
+        <is>
+          <t>Robotics, Arduino &amp; Embedded Systems</t>
+        </is>
+      </c>
+      <c r="B576" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C576" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — James Bruton</t>
+        </is>
+      </c>
+      <c r="D576" s="26" t="inlineStr">
+        <is>
+          <t>Experimental Robot Builds</t>
+        </is>
+      </c>
+      <c r="E576" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5YPduEo7dU4</t>
+        </is>
+      </c>
+      <c r="F576" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G576" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/5YPduEo7dU4" title="Experimental Robot Builds" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H576" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I576" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Using 20-sided dice to stabilise my walking machine?".</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="26" t="inlineStr">
+        <is>
+          <t>Electronics &amp; Circuit Theory</t>
+        </is>
+      </c>
+      <c r="B577" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C577" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — ElectroBOOM</t>
+        </is>
+      </c>
+      <c r="D577" s="26" t="inlineStr">
+        <is>
+          <t>Circuit Theory Through Failure</t>
+        </is>
+      </c>
+      <c r="E577" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Se1NPlfUCss</t>
+        </is>
+      </c>
+      <c r="F577" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G577" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/Se1NPlfUCss" title="Circuit Theory Through Failure" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H577" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I577" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Taser Knife Fighting at Open Sauce 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="26" t="inlineStr">
+        <is>
+          <t>Mechanical, Civil &amp; General Engineering</t>
+        </is>
+      </c>
+      <c r="B578" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C578" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Efficient Engineer</t>
+        </is>
+      </c>
+      <c r="D578" s="26" t="inlineStr">
+        <is>
+          <t>Mechanics of Materials &amp; Thermodynamics</t>
+        </is>
+      </c>
+      <c r="E578" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xKxHQ19sxkk</t>
+        </is>
+      </c>
+      <c r="F578" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G578" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/xKxHQ19sxkk" title="Mechanics of Materials &amp; Thermodynamics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H578" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I578" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The Explosion that Changed the Pipeline Industry".</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="26" t="inlineStr">
+        <is>
+          <t>Mechanical, Civil &amp; General Engineering</t>
+        </is>
+      </c>
+      <c r="B579" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C579" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Lesics</t>
+        </is>
+      </c>
+      <c r="D579" s="26" t="inlineStr">
+        <is>
+          <t>Mechanical Systems Animated</t>
+        </is>
+      </c>
+      <c r="E579" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LA0_U_3Ac4k</t>
+        </is>
+      </c>
+      <c r="F579" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G579" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/LA0_U_3Ac4k" title="Mechanical Systems Animated" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H579" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I579" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Jeddah Tower: How the World's Heaviest Building Defies the Desert Sand".</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="26" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="B580" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C580" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Jacob Clifford (ACDC Leadership)</t>
+        </is>
+      </c>
+      <c r="D580" s="26" t="inlineStr">
+        <is>
+          <t>AP Micro &amp; Macro Review</t>
+        </is>
+      </c>
+      <c r="E580" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cFd6ysbqCXk</t>
+        </is>
+      </c>
+      <c r="F580" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G580" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/cFd6ysbqCXk" title="AP Micro &amp; Macro Review" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H580" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I580" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Consumer Behavior | AP Business Topic 2.2".</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="26" t="inlineStr">
+        <is>
+          <t>Finance, Accounting &amp; Investing</t>
+        </is>
+      </c>
+      <c r="B581" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C581" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Accounting Stuff</t>
+        </is>
+      </c>
+      <c r="D581" s="26" t="inlineStr">
+        <is>
+          <t>Accounting Basics — Full Series</t>
+        </is>
+      </c>
+      <c r="E581" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ISNDfo8VG78</t>
+        </is>
+      </c>
+      <c r="F581" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G581" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/ISNDfo8VG78" title="Accounting Basics — Full Series" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H581" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I581" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Cash vs Accrual Methods Quiz: 20 Questions for Beginners".</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="26" t="inlineStr">
+        <is>
+          <t>Finance, Accounting &amp; Investing</t>
+        </is>
+      </c>
+      <c r="B582" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C582" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Ben Felix</t>
+        </is>
+      </c>
+      <c r="D582" s="26" t="inlineStr">
+        <is>
+          <t>Evidence-Based Investing</t>
+        </is>
+      </c>
+      <c r="E582" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=skc2T5fcoLY</t>
+        </is>
+      </c>
+      <c r="F582" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G582" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/skc2T5fcoLY" title="Evidence-Based Investing" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H582" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I582" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "When Compounding Works Against You".</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="26" t="inlineStr">
+        <is>
+          <t>Business, Startups &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="B583" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C583" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Y Combinator</t>
+        </is>
+      </c>
+      <c r="D583" s="26" t="inlineStr">
+        <is>
+          <t>Startup School — Full Lecture Series</t>
+        </is>
+      </c>
+      <c r="E583" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YEvLKzsEwMw</t>
+        </is>
+      </c>
+      <c r="F583" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G583" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/YEvLKzsEwMw" title="Startup School — Full Lecture Series" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H583" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I583" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Susan Kare: Designing Icons &amp; Graphics For the Original Mac".</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="26" t="inlineStr">
+        <is>
+          <t>Business, Startups &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="B584" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C584" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — TED</t>
+        </is>
+      </c>
+      <c r="D584" s="26" t="inlineStr">
+        <is>
+          <t>Business &amp; Leadership Talks</t>
+        </is>
+      </c>
+      <c r="E584" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ip77mh3Of0I</t>
+        </is>
+      </c>
+      <c r="F584" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G584" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/Ip77mh3Of0I" title="Business &amp; Leadership Talks" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H584" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I584" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Why Economic Inequality Is the Biggest Threat to Democracy | Sally Kohn | TED".</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="26" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Growth</t>
+        </is>
+      </c>
+      <c r="B585" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C585" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — HubSpot Marketing</t>
+        </is>
+      </c>
+      <c r="D585" s="26" t="inlineStr">
+        <is>
+          <t>Inbound Marketing &amp; Content Strategy</t>
+        </is>
+      </c>
+      <c r="E585" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zGCVaDX9y3U</t>
+        </is>
+      </c>
+      <c r="F585" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G585" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/zGCVaDX9y3U" title="Inbound Marketing &amp; Content Strategy" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H585" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I585" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Vibe Coding Explained (It's Not Scary)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="26" t="inlineStr">
+        <is>
+          <t>Psychology &amp; Behavioural Science</t>
+        </is>
+      </c>
+      <c r="B586" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C586" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Sprouts</t>
+        </is>
+      </c>
+      <c r="D586" s="26" t="inlineStr">
+        <is>
+          <t>Learning Theory &amp; Educational Psychology</t>
+        </is>
+      </c>
+      <c r="E586" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3xsfuDXEfd0</t>
+        </is>
+      </c>
+      <c r="F586" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G586" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/3xsfuDXEfd0" title="Learning Theory &amp; Educational Psychology" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H586" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I586" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The RACI Matrix Explained".</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="26" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="B587" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C587" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Extra History</t>
+        </is>
+      </c>
+      <c r="D587" s="26" t="inlineStr">
+        <is>
+          <t>Historical Narrative Series</t>
+        </is>
+      </c>
+      <c r="E587" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JrsF6jYu5R8</t>
+        </is>
+      </c>
+      <c r="F587" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G587" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/JrsF6jYu5R8" title="Historical Narrative Series" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H587" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I587" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Take THAT Potato Salad!".</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="26" t="inlineStr">
+        <is>
+          <t>Geography &amp; Geopolitics</t>
+        </is>
+      </c>
+      <c r="B588" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C588" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — RealLifeLore</t>
+        </is>
+      </c>
+      <c r="D588" s="26" t="inlineStr">
+        <is>
+          <t>Geography &amp; Geopolitical Analysis</t>
+        </is>
+      </c>
+      <c r="E588" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JjhyYOKmFGM</t>
+        </is>
+      </c>
+      <c r="F588" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G588" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/JjhyYOKmFGM" title="Geography &amp; Geopolitical Analysis" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H588" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I588" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How China Keeps Winning by Doing Nothing".</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="26" t="inlineStr">
+        <is>
+          <t>Geography &amp; Geopolitics</t>
+        </is>
+      </c>
+      <c r="B589" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C589" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Geography Now</t>
+        </is>
+      </c>
+      <c r="D589" s="26" t="inlineStr">
+        <is>
+          <t>Every Country Profiled</t>
+        </is>
+      </c>
+      <c r="E589" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=56pz7qiEtPQ</t>
+        </is>
+      </c>
+      <c r="F589" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G589" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/56pz7qiEtPQ" title="Every Country Profiled" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H589" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I589" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How to tell Indian writing systems apart".</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="26" t="inlineStr">
+        <is>
+          <t>English Language &amp; Grammar (ESL)</t>
+        </is>
+      </c>
+      <c r="B590" s="26" t="inlineStr">
+        <is>
+          <t>Beginner/Intermediate</t>
+        </is>
+      </c>
+      <c r="C590" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — English with Lucy</t>
+        </is>
+      </c>
+      <c r="D590" s="26" t="inlineStr">
+        <is>
+          <t>British English Pronunciation &amp; Grammar</t>
+        </is>
+      </c>
+      <c r="E590" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7MlMyOyersk</t>
+        </is>
+      </c>
+      <c r="F590" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G590" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/7MlMyOyersk" title="British English Pronunciation &amp; Grammar" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H590" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I590" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "You might be using 'to' wrong...".</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="26" t="inlineStr">
+        <is>
+          <t>English Language &amp; Grammar (ESL)</t>
+        </is>
+      </c>
+      <c r="B591" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C591" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Rachel's English</t>
+        </is>
+      </c>
+      <c r="D591" s="26" t="inlineStr">
+        <is>
+          <t>American Pronunciation Training</t>
+        </is>
+      </c>
+      <c r="E591" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sQ27dmGvWw0</t>
+        </is>
+      </c>
+      <c r="F591" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G591" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/sQ27dmGvWw0" title="American Pronunciation Training" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H591" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I591" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "What Does "Literally" Actually Mean? 🤔".</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="26" t="inlineStr">
+        <is>
+          <t>IELTS Preparation</t>
+        </is>
+      </c>
+      <c r="B592" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C592" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — IELTS Advantage</t>
+        </is>
+      </c>
+      <c r="D592" s="26" t="inlineStr">
+        <is>
+          <t>Writing Task 1 &amp; 2 Strategy</t>
+        </is>
+      </c>
+      <c r="E592" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gOZstN8hMmA</t>
+        </is>
+      </c>
+      <c r="F592" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G592" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/gOZstN8hMmA" title="Writing Task 1 &amp; 2 Strategy" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H592" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I592" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "He Took IELTS 4 Times, Stuck at 6.5. Then Said Scored 8.5 Overall.".</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="26" t="inlineStr">
+        <is>
+          <t>SAT &amp; Digital SAT</t>
+        </is>
+      </c>
+      <c r="B593" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C593" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — College Board</t>
+        </is>
+      </c>
+      <c r="D593" s="26" t="inlineStr">
+        <is>
+          <t>Official SAT Suite &amp; Bluebook Guidance</t>
+        </is>
+      </c>
+      <c r="E593" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IXw8mJH2kW8</t>
+        </is>
+      </c>
+      <c r="F593" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G593" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/IXw8mJH2kW8" title="Official SAT Suite &amp; Bluebook Guidance" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H593" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I593" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Studying for the SAT? Check out SAT Question of the Day. #SAT #SATprep".</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="26" t="inlineStr">
+        <is>
+          <t>GRE, GMAT &amp; Graduate Admissions Tests</t>
+        </is>
+      </c>
+      <c r="B594" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C594" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — GregMat</t>
+        </is>
+      </c>
+      <c r="D594" s="26" t="inlineStr">
+        <is>
+          <t>GRE Complete Preparation</t>
+        </is>
+      </c>
+      <c r="E594" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n_ReXuAF1Ro</t>
+        </is>
+      </c>
+      <c r="F594" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G594" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/n_ReXuAF1Ro" title="GRE Complete Preparation" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H594" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I594" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Arithmetic Progress Quiz #6 (Lessons 37 - 42)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="26" t="inlineStr">
+        <is>
+          <t>AI Safety, Ethics &amp; Policy</t>
+        </is>
+      </c>
+      <c r="B595" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C595" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Rational Animations</t>
+        </is>
+      </c>
+      <c r="D595" s="26" t="inlineStr">
+        <is>
+          <t>AI Risk &amp; Rationality Concepts</t>
+        </is>
+      </c>
+      <c r="E595" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yh4H4Ifp0Lk</t>
+        </is>
+      </c>
+      <c r="F595" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G595" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/yh4H4Ifp0Lk" title="AI Risk &amp; Rationality Concepts" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H595" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I595" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Rogue OpenAI models hacked Hugging Face to cheat on a test".</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="26" t="inlineStr">
+        <is>
+          <t>Blockchain, Web3 &amp; Quantum Computing</t>
+        </is>
+      </c>
+      <c r="B596" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C596" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Patrick Collins</t>
+        </is>
+      </c>
+      <c r="D596" s="26" t="inlineStr">
+        <is>
+          <t>Solidity, Blockchain &amp; Smart Contracts Full Course</t>
+        </is>
+      </c>
+      <c r="E596" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MyjINFu7-J4</t>
+        </is>
+      </c>
+      <c r="F596" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G596" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/MyjINFu7-J4" title="Solidity, Blockchain &amp; Smart Contracts Full Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H596" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I596" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Making a billion dollar app with Cygent and Claude".</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="26" t="inlineStr">
+        <is>
+          <t>Design — UI/UX &amp; Graphic Design</t>
+        </is>
+      </c>
+      <c r="B597" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C597" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — DesignCourse</t>
+        </is>
+      </c>
+      <c r="D597" s="26" t="inlineStr">
+        <is>
+          <t>UI Design &amp; Frontend Crossover</t>
+        </is>
+      </c>
+      <c r="E597" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_UYUAaAfvdA</t>
+        </is>
+      </c>
+      <c r="F597" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G597" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/_UYUAaAfvdA" title="UI Design &amp; Frontend Crossover" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H597" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I597" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Demo video of my most ambitious product".</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="26" t="inlineStr">
+        <is>
+          <t>Art, Drawing &amp; 3D</t>
+        </is>
+      </c>
+      <c r="B598" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C598" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Draw with Jazza</t>
+        </is>
+      </c>
+      <c r="D598" s="26" t="inlineStr">
+        <is>
+          <t>Drawing Challenges &amp; Techniques</t>
+        </is>
+      </c>
+      <c r="E598" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MLNvaaWDqOs</t>
+        </is>
+      </c>
+      <c r="F598" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G598" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/MLNvaaWDqOs" title="Drawing Challenges &amp; Techniques" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H598" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I598" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "We are Warriors - (Music Video)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="26" t="inlineStr">
+        <is>
+          <t>Photography, Video &amp; Content Creation</t>
+        </is>
+      </c>
+      <c r="B599" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C599" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Peter McKinnon</t>
+        </is>
+      </c>
+      <c r="D599" s="26" t="inlineStr">
+        <is>
+          <t>Photography &amp; Cinematography</t>
+        </is>
+      </c>
+      <c r="E599" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gUFP3dx01wc</t>
+        </is>
+      </c>
+      <c r="F599" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G599" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/gUFP3dx01wc" title="Photography &amp; Cinematography" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H599" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I599" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "rawdogging photos in nyc".</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="26" t="inlineStr">
+        <is>
+          <t>Photography, Video &amp; Content Creation</t>
+        </is>
+      </c>
+      <c r="B600" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C600" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Film Riot</t>
+        </is>
+      </c>
+      <c r="D600" s="26" t="inlineStr">
+        <is>
+          <t>Filmmaking &amp; VFX</t>
+        </is>
+      </c>
+      <c r="E600" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f4lIRqPIqrA</t>
+        </is>
+      </c>
+      <c r="F600" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G600" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/f4lIRqPIqrA" title="Filmmaking &amp; VFX" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H600" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I600" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Zero Gravity Space Effect".</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="26" t="inlineStr">
+        <is>
+          <t>Music Theory &amp; Instruments</t>
+        </is>
+      </c>
+      <c r="B601" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C601" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Adam Neely</t>
+        </is>
+      </c>
+      <c r="D601" s="26" t="inlineStr">
+        <is>
+          <t>Advanced Music Theory &amp; Rhythm</t>
+        </is>
+      </c>
+      <c r="E601" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zNf6_6liDbg</t>
+        </is>
+      </c>
+      <c r="F601" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G601" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/zNf6_6liDbg" title="Advanced Music Theory &amp; Rhythm" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H601" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I601" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "180bpm shred".</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="26" t="inlineStr">
+        <is>
+          <t>Languages (Spanish, French, German, Japanese, Arabic)</t>
+        </is>
+      </c>
+      <c r="B602" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C602" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Dreaming Spanish</t>
+        </is>
+      </c>
+      <c r="D602" s="26" t="inlineStr">
+        <is>
+          <t>Comprehensible Input Spanish</t>
+        </is>
+      </c>
+      <c r="E602" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ImIlt5KKM-s</t>
+        </is>
+      </c>
+      <c r="F602" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G602" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/ImIlt5KKM-s" title="Comprehensible Input Spanish" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H602" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I602" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How to order tapas - Simple Spanish".</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="26" t="inlineStr">
+        <is>
+          <t>Public Speaking &amp; Communication</t>
+        </is>
+      </c>
+      <c r="B603" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C603" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Charisma on Command</t>
+        </is>
+      </c>
+      <c r="D603" s="26" t="inlineStr">
+        <is>
+          <t>Social Skills &amp; Presence Analysis</t>
+        </is>
+      </c>
+      <c r="E603" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_Fh6SvCclwY</t>
+        </is>
+      </c>
+      <c r="F603" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G603" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/_Fh6SvCclwY" title="Social Skills &amp; Presence Analysis" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H603" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I603" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "How Mamdani Became Impossible to Ignore".</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="26" t="inlineStr">
+        <is>
+          <t>Productivity, Study Skills &amp; Learning How to Learn</t>
+        </is>
+      </c>
+      <c r="B604" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C604" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Med School Insiders</t>
+        </is>
+      </c>
+      <c r="D604" s="26" t="inlineStr">
+        <is>
+          <t>Deliberate Practice &amp; Study Efficiency</t>
+        </is>
+      </c>
+      <c r="E604" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9MVKkvLHQ_Q</t>
+        </is>
+      </c>
+      <c r="F604" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G604" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/9MVKkvLHQ_Q" title="Deliberate Practice &amp; Study Efficiency" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H604" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I604" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "10 Neurology Subspecialties Explained".</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="26" t="inlineStr">
+        <is>
+          <t>Career, Interviews &amp; Professional Skills</t>
+        </is>
+      </c>
+      <c r="B605" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C605" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Exponent</t>
+        </is>
+      </c>
+      <c r="D605" s="26" t="inlineStr">
+        <is>
+          <t>PM, Data &amp; Engineering Interview Practice</t>
+        </is>
+      </c>
+      <c r="E605" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=knEiqlfpV5k</t>
+        </is>
+      </c>
+      <c r="F605" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G605" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/knEiqlfpV5k" title="PM, Data &amp; Engineering Interview Practice" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H605" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I605" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Forward Deployed Engineer Interviews at LangChain".</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="26" t="inlineStr">
+        <is>
+          <t>Health, Fitness &amp; Wellbeing</t>
+        </is>
+      </c>
+      <c r="B606" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C606" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Athlean-X</t>
+        </is>
+      </c>
+      <c r="D606" s="26" t="inlineStr">
+        <is>
+          <t>Exercise Technique &amp; Injury Prevention</t>
+        </is>
+      </c>
+      <c r="E606" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-dhegeVKdgE</t>
+        </is>
+      </c>
+      <c r="F606" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G606" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/-dhegeVKdgE" title="Exercise Technique &amp; Injury Prevention" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H606" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I606" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "You Hate Your Saggy Chest (HERE'S HOW TO FIX IT!)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="26" t="inlineStr">
+        <is>
+          <t>Life Skills, Cooking &amp; Practical Knowledge</t>
+        </is>
+      </c>
+      <c r="B607" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C607" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Ethan Chlebowski</t>
+        </is>
+      </c>
+      <c r="D607" s="26" t="inlineStr">
+        <is>
+          <t>Cooking Technique &amp; Food Science</t>
+        </is>
+      </c>
+      <c r="E607" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wfYEk0lXtwE</t>
+        </is>
+      </c>
+      <c r="F607" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G607" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/wfYEk0lXtwE" title="Cooking Technique &amp; Food Science" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H607" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I607" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "I turned a Banh Mi into a high protein rice bowl.".</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="26" t="inlineStr">
+        <is>
+          <t>Life Skills, Cooking &amp; Practical Knowledge</t>
+        </is>
+      </c>
+      <c r="B608" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C608" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Adam Ragusea</t>
+        </is>
+      </c>
+      <c r="D608" s="26" t="inlineStr">
+        <is>
+          <t>Food Science &amp; Kitchen Reasoning</t>
+        </is>
+      </c>
+      <c r="E608" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xlM8X7KHveE</t>
+        </is>
+      </c>
+      <c r="F608" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G608" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/xlM8X7KHveE" title="Food Science &amp; Kitchen Reasoning" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H608" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I608" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "Standards to expect from YouTubers".</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="26" t="inlineStr">
+        <is>
+          <t>Law, Government &amp; Civics</t>
+        </is>
+      </c>
+      <c r="B609" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C609" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Yale Courses</t>
+        </is>
+      </c>
+      <c r="D609" s="26" t="inlineStr">
+        <is>
+          <t>Constitutional Law &amp; Political Philosophy</t>
+        </is>
+      </c>
+      <c r="E609" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=v0mycV8ovGQ</t>
+        </is>
+      </c>
+      <c r="F609" s="26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G609" s="26" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/v0mycV8ovGQ" title="Constitutional Law &amp; Political Philosophy" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
+        </is>
+      </c>
+      <c r="H609" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I609" s="26" t="inlineStr">
+        <is>
+          <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The Psychology of Negotiation: Q&amp;A with Barry Nalebuff and Daylian Cain".</t>
         </is>
       </c>
     </row>

--- a/data/Global_Learning_Resource_Directory.xlsx
+++ b/data/Global_Learning_Resource_Directory.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I609"/>
+  <dimension ref="A1:I753"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="14" min="1" max="1"/>
@@ -29402,6 +29402,6774 @@
       <c r="I609" s="26" t="inlineStr">
         <is>
           <t>Verified real video from this channel via YouTube Data API v3 on 17 August 2026. Latest upload at fetch time: "The Psychology of Negotiation: Q&amp;A with Barry Nalebuff and Daylian Cain".</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="26" t="inlineStr">
+        <is>
+          <t>Mathematics — Foundations &amp; Arithmetic</t>
+        </is>
+      </c>
+      <c r="B610" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C610" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — tecmath</t>
+        </is>
+      </c>
+      <c r="D610" s="26" t="inlineStr">
+        <is>
+          <t>Fast Mental Math Tricks</t>
+        </is>
+      </c>
+      <c r="E610" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=tecmath+Fast+Mental+Math+Tricks</t>
+        </is>
+      </c>
+      <c r="F610" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G610" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H610" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I610" s="26" t="inlineStr">
+        <is>
+          <t>Mental arithmetic shortcuts; very high engagement per video (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="26" t="inlineStr">
+        <is>
+          <t>Mathematics — Foundations &amp; Arithmetic</t>
+        </is>
+      </c>
+      <c r="B611" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C611" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Mario's Math Tutoring</t>
+        </is>
+      </c>
+      <c r="D611" s="26" t="inlineStr">
+        <is>
+          <t>Middle &amp; High School Math Playlists</t>
+        </is>
+      </c>
+      <c r="E611" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Mario%27s+Math+Tutoring+Middle+%26+High+School+Math+Playlists</t>
+        </is>
+      </c>
+      <c r="F611" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G611" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H611" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I611" s="26" t="inlineStr">
+        <is>
+          <t>Concise exam-focused walkthroughs (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="26" t="inlineStr">
+        <is>
+          <t>Calculus &amp; Advanced Mathematics</t>
+        </is>
+      </c>
+      <c r="B612" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C612" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Flammable Maths</t>
+        </is>
+      </c>
+      <c r="D612" s="26" t="inlineStr">
+        <is>
+          <t>Advanced Integration &amp; Series</t>
+        </is>
+      </c>
+      <c r="E612" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Flammable+Maths+Advanced+Integration+%26+Series</t>
+        </is>
+      </c>
+      <c r="F612" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G612" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H612" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I612" s="26" t="inlineStr">
+        <is>
+          <t>Niche, hard problems for enthusiasts (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="26" t="inlineStr">
+        <is>
+          <t>Linear Algebra</t>
+        </is>
+      </c>
+      <c r="B613" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C613" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Kimberly Brehm</t>
+        </is>
+      </c>
+      <c r="D613" s="26" t="inlineStr">
+        <is>
+          <t>Linear Algebra Course</t>
+        </is>
+      </c>
+      <c r="E613" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Kimberly+Brehm+Linear+Algebra+Course</t>
+        </is>
+      </c>
+      <c r="F613" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G613" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H613" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I613" s="26" t="inlineStr">
+        <is>
+          <t>Full semester coverage, textbook aligned (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="26" t="inlineStr">
+        <is>
+          <t>Statistics, Probability &amp; Data Literacy</t>
+        </is>
+      </c>
+      <c r="B614" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C614" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — jbstatistics</t>
+        </is>
+      </c>
+      <c r="D614" s="26" t="inlineStr">
+        <is>
+          <t>Introductory Statistics</t>
+        </is>
+      </c>
+      <c r="E614" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=jbstatistics+Introductory+Statistics</t>
+        </is>
+      </c>
+      <c r="F614" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G614" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H614" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I614" s="26" t="inlineStr">
+        <is>
+          <t>Precise, textbook-accurate short lectures (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="26" t="inlineStr">
+        <is>
+          <t>Statistics, Probability &amp; Data Literacy</t>
+        </is>
+      </c>
+      <c r="B615" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C615" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Brandon Foltz</t>
+        </is>
+      </c>
+      <c r="D615" s="26" t="inlineStr">
+        <is>
+          <t>Statistics 101</t>
+        </is>
+      </c>
+      <c r="E615" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Brandon+Foltz+Statistics+101</t>
+        </is>
+      </c>
+      <c r="F615" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G615" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H615" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I615" s="26" t="inlineStr">
+        <is>
+          <t>Slow, patient, beginner-friendly series (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="26" t="inlineStr">
+        <is>
+          <t>Physics — School &amp; AP</t>
+        </is>
+      </c>
+      <c r="B616" s="26" t="inlineStr">
+        <is>
+          <t>Elementary–Middle School</t>
+        </is>
+      </c>
+      <c r="C616" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Flipping Physics</t>
+        </is>
+      </c>
+      <c r="D616" s="26" t="inlineStr">
+        <is>
+          <t>AP Physics 1, 2 and C Playlists</t>
+        </is>
+      </c>
+      <c r="E616" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Flipping+Physics+AP+Physics+1%2C+2+and+C+Playlists</t>
+        </is>
+      </c>
+      <c r="F616" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G616" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H616" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I616" s="26" t="inlineStr">
+        <is>
+          <t>Built specifically around the AP curriculum (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="26" t="inlineStr">
+        <is>
+          <t>Physics — School &amp; AP</t>
+        </is>
+      </c>
+      <c r="B617" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C617" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Science ABC / MinutePhysics</t>
+        </is>
+      </c>
+      <c r="D617" s="26" t="inlineStr">
+        <is>
+          <t>Short Concept Explainers</t>
+        </is>
+      </c>
+      <c r="E617" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Science+ABC+%2F+MinutePhysics+Short+Concept+Explainers</t>
+        </is>
+      </c>
+      <c r="F617" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G617" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H617" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I617" s="26" t="inlineStr">
+        <is>
+          <t>Quick intuition builders between formal lessons (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="26" t="inlineStr">
+        <is>
+          <t>Physics — University &amp; Theoretical</t>
+        </is>
+      </c>
+      <c r="B618" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C618" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Leonard Susskind (Stanford)</t>
+        </is>
+      </c>
+      <c r="D618" s="26" t="inlineStr">
+        <is>
+          <t>The Theoretical Minimum Lecture Series</t>
+        </is>
+      </c>
+      <c r="E618" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Leonard+Susskind+%28Stanford%29+The+Theoretical+Minimum+Lecture+Series</t>
+        </is>
+      </c>
+      <c r="F618" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G618" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H618" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I618" s="26" t="inlineStr">
+        <is>
+          <t>Full graduate-level physics from a leading physicist (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="26" t="inlineStr">
+        <is>
+          <t>Physics — University &amp; Theoretical</t>
+        </is>
+      </c>
+      <c r="B619" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C619" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Physics Explained</t>
+        </is>
+      </c>
+      <c r="D619" s="26" t="inlineStr">
+        <is>
+          <t>Deep Derivations (Schrodinger, GR)</t>
+        </is>
+      </c>
+      <c r="E619" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Physics+Explained+Deep+Derivations+%28Schrodinger%2C+GR%29</t>
+        </is>
+      </c>
+      <c r="F619" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G619" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H619" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I619" s="26" t="inlineStr">
+        <is>
+          <t>Long-form derivations done properly (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="26" t="inlineStr">
+        <is>
+          <t>Physics — University &amp; Theoretical</t>
+        </is>
+      </c>
+      <c r="B620" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C620" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — ZAP Physics / Andrew Dotson</t>
+        </is>
+      </c>
+      <c r="D620" s="26" t="inlineStr">
+        <is>
+          <t>Computational &amp; Graduate Physics</t>
+        </is>
+      </c>
+      <c r="E620" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=ZAP+Physics+%2F+Andrew+Dotson+Computational+%26+Graduate+Physics</t>
+        </is>
+      </c>
+      <c r="F620" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G620" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H620" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I620" s="26" t="inlineStr">
+        <is>
+          <t>Grad-student perspective on hard problems (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="26" t="inlineStr">
+        <is>
+          <t>Chemistry — General</t>
+        </is>
+      </c>
+      <c r="B621" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C621" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Melissa Maribel</t>
+        </is>
+      </c>
+      <c r="D621" s="26" t="inlineStr">
+        <is>
+          <t>Chemistry Exam Prep</t>
+        </is>
+      </c>
+      <c r="E621" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Melissa+Maribel+Chemistry+Exam+Prep</t>
+        </is>
+      </c>
+      <c r="F621" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G621" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H621" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I621" s="26" t="inlineStr">
+        <is>
+          <t>Targeted at struggling first-year students (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="26" t="inlineStr">
+        <is>
+          <t>Chemistry — General</t>
+        </is>
+      </c>
+      <c r="B622" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C622" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Chad's Prep</t>
+        </is>
+      </c>
+      <c r="D622" s="26" t="inlineStr">
+        <is>
+          <t>General Chemistry &amp; MCAT Chemistry</t>
+        </is>
+      </c>
+      <c r="E622" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Chad%27s+Prep+General+Chemistry+%26+MCAT+Chemistry</t>
+        </is>
+      </c>
+      <c r="F622" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G622" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H622" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I622" s="26" t="inlineStr">
+        <is>
+          <t>Structured exam-focused course (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="26" t="inlineStr">
+        <is>
+          <t>Organic Chemistry</t>
+        </is>
+      </c>
+      <c r="B623" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C623" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Leah4sci</t>
+        </is>
+      </c>
+      <c r="D623" s="26" t="inlineStr">
+        <is>
+          <t>Organic Chemistry Reactions &amp; Mechanisms</t>
+        </is>
+      </c>
+      <c r="E623" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Leah4sci+Organic+Chemistry+Reactions+%26+Mechanisms</t>
+        </is>
+      </c>
+      <c r="F623" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G623" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H623" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I623" s="26" t="inlineStr">
+        <is>
+          <t>Mechanism-first teaching with practice problems (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="26" t="inlineStr">
+        <is>
+          <t>Organic Chemistry</t>
+        </is>
+      </c>
+      <c r="B624" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C624" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Chad's Prep</t>
+        </is>
+      </c>
+      <c r="D624" s="26" t="inlineStr">
+        <is>
+          <t>Organic Chemistry Course</t>
+        </is>
+      </c>
+      <c r="E624" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Chad%27s+Prep+Organic+Chemistry+Course</t>
+        </is>
+      </c>
+      <c r="F624" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G624" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H624" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I624" s="26" t="inlineStr">
+        <is>
+          <t>Exam-oriented structured lessons (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="26" t="inlineStr">
+        <is>
+          <t>Organic Chemistry</t>
+        </is>
+      </c>
+      <c r="B625" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C625" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Frank Wong / OChem Tutor channels</t>
+        </is>
+      </c>
+      <c r="D625" s="26" t="inlineStr">
+        <is>
+          <t>Synthesis Problem Solving</t>
+        </is>
+      </c>
+      <c r="E625" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Frank+Wong+%2F+OChem+Tutor+channels+Synthesis+Problem+Solving</t>
+        </is>
+      </c>
+      <c r="F625" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G625" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H625" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I625" s="26" t="inlineStr">
+        <is>
+          <t>Multi-step synthesis practice (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="26" t="inlineStr">
+        <is>
+          <t>Biology &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B626" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C626" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — iBiology</t>
+        </is>
+      </c>
+      <c r="D626" s="26" t="inlineStr">
+        <is>
+          <t>Research Talks by Working Biologists</t>
+        </is>
+      </c>
+      <c r="E626" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=iBiology+Research+Talks+by+Working+Biologists</t>
+        </is>
+      </c>
+      <c r="F626" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G626" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H626" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I626" s="26" t="inlineStr">
+        <is>
+          <t>Frontier research explained by the scientists doing it (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy, Physiology &amp; Medicine</t>
+        </is>
+      </c>
+      <c r="B627" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C627" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Khan Academy Medicine</t>
+        </is>
+      </c>
+      <c r="D627" s="26" t="inlineStr">
+        <is>
+          <t>Health &amp; Medicine Playlists</t>
+        </is>
+      </c>
+      <c r="E627" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Khan+Academy+Medicine+Health+%26+Medicine+Playlists</t>
+        </is>
+      </c>
+      <c r="F627" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G627" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H627" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I627" s="26" t="inlineStr">
+        <is>
+          <t>Free MCAT-aligned coverage (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy, Physiology &amp; Medicine</t>
+        </is>
+      </c>
+      <c r="B628" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C628" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Dr. Matt &amp; Dr. Mike</t>
+        </is>
+      </c>
+      <c r="D628" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy &amp; Physiology</t>
+        </is>
+      </c>
+      <c r="E628" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Dr.+Matt+%26+Dr.+Mike+Anatomy+%26+Physiology</t>
+        </is>
+      </c>
+      <c r="F628" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G628" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H628" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I628" s="26" t="inlineStr">
+        <is>
+          <t>Two-lecturer format covering full A&amp;P syllabus (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy, Physiology &amp; Medicine</t>
+        </is>
+      </c>
+      <c r="B629" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C629" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — TeachMeAnatomy / Kenhub</t>
+        </is>
+      </c>
+      <c r="D629" s="26" t="inlineStr">
+        <is>
+          <t>Anatomy Regional Playlists</t>
+        </is>
+      </c>
+      <c r="E629" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=TeachMeAnatomy+%2F+Kenhub+Anatomy+Regional+Playlists</t>
+        </is>
+      </c>
+      <c r="F629" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G629" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H629" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I629" s="26" t="inlineStr">
+        <is>
+          <t>Structured regional anatomy revision (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="26" t="inlineStr">
+        <is>
+          <t>Astronomy, Space &amp; Cosmology</t>
+        </is>
+      </c>
+      <c r="B630" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C630" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Launch Pad Astronomy</t>
+        </is>
+      </c>
+      <c r="D630" s="26" t="inlineStr">
+        <is>
+          <t>Astronomy Concepts</t>
+        </is>
+      </c>
+      <c r="E630" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Launch+Pad+Astronomy+Astronomy+Concepts</t>
+        </is>
+      </c>
+      <c r="F630" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G630" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H630" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I630" s="26" t="inlineStr">
+        <is>
+          <t>Well-structured teaching of core astronomy (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="26" t="inlineStr">
+        <is>
+          <t>Earth, Environmental &amp; Climate Science</t>
+        </is>
+      </c>
+      <c r="B631" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C631" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Simon Clark</t>
+        </is>
+      </c>
+      <c r="D631" s="26" t="inlineStr">
+        <is>
+          <t>Climate Science &amp; Atmospheric Physics</t>
+        </is>
+      </c>
+      <c r="E631" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Simon+Clark+Climate+Science+%26+Atmospheric+Physics</t>
+        </is>
+      </c>
+      <c r="F631" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G631" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H631" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I631" s="26" t="inlineStr">
+        <is>
+          <t>PhD-level climate explanation for general audiences (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="26" t="inlineStr">
+        <is>
+          <t>Earth, Environmental &amp; Climate Science</t>
+        </is>
+      </c>
+      <c r="B632" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C632" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — National Geographic</t>
+        </is>
+      </c>
+      <c r="D632" s="26" t="inlineStr">
+        <is>
+          <t>Earth &amp; Environment Documentaries</t>
+        </is>
+      </c>
+      <c r="E632" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=National+Geographic+Earth+%26+Environment+Documentaries</t>
+        </is>
+      </c>
+      <c r="F632" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G632" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H632" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I632" s="26" t="inlineStr">
+        <is>
+          <t>High-quality documentary source (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="26" t="inlineStr">
+        <is>
+          <t>Computer Science Fundamentals</t>
+        </is>
+      </c>
+      <c r="B633" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C633" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Gate Smashers</t>
+        </is>
+      </c>
+      <c r="D633" s="26" t="inlineStr">
+        <is>
+          <t>CS Core Subjects (exam-focused)</t>
+        </is>
+      </c>
+      <c r="E633" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Gate+Smashers+CS+Core+Subjects+%28exam-focused%29</t>
+        </is>
+      </c>
+      <c r="F633" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G633" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H633" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I633" s="26" t="inlineStr">
+        <is>
+          <t>Rapid revision for competitive CS exams (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="26" t="inlineStr">
+        <is>
+          <t>Python Programming</t>
+        </is>
+      </c>
+      <c r="B634" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C634" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Real Python</t>
+        </is>
+      </c>
+      <c r="D634" s="26" t="inlineStr">
+        <is>
+          <t>Python Concepts &amp; Tooling</t>
+        </is>
+      </c>
+      <c r="E634" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Real+Python+Python+Concepts+%26+Tooling</t>
+        </is>
+      </c>
+      <c r="F634" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G634" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H634" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I634" s="26" t="inlineStr">
+        <is>
+          <t>Companion to the well-known written tutorials (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="26" t="inlineStr">
+        <is>
+          <t>Python Programming</t>
+        </is>
+      </c>
+      <c r="B635" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C635" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — CS Dojo</t>
+        </is>
+      </c>
+      <c r="D635" s="26" t="inlineStr">
+        <is>
+          <t>Python for Beginners &amp; Interviews</t>
+        </is>
+      </c>
+      <c r="E635" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=CS+Dojo+Python+for+Beginners+%26+Interviews</t>
+        </is>
+      </c>
+      <c r="F635" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G635" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H635" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I635" s="26" t="inlineStr">
+        <is>
+          <t>Beginner to interview-prep bridge (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="26" t="inlineStr">
+        <is>
+          <t>Web Development — HTML, CSS &amp; JavaScript</t>
+        </is>
+      </c>
+      <c r="B636" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C636" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Wes Bos</t>
+        </is>
+      </c>
+      <c r="D636" s="26" t="inlineStr">
+        <is>
+          <t>JavaScript30 and Modern JS</t>
+        </is>
+      </c>
+      <c r="E636" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Wes+Bos+JavaScript30+and+Modern+JS</t>
+        </is>
+      </c>
+      <c r="F636" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G636" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H636" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I636" s="26" t="inlineStr">
+        <is>
+          <t>Practical vanilla-JS challenge series (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="26" t="inlineStr">
+        <is>
+          <t>Frontend Frameworks (React, Next.js, Vue)</t>
+        </is>
+      </c>
+      <c r="B637" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C637" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Vercel</t>
+        </is>
+      </c>
+      <c r="D637" s="26" t="inlineStr">
+        <is>
+          <t>Next.js Official Talks &amp; Tutorials</t>
+        </is>
+      </c>
+      <c r="E637" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Vercel+Next.js+Official+Talks+%26+Tutorials</t>
+        </is>
+      </c>
+      <c r="F637" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G637" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H637" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I637" s="26" t="inlineStr">
+        <is>
+          <t>Primary source from the framework team (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="26" t="inlineStr">
+        <is>
+          <t>Backend, APIs &amp; System Design</t>
+        </is>
+      </c>
+      <c r="B638" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C638" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Hussein Nasser</t>
+        </is>
+      </c>
+      <c r="D638" s="26" t="inlineStr">
+        <is>
+          <t>Backend Engineering &amp; Networking Deep Dives</t>
+        </is>
+      </c>
+      <c r="E638" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@hnasser</t>
+        </is>
+      </c>
+      <c r="F638" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G638" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H638" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I638" s="26" t="inlineStr">
+        <is>
+          <t>Protocol-level backend understanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="26" t="inlineStr">
+        <is>
+          <t>Backend, APIs &amp; System Design</t>
+        </is>
+      </c>
+      <c r="B639" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C639" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Arpit Bhayani</t>
+        </is>
+      </c>
+      <c r="D639" s="26" t="inlineStr">
+        <is>
+          <t>Distributed Systems Deep Dives</t>
+        </is>
+      </c>
+      <c r="E639" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Arpit+Bhayani+Distributed+Systems+Deep+Dives</t>
+        </is>
+      </c>
+      <c r="F639" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G639" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H639" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I639" s="26" t="inlineStr">
+        <is>
+          <t>Rigorous internals content (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="26" t="inlineStr">
+        <is>
+          <t>Backend, APIs &amp; System Design</t>
+        </is>
+      </c>
+      <c r="B640" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C640" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Tech Dummies Narendra L</t>
+        </is>
+      </c>
+      <c r="D640" s="26" t="inlineStr">
+        <is>
+          <t>System Design Case Studies</t>
+        </is>
+      </c>
+      <c r="E640" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Tech+Dummies+Narendra+L+System+Design+Case+Studies</t>
+        </is>
+      </c>
+      <c r="F640" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G640" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H640" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I640" s="26" t="inlineStr">
+        <is>
+          <t>Real architectures of well-known products (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="26" t="inlineStr">
+        <is>
+          <t>C, C++ &amp; Systems Programming</t>
+        </is>
+      </c>
+      <c r="B641" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C641" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — CodeBeauty</t>
+        </is>
+      </c>
+      <c r="D641" s="26" t="inlineStr">
+        <is>
+          <t>C++ for Beginners</t>
+        </is>
+      </c>
+      <c r="E641" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=CodeBeauty+C%2B%2B+for+Beginners</t>
+        </is>
+      </c>
+      <c r="F641" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G641" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H641" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I641" s="26" t="inlineStr">
+        <is>
+          <t>Approachable teaching style (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="26" t="inlineStr">
+        <is>
+          <t>C, C++ &amp; Systems Programming</t>
+        </is>
+      </c>
+      <c r="B642" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C642" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Jacob Sorber</t>
+        </is>
+      </c>
+      <c r="D642" s="26" t="inlineStr">
+        <is>
+          <t>Systems Programming in C</t>
+        </is>
+      </c>
+      <c r="E642" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Jacob+Sorber+Systems+Programming+in+C</t>
+        </is>
+      </c>
+      <c r="F642" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G642" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H642" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I642" s="26" t="inlineStr">
+        <is>
+          <t>Low-level OS and memory topics (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="26" t="inlineStr">
+        <is>
+          <t>C, C++ &amp; Systems Programming</t>
+        </is>
+      </c>
+      <c r="B643" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C643" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Low Level Learning</t>
+        </is>
+      </c>
+      <c r="D643" s="26" t="inlineStr">
+        <is>
+          <t>Systems, Embedded &amp; Memory</t>
+        </is>
+      </c>
+      <c r="E643" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Low+Level+Learning+Systems%2C+Embedded+%26+Memory</t>
+        </is>
+      </c>
+      <c r="F643" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G643" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H643" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I643" s="26" t="inlineStr">
+        <is>
+          <t>Modern low-level programming content (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="26" t="inlineStr">
+        <is>
+          <t>Other Languages (C#, Rust, Go, Kotlin, PHP)</t>
+        </is>
+      </c>
+      <c r="B644" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C644" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — No Boilerplate</t>
+        </is>
+      </c>
+      <c r="D644" s="26" t="inlineStr">
+        <is>
+          <t>Rust Concepts &amp; Philosophy</t>
+        </is>
+      </c>
+      <c r="E644" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=No+Boilerplate+Rust+Concepts+%26+Philosophy</t>
+        </is>
+      </c>
+      <c r="F644" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G644" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H644" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I644" s="26" t="inlineStr">
+        <is>
+          <t>High-signal short explanations (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="26" t="inlineStr">
+        <is>
+          <t>Other Languages (C#, Rust, Go, Kotlin, PHP)</t>
+        </is>
+      </c>
+      <c r="B645" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C645" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Program With Gio</t>
+        </is>
+      </c>
+      <c r="D645" s="26" t="inlineStr">
+        <is>
+          <t>PHP &amp; Laravel</t>
+        </is>
+      </c>
+      <c r="E645" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Program+With+Gio+PHP+%26+Laravel</t>
+        </is>
+      </c>
+      <c r="F645" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G645" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H645" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I645" s="26" t="inlineStr">
+        <is>
+          <t>Structured modern PHP (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="26" t="inlineStr">
+        <is>
+          <t>Data Structures &amp; Algorithms</t>
+        </is>
+      </c>
+      <c r="B646" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C646" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — William Fiset</t>
+        </is>
+      </c>
+      <c r="D646" s="26" t="inlineStr">
+        <is>
+          <t>Data Structures &amp; Graph Theory</t>
+        </is>
+      </c>
+      <c r="E646" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=William+Fiset+Data+Structures+%26+Graph+Theory</t>
+        </is>
+      </c>
+      <c r="F646" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G646" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H646" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I646" s="26" t="inlineStr">
+        <is>
+          <t>Rigorous, implementation-focused (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="26" t="inlineStr">
+        <is>
+          <t>Data Structures &amp; Algorithms</t>
+        </is>
+      </c>
+      <c r="B647" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C647" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Back To Back SWE</t>
+        </is>
+      </c>
+      <c r="D647" s="26" t="inlineStr">
+        <is>
+          <t>Algorithm Problem Breakdowns</t>
+        </is>
+      </c>
+      <c r="E647" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Back+To+Back+SWE+Algorithm+Problem+Breakdowns</t>
+        </is>
+      </c>
+      <c r="F647" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G647" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H647" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I647" s="26" t="inlineStr">
+        <is>
+          <t>Deep reasoning through each problem (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="26" t="inlineStr">
+        <is>
+          <t>Data Structures &amp; Algorithms</t>
+        </is>
+      </c>
+      <c r="B648" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C648" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Tushar Roy</t>
+        </is>
+      </c>
+      <c r="D648" s="26" t="inlineStr">
+        <is>
+          <t>Coding Interview Problem Walkthroughs</t>
+        </is>
+      </c>
+      <c r="E648" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Tushar+Roy+Coding+Interview+Problem+Walkthroughs</t>
+        </is>
+      </c>
+      <c r="F648" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G648" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H648" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I648" s="26" t="inlineStr">
+        <is>
+          <t>Classic algorithm explanations (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="26" t="inlineStr">
+        <is>
+          <t>Databases &amp; SQL</t>
+        </is>
+      </c>
+      <c r="B649" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C649" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Database Star</t>
+        </is>
+      </c>
+      <c r="D649" s="26" t="inlineStr">
+        <is>
+          <t>Advanced SQL &amp; Database Design</t>
+        </is>
+      </c>
+      <c r="E649" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Database+Star+Advanced+SQL+%26+Database+Design</t>
+        </is>
+      </c>
+      <c r="F649" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G649" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H649" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I649" s="26" t="inlineStr">
+        <is>
+          <t>Design-level database thinking (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="26" t="inlineStr">
+        <is>
+          <t>Databases &amp; SQL</t>
+        </is>
+      </c>
+      <c r="B650" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C650" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — MongoDB</t>
+        </is>
+      </c>
+      <c r="D650" s="26" t="inlineStr">
+        <is>
+          <t>NoSQL &amp; MongoDB Official Tutorials</t>
+        </is>
+      </c>
+      <c r="E650" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=MongoDB+NoSQL+%26+MongoDB+Official+Tutorials</t>
+        </is>
+      </c>
+      <c r="F650" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G650" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H650" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I650" s="26" t="inlineStr">
+        <is>
+          <t>Primary source for document databases (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="26" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="B651" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C651" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Luis Serrano</t>
+        </is>
+      </c>
+      <c r="D651" s="26" t="inlineStr">
+        <is>
+          <t>Machine Learning Intuitively Explained</t>
+        </is>
+      </c>
+      <c r="E651" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Luis+Serrano+Machine+Learning+Intuitively+Explained</t>
+        </is>
+      </c>
+      <c r="F651" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G651" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H651" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I651" s="26" t="inlineStr">
+        <is>
+          <t>Excellent low-maths conceptual grounding (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="26" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="B652" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C652" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Machine Learning Street Talk</t>
+        </is>
+      </c>
+      <c r="D652" s="26" t="inlineStr">
+        <is>
+          <t>Research Discussions &amp; Interviews</t>
+        </is>
+      </c>
+      <c r="E652" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Machine+Learning+Street+Talk+Research+Discussions+%26+Interviews</t>
+        </is>
+      </c>
+      <c r="F652" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G652" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H652" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I652" s="26" t="inlineStr">
+        <is>
+          <t>Serious debate on ML research directions (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="26" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Neural Networks</t>
+        </is>
+      </c>
+      <c r="B653" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C653" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — MIT 6.S191</t>
+        </is>
+      </c>
+      <c r="D653" s="26" t="inlineStr">
+        <is>
+          <t>Introduction to Deep Learning</t>
+        </is>
+      </c>
+      <c r="E653" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=MIT+6.S191+Introduction+to+Deep+Learning</t>
+        </is>
+      </c>
+      <c r="F653" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G653" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H653" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I653" s="26" t="inlineStr">
+        <is>
+          <t>MIT's annually updated deep learning bootcamp (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="26" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Neural Networks</t>
+        </is>
+      </c>
+      <c r="B654" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C654" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Aladdin Persson</t>
+        </is>
+      </c>
+      <c r="D654" s="26" t="inlineStr">
+        <is>
+          <t>PyTorch &amp; Paper Implementations</t>
+        </is>
+      </c>
+      <c r="E654" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Aladdin+Persson+PyTorch+%26+Paper+Implementations</t>
+        </is>
+      </c>
+      <c r="F654" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G654" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H654" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I654" s="26" t="inlineStr">
+        <is>
+          <t>Reimplements papers line by line (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="26" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Neural Networks</t>
+        </is>
+      </c>
+      <c r="B655" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C655" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Sebastian Raschka</t>
+        </is>
+      </c>
+      <c r="D655" s="26" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; LLM Fundamentals</t>
+        </is>
+      </c>
+      <c r="E655" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Sebastian+Raschka+Deep+Learning+%26+LLM+Fundamentals</t>
+        </is>
+      </c>
+      <c r="F655" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G655" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H655" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I655" s="26" t="inlineStr">
+        <is>
+          <t>Rigorous, textbook-grade teaching (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="26" t="inlineStr">
+        <is>
+          <t>Large Language Models &amp; Generative AI</t>
+        </is>
+      </c>
+      <c r="B656" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C656" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — James Briggs</t>
+        </is>
+      </c>
+      <c r="D656" s="26" t="inlineStr">
+        <is>
+          <t>RAG, Vector Databases &amp; LangChain</t>
+        </is>
+      </c>
+      <c r="E656" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=James+Briggs+RAG%2C+Vector+Databases+%26+LangChain</t>
+        </is>
+      </c>
+      <c r="F656" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G656" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H656" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I656" s="26" t="inlineStr">
+        <is>
+          <t>Applied LLM engineering (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="26" t="inlineStr">
+        <is>
+          <t>Large Language Models &amp; Generative AI</t>
+        </is>
+      </c>
+      <c r="B657" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C657" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — AI Engineer</t>
+        </is>
+      </c>
+      <c r="D657" s="26" t="inlineStr">
+        <is>
+          <t>Conference Talks on LLM Systems</t>
+        </is>
+      </c>
+      <c r="E657" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=AI+Engineer+Conference+Talks+on+LLM+Systems</t>
+        </is>
+      </c>
+      <c r="F657" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G657" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H657" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I657" s="26" t="inlineStr">
+        <is>
+          <t>Industry practice from teams shipping LLM products (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="26" t="inlineStr">
+        <is>
+          <t>Computer Vision</t>
+        </is>
+      </c>
+      <c r="B658" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C658" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — First Principles of Computer Vision</t>
+        </is>
+      </c>
+      <c r="D658" s="26" t="inlineStr">
+        <is>
+          <t>Classical CV Theory</t>
+        </is>
+      </c>
+      <c r="E658" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=First+Principles+of+Computer+Vision+Classical+CV+Theory</t>
+        </is>
+      </c>
+      <c r="F658" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G658" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H658" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I658" s="26" t="inlineStr">
+        <is>
+          <t>Columbia course-grade classical vision (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="26" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B659" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C659" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — StatQuest</t>
+        </is>
+      </c>
+      <c r="D659" s="26" t="inlineStr">
+        <is>
+          <t>Statistics Behind Data Science</t>
+        </is>
+      </c>
+      <c r="E659" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=StatQuest+Statistics+Behind+Data+Science</t>
+        </is>
+      </c>
+      <c r="F659" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G659" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H659" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I659" s="26" t="inlineStr">
+        <is>
+          <t>Conceptual grounding for analytics (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="26" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B660" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C660" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Tina Huang</t>
+        </is>
+      </c>
+      <c r="D660" s="26" t="inlineStr">
+        <is>
+          <t>Data Career &amp; Study Strategy</t>
+        </is>
+      </c>
+      <c r="E660" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Tina+Huang+Data+Career+%26+Study+Strategy</t>
+        </is>
+      </c>
+      <c r="F660" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G660" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H660" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I660" s="26" t="inlineStr">
+        <is>
+          <t>Career navigation for analysts (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="26" t="inlineStr">
+        <is>
+          <t>Excel, Spreadsheets &amp; Business Tools</t>
+        </is>
+      </c>
+      <c r="B661" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C661" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — MyOnlineTrainingHub</t>
+        </is>
+      </c>
+      <c r="D661" s="26" t="inlineStr">
+        <is>
+          <t>Excel &amp; Power BI Tutorials</t>
+        </is>
+      </c>
+      <c r="E661" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=MyOnlineTrainingHub+Excel+%26+Power+BI+Tutorials</t>
+        </is>
+      </c>
+      <c r="F661" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G661" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H661" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I661" s="26" t="inlineStr">
+        <is>
+          <t>Professional-grade business intelligence teaching (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="26" t="inlineStr">
+        <is>
+          <t>Excel, Spreadsheets &amp; Business Tools</t>
+        </is>
+      </c>
+      <c r="B662" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C662" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Kenji Explains</t>
+        </is>
+      </c>
+      <c r="D662" s="26" t="inlineStr">
+        <is>
+          <t>Excel for Business &amp; Finance</t>
+        </is>
+      </c>
+      <c r="E662" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Kenji+Explains+Excel+for+Business+%26+Finance</t>
+        </is>
+      </c>
+      <c r="F662" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G662" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H662" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I662" s="26" t="inlineStr">
+        <is>
+          <t>Short, high-utility business Excel skills (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="26" t="inlineStr">
+        <is>
+          <t>Excel, Spreadsheets &amp; Business Tools</t>
+        </is>
+      </c>
+      <c r="B663" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C663" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Microsoft 365</t>
+        </is>
+      </c>
+      <c r="D663" s="26" t="inlineStr">
+        <is>
+          <t>Official Excel &amp; Power BI Tutorials</t>
+        </is>
+      </c>
+      <c r="E663" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Microsoft+365+Official+Excel+%26+Power+BI+Tutorials</t>
+        </is>
+      </c>
+      <c r="F663" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G663" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H663" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I663" s="26" t="inlineStr">
+        <is>
+          <t>Primary source documentation in video form (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="26" t="inlineStr">
+        <is>
+          <t>Cybersecurity &amp; Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="B664" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C664" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Cyber Mentor</t>
+        </is>
+      </c>
+      <c r="D664" s="26" t="inlineStr">
+        <is>
+          <t>Practical Ethical Hacking Full Course</t>
+        </is>
+      </c>
+      <c r="E664" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=The+Cyber+Mentor+Practical+Ethical+Hacking+Full+Course</t>
+        </is>
+      </c>
+      <c r="F664" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G664" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H664" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I664" s="26" t="inlineStr">
+        <is>
+          <t>Free full-length penetration testing course (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="26" t="inlineStr">
+        <is>
+          <t>Cybersecurity &amp; Ethical Hacking</t>
+        </is>
+      </c>
+      <c r="B665" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C665" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — HackerSploit</t>
+        </is>
+      </c>
+      <c r="D665" s="26" t="inlineStr">
+        <is>
+          <t>Linux Security &amp; Pentesting</t>
+        </is>
+      </c>
+      <c r="E665" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=HackerSploit+Linux+Security+%26+Pentesting</t>
+        </is>
+      </c>
+      <c r="F665" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G665" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H665" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I665" s="26" t="inlineStr">
+        <is>
+          <t>Tool-focused practical training (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="26" t="inlineStr">
+        <is>
+          <t>Networking &amp; IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="B666" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C666" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — PowerCert Animated Videos</t>
+        </is>
+      </c>
+      <c r="D666" s="26" t="inlineStr">
+        <is>
+          <t>Networking Concepts Animated</t>
+        </is>
+      </c>
+      <c r="E666" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=PowerCert+Animated+Videos+Networking+Concepts+Animated</t>
+        </is>
+      </c>
+      <c r="F666" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G666" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H666" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I666" s="26" t="inlineStr">
+        <is>
+          <t>Short animated concept clarity (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="26" t="inlineStr">
+        <is>
+          <t>Networking &amp; IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="B667" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C667" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Practical Networking</t>
+        </is>
+      </c>
+      <c r="D667" s="26" t="inlineStr">
+        <is>
+          <t>TCP/IP and Routing Explained</t>
+        </is>
+      </c>
+      <c r="E667" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Practical+Networking+TCP%2FIP+and+Routing+Explained</t>
+        </is>
+      </c>
+      <c r="F667" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G667" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H667" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I667" s="26" t="inlineStr">
+        <is>
+          <t>Rigorous protocol-level teaching (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="26" t="inlineStr">
+        <is>
+          <t>DevOps, Cloud &amp; Containers</t>
+        </is>
+      </c>
+      <c r="B668" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C668" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — DevOps Toolkit</t>
+        </is>
+      </c>
+      <c r="D668" s="26" t="inlineStr">
+        <is>
+          <t>Advanced Kubernetes &amp; GitOps</t>
+        </is>
+      </c>
+      <c r="E668" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=DevOps+Toolkit+Advanced+Kubernetes+%26+GitOps</t>
+        </is>
+      </c>
+      <c r="F668" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G668" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H668" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I668" s="26" t="inlineStr">
+        <is>
+          <t>Opinionated senior-level tooling analysis (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="26" t="inlineStr">
+        <is>
+          <t>DevOps, Cloud &amp; Containers</t>
+        </is>
+      </c>
+      <c r="B669" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C669" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Cloud With Raj / Be A Better Dev</t>
+        </is>
+      </c>
+      <c r="D669" s="26" t="inlineStr">
+        <is>
+          <t>AWS Services Explained</t>
+        </is>
+      </c>
+      <c r="E669" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Cloud+With+Raj+%2F+Be+A+Better+Dev+AWS+Services+Explained</t>
+        </is>
+      </c>
+      <c r="F669" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G669" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H669" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I669" s="26" t="inlineStr">
+        <is>
+          <t>Service-by-service AWS teaching (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="26" t="inlineStr">
+        <is>
+          <t>Linux &amp; Operating Systems</t>
+        </is>
+      </c>
+      <c r="B670" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C670" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Linux Foundation</t>
+        </is>
+      </c>
+      <c r="D670" s="26" t="inlineStr">
+        <is>
+          <t>Official Linux &amp; Open Source Training</t>
+        </is>
+      </c>
+      <c r="E670" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=The+Linux+Foundation+Official+Linux+%26+Open+Source+Training</t>
+        </is>
+      </c>
+      <c r="F670" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G670" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H670" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I670" s="26" t="inlineStr">
+        <is>
+          <t>Authoritative source (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="26" t="inlineStr">
+        <is>
+          <t>Linux &amp; Operating Systems</t>
+        </is>
+      </c>
+      <c r="B671" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C671" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Luke Smith</t>
+        </is>
+      </c>
+      <c r="D671" s="26" t="inlineStr">
+        <is>
+          <t>Unix Tooling &amp; Scripting</t>
+        </is>
+      </c>
+      <c r="E671" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Luke+Smith+Unix+Tooling+%26+Scripting</t>
+        </is>
+      </c>
+      <c r="F671" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G671" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H671" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I671" s="26" t="inlineStr">
+        <is>
+          <t>Minimalist command-line workflows (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="26" t="inlineStr">
+        <is>
+          <t>Game Development</t>
+        </is>
+      </c>
+      <c r="B672" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C672" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Blackthornprod</t>
+        </is>
+      </c>
+      <c r="D672" s="26" t="inlineStr">
+        <is>
+          <t>Indie Game Design &amp; Art</t>
+        </is>
+      </c>
+      <c r="E672" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Blackthornprod+Indie+Game+Design+%26+Art</t>
+        </is>
+      </c>
+      <c r="F672" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G672" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H672" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I672" s="26" t="inlineStr">
+        <is>
+          <t>Design-thinking plus implementation (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="26" t="inlineStr">
+        <is>
+          <t>Robotics, Arduino &amp; Embedded Systems</t>
+        </is>
+      </c>
+      <c r="B673" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C673" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Construct</t>
+        </is>
+      </c>
+      <c r="D673" s="26" t="inlineStr">
+        <is>
+          <t>ROS &amp; ROS2 Robotics Courses</t>
+        </is>
+      </c>
+      <c r="E673" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=The+Construct+ROS+%26+ROS2+Robotics+Courses</t>
+        </is>
+      </c>
+      <c r="F673" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G673" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H673" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I673" s="26" t="inlineStr">
+        <is>
+          <t>The main free ROS education source (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="26" t="inlineStr">
+        <is>
+          <t>Robotics, Arduino &amp; Embedded Systems</t>
+        </is>
+      </c>
+      <c r="B674" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C674" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Robotics Back-End</t>
+        </is>
+      </c>
+      <c r="D674" s="26" t="inlineStr">
+        <is>
+          <t>ROS for Beginners</t>
+        </is>
+      </c>
+      <c r="E674" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Robotics+Back-End+ROS+for+Beginners</t>
+        </is>
+      </c>
+      <c r="F674" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G674" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H674" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I674" s="26" t="inlineStr">
+        <is>
+          <t>Structured entry into robot software (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="26" t="inlineStr">
+        <is>
+          <t>Robotics, Arduino &amp; Embedded Systems</t>
+        </is>
+      </c>
+      <c r="B675" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C675" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Michael Reeves</t>
+        </is>
+      </c>
+      <c r="D675" s="26" t="inlineStr">
+        <is>
+          <t>Chaotic Applied Robotics</t>
+        </is>
+      </c>
+      <c r="E675" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Michael+Reeves+Chaotic+Applied+Robotics</t>
+        </is>
+      </c>
+      <c r="F675" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G675" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H675" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I675" s="26" t="inlineStr">
+        <is>
+          <t>Entertainment, but genuinely instructive on integration (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="26" t="inlineStr">
+        <is>
+          <t>Robotics, Arduino &amp; Embedded Systems</t>
+        </is>
+      </c>
+      <c r="B676" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C676" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Khan Academy / freeCodeCamp</t>
+        </is>
+      </c>
+      <c r="D676" s="26" t="inlineStr">
+        <is>
+          <t>Arduino &amp; Embedded C Courses</t>
+        </is>
+      </c>
+      <c r="E676" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Khan+Academy+%2F+freeCodeCamp+Arduino+%26+Embedded+C+Courses</t>
+        </is>
+      </c>
+      <c r="F676" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G676" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H676" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I676" s="26" t="inlineStr">
+        <is>
+          <t>Long-form structured introductions (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="26" t="inlineStr">
+        <is>
+          <t>Electronics &amp; Circuit Theory</t>
+        </is>
+      </c>
+      <c r="B677" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C677" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — All About Electronics</t>
+        </is>
+      </c>
+      <c r="D677" s="26" t="inlineStr">
+        <is>
+          <t>Circuit Analysis &amp; Semiconductor Theory</t>
+        </is>
+      </c>
+      <c r="E677" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=All+About+Electronics+Circuit+Analysis+%26+Semiconductor+Theory</t>
+        </is>
+      </c>
+      <c r="F677" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G677" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H677" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I677" s="26" t="inlineStr">
+        <is>
+          <t>University-syllabus electronics (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="26" t="inlineStr">
+        <is>
+          <t>Electronics &amp; Circuit Theory</t>
+        </is>
+      </c>
+      <c r="B678" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C678" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Afrotechmods</t>
+        </is>
+      </c>
+      <c r="D678" s="26" t="inlineStr">
+        <is>
+          <t>Electronics Fundamentals Explained</t>
+        </is>
+      </c>
+      <c r="E678" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Afrotechmods+Electronics+Fundamentals+Explained</t>
+        </is>
+      </c>
+      <c r="F678" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G678" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H678" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I678" s="26" t="inlineStr">
+        <is>
+          <t>Short, clear component tutorials (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="26" t="inlineStr">
+        <is>
+          <t>Mechanical, Civil &amp; General Engineering</t>
+        </is>
+      </c>
+      <c r="B679" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C679" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — NPTEL</t>
+        </is>
+      </c>
+      <c r="D679" s="26" t="inlineStr">
+        <is>
+          <t>IIT Engineering Course Lectures</t>
+        </is>
+      </c>
+      <c r="E679" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=NPTEL+IIT+Engineering+Course+Lectures</t>
+        </is>
+      </c>
+      <c r="F679" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G679" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H679" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I679" s="26" t="inlineStr">
+        <is>
+          <t>Full accredited Indian engineering courses (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="26" t="inlineStr">
+        <is>
+          <t>Mechanical, Civil &amp; General Engineering</t>
+        </is>
+      </c>
+      <c r="B680" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C680" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Engineering Explained</t>
+        </is>
+      </c>
+      <c r="D680" s="26" t="inlineStr">
+        <is>
+          <t>Automotive Engineering</t>
+        </is>
+      </c>
+      <c r="E680" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Engineering+Explained+Automotive+Engineering</t>
+        </is>
+      </c>
+      <c r="F680" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G680" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H680" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I680" s="26" t="inlineStr">
+        <is>
+          <t>Rigorous mechanical explanation (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="26" t="inlineStr">
+        <is>
+          <t>Mechanical, Civil &amp; General Engineering</t>
+        </is>
+      </c>
+      <c r="B681" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C681" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Engineering Mindset</t>
+        </is>
+      </c>
+      <c r="D681" s="26" t="inlineStr">
+        <is>
+          <t>HVAC, Electrical &amp; Building Systems</t>
+        </is>
+      </c>
+      <c r="E681" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=The+Engineering+Mindset+HVAC%2C+Electrical+%26+Building+Systems</t>
+        </is>
+      </c>
+      <c r="F681" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G681" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H681" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I681" s="26" t="inlineStr">
+        <is>
+          <t>Industry-practical systems teaching (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="26" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="B682" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C682" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Economics Explained</t>
+        </is>
+      </c>
+      <c r="D682" s="26" t="inlineStr">
+        <is>
+          <t>Country &amp; Systems Analysis</t>
+        </is>
+      </c>
+      <c r="E682" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Economics+Explained+Country+%26+Systems+Analysis</t>
+        </is>
+      </c>
+      <c r="F682" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G682" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H682" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I682" s="26" t="inlineStr">
+        <is>
+          <t>Applied economic analysis of real economies (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="26" t="inlineStr">
+        <is>
+          <t>Finance, Accounting &amp; Investing</t>
+        </is>
+      </c>
+      <c r="B683" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C683" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Corporate Finance Institute</t>
+        </is>
+      </c>
+      <c r="D683" s="26" t="inlineStr">
+        <is>
+          <t>Financial Modelling &amp; Excel for Finance</t>
+        </is>
+      </c>
+      <c r="E683" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Corporate+Finance+Institute+Financial+Modelling+%26+Excel+for+Finance</t>
+        </is>
+      </c>
+      <c r="F683" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G683" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H683" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I683" s="26" t="inlineStr">
+        <is>
+          <t>Professional finance skills (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="26" t="inlineStr">
+        <is>
+          <t>Finance, Accounting &amp; Investing</t>
+        </is>
+      </c>
+      <c r="B684" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C684" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Two Cents (PBS)</t>
+        </is>
+      </c>
+      <c r="D684" s="26" t="inlineStr">
+        <is>
+          <t>Personal Finance Fundamentals</t>
+        </is>
+      </c>
+      <c r="E684" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Two+Cents+%28PBS%29+Personal+Finance+Fundamentals</t>
+        </is>
+      </c>
+      <c r="F684" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G684" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H684" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I684" s="26" t="inlineStr">
+        <is>
+          <t>Practical money management (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="26" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Growth</t>
+        </is>
+      </c>
+      <c r="B685" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C685" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Adam Erhart</t>
+        </is>
+      </c>
+      <c r="D685" s="26" t="inlineStr">
+        <is>
+          <t>Marketing Strategy for Small Business</t>
+        </is>
+      </c>
+      <c r="E685" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Adam+Erhart+Marketing+Strategy+for+Small+Business</t>
+        </is>
+      </c>
+      <c r="F685" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G685" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H685" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I685" s="26" t="inlineStr">
+        <is>
+          <t>Strategy over tactics (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="26" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Growth</t>
+        </is>
+      </c>
+      <c r="B686" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C686" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Google Analytics / Google Skillshop</t>
+        </is>
+      </c>
+      <c r="D686" s="26" t="inlineStr">
+        <is>
+          <t>Analytics &amp; Ads Official Training</t>
+        </is>
+      </c>
+      <c r="E686" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Google+Analytics+%2F+Google+Skillshop+Analytics+%26+Ads+Official+Training</t>
+        </is>
+      </c>
+      <c r="F686" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G686" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H686" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I686" s="26" t="inlineStr">
+        <is>
+          <t>Primary source certification training (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="26" t="inlineStr">
+        <is>
+          <t>Psychology &amp; Behavioural Science</t>
+        </is>
+      </c>
+      <c r="B687" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C687" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — SciShow Psych</t>
+        </is>
+      </c>
+      <c r="D687" s="26" t="inlineStr">
+        <is>
+          <t>Research-Based Psychology Explainers</t>
+        </is>
+      </c>
+      <c r="E687" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=SciShow+Psych+Research-Based+Psychology+Explainers</t>
+        </is>
+      </c>
+      <c r="F687" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G687" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H687" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I687" s="26" t="inlineStr">
+        <is>
+          <t>Study-referenced short explainers (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="26" t="inlineStr">
+        <is>
+          <t>Psychology &amp; Behavioural Science</t>
+        </is>
+      </c>
+      <c r="B688" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C688" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Practical Psychology</t>
+        </is>
+      </c>
+      <c r="D688" s="26" t="inlineStr">
+        <is>
+          <t>Applied Psychology &amp; Study Techniques</t>
+        </is>
+      </c>
+      <c r="E688" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Practical+Psychology+Applied+Psychology+%26+Study+Techniques</t>
+        </is>
+      </c>
+      <c r="F688" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G688" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H688" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I688" s="26" t="inlineStr">
+        <is>
+          <t>Practical application of research (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="26" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Critical Thinking</t>
+        </is>
+      </c>
+      <c r="B689" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C689" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Academy of Ideas</t>
+        </is>
+      </c>
+      <c r="D689" s="26" t="inlineStr">
+        <is>
+          <t>Classical Philosophers Explained</t>
+        </is>
+      </c>
+      <c r="E689" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Academy+of+Ideas+Classical+Philosophers+Explained</t>
+        </is>
+      </c>
+      <c r="F689" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G689" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H689" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I689" s="26" t="inlineStr">
+        <is>
+          <t>Deep readings of major thinkers (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="26" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Critical Thinking</t>
+        </is>
+      </c>
+      <c r="B690" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C690" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Then &amp; Now</t>
+        </is>
+      </c>
+      <c r="D690" s="26" t="inlineStr">
+        <is>
+          <t>Political Philosophy &amp; Theory</t>
+        </is>
+      </c>
+      <c r="E690" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Then+%26+Now+Political+Philosophy+%26+Theory</t>
+        </is>
+      </c>
+      <c r="F690" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G690" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H690" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I690" s="26" t="inlineStr">
+        <is>
+          <t>Careful contemporary political philosophy (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="26" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Critical Thinking</t>
+        </is>
+      </c>
+      <c r="B691" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C691" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Kane B</t>
+        </is>
+      </c>
+      <c r="D691" s="26" t="inlineStr">
+        <is>
+          <t>Analytic Philosophy Lectures</t>
+        </is>
+      </c>
+      <c r="E691" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Kane+B+Analytic+Philosophy+Lectures</t>
+        </is>
+      </c>
+      <c r="F691" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G691" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H691" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I691" s="26" t="inlineStr">
+        <is>
+          <t>Serious analytic philosophy at depth (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="26" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Critical Thinking</t>
+        </is>
+      </c>
+      <c r="B692" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C692" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Jeffrey Kaplan</t>
+        </is>
+      </c>
+      <c r="D692" s="26" t="inlineStr">
+        <is>
+          <t>Philosophy &amp; Legal Theory Lectures</t>
+        </is>
+      </c>
+      <c r="E692" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Jeffrey+Kaplan+Philosophy+%26+Legal+Theory+Lectures</t>
+        </is>
+      </c>
+      <c r="F692" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G692" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H692" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I692" s="26" t="inlineStr">
+        <is>
+          <t>Exceptionally clear lecture explanations (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="26" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="B693" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C693" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Timeline / Real History</t>
+        </is>
+      </c>
+      <c r="D693" s="26" t="inlineStr">
+        <is>
+          <t>Full History Documentaries</t>
+        </is>
+      </c>
+      <c r="E693" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Timeline+%2F+Real+History+Full+History+Documentaries</t>
+        </is>
+      </c>
+      <c r="F693" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G693" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H693" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I693" s="26" t="inlineStr">
+        <is>
+          <t>Licensed full-length documentaries (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="26" t="inlineStr">
+        <is>
+          <t>Geography &amp; Geopolitics</t>
+        </is>
+      </c>
+      <c r="B694" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C694" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Caspian Report</t>
+        </is>
+      </c>
+      <c r="D694" s="26" t="inlineStr">
+        <is>
+          <t>Geopolitical Analysis</t>
+        </is>
+      </c>
+      <c r="E694" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Caspian+Report+Geopolitical+Analysis</t>
+        </is>
+      </c>
+      <c r="F694" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G694" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H694" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I694" s="26" t="inlineStr">
+        <is>
+          <t>Regional strategic analysis (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="26" t="inlineStr">
+        <is>
+          <t>Geography &amp; Geopolitics</t>
+        </is>
+      </c>
+      <c r="B695" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C695" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Atlas Pro</t>
+        </is>
+      </c>
+      <c r="D695" s="26" t="inlineStr">
+        <is>
+          <t>Physical Geography &amp; Earth Systems</t>
+        </is>
+      </c>
+      <c r="E695" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Atlas+Pro+Physical+Geography+%26+Earth+Systems</t>
+        </is>
+      </c>
+      <c r="F695" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G695" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H695" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I695" s="26" t="inlineStr">
+        <is>
+          <t>Strong physical geography teaching (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="26" t="inlineStr">
+        <is>
+          <t>English Language &amp; Grammar (ESL)</t>
+        </is>
+      </c>
+      <c r="B696" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C696" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Learn English with EnglishClass101</t>
+        </is>
+      </c>
+      <c r="D696" s="26" t="inlineStr">
+        <is>
+          <t>Vocabulary &amp; Listening Practice</t>
+        </is>
+      </c>
+      <c r="E696" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Learn+English+with+EnglishClass101+Vocabulary+%26+Listening+Practice</t>
+        </is>
+      </c>
+      <c r="F696" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G696" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H696" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I696" s="26" t="inlineStr">
+        <is>
+          <t>Structured daily practice content (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="26" t="inlineStr">
+        <is>
+          <t>English Language &amp; Grammar (ESL)</t>
+        </is>
+      </c>
+      <c r="B697" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C697" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Speak English With Vanessa</t>
+        </is>
+      </c>
+      <c r="D697" s="26" t="inlineStr">
+        <is>
+          <t>Conversational Fluency</t>
+        </is>
+      </c>
+      <c r="E697" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Speak+English+With+Vanessa+Conversational+Fluency</t>
+        </is>
+      </c>
+      <c r="F697" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G697" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H697" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I697" s="26" t="inlineStr">
+        <is>
+          <t>Natural conversation training (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="26" t="inlineStr">
+        <is>
+          <t>Academic Writing &amp; Research Skills</t>
+        </is>
+      </c>
+      <c r="B698" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C698" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Andy Stapleton</t>
+        </is>
+      </c>
+      <c r="D698" s="26" t="inlineStr">
+        <is>
+          <t>PhD Life, Writing &amp; Publishing</t>
+        </is>
+      </c>
+      <c r="E698" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@AndyStapleton</t>
+        </is>
+      </c>
+      <c r="F698" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G698" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H698" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I698" s="26" t="inlineStr">
+        <is>
+          <t>Practical academic publishing guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="26" t="inlineStr">
+        <is>
+          <t>Academic Writing &amp; Research Skills</t>
+        </is>
+      </c>
+      <c r="B699" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C699" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Academic English Now</t>
+        </is>
+      </c>
+      <c r="D699" s="26" t="inlineStr">
+        <is>
+          <t>Academic Writing for Non-Native Speakers</t>
+        </is>
+      </c>
+      <c r="E699" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Academic+English+Now+Academic+Writing+for+Non-Native+Speakers</t>
+        </is>
+      </c>
+      <c r="F699" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G699" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H699" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I699" s="26" t="inlineStr">
+        <is>
+          <t>Targeted at international researchers (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="26" t="inlineStr">
+        <is>
+          <t>Academic Writing &amp; Research Skills</t>
+        </is>
+      </c>
+      <c r="B700" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C700" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Purdue OWL / Purdue University</t>
+        </is>
+      </c>
+      <c r="D700" s="26" t="inlineStr">
+        <is>
+          <t>Citation &amp; Academic Writing Guides</t>
+        </is>
+      </c>
+      <c r="E700" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Purdue+OWL+%2F+Purdue+University+Citation+%26+Academic+Writing+Guides</t>
+        </is>
+      </c>
+      <c r="F700" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G700" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H700" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I700" s="26" t="inlineStr">
+        <is>
+          <t>The reference standard for APA/MLA/Chicago (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="26" t="inlineStr">
+        <is>
+          <t>Academic Writing &amp; Research Skills</t>
+        </is>
+      </c>
+      <c r="B701" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C701" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — David Stuart / Research Methods channels</t>
+        </is>
+      </c>
+      <c r="D701" s="26" t="inlineStr">
+        <is>
+          <t>Literature Review Technique</t>
+        </is>
+      </c>
+      <c r="E701" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=David+Stuart+%2F+Research+Methods+channels+Literature+Review+Technique</t>
+        </is>
+      </c>
+      <c r="F701" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G701" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H701" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I701" s="26" t="inlineStr">
+        <is>
+          <t>Systematic review methodology (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="26" t="inlineStr">
+        <is>
+          <t>Academic Writing &amp; Research Skills</t>
+        </is>
+      </c>
+      <c r="B702" s="26" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="C702" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Zotero / Mendeley Official</t>
+        </is>
+      </c>
+      <c r="D702" s="26" t="inlineStr">
+        <is>
+          <t>Reference Management Tutorials</t>
+        </is>
+      </c>
+      <c r="E702" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Zotero+%2F+Mendeley+Official+Reference+Management+Tutorials</t>
+        </is>
+      </c>
+      <c r="F702" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G702" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H702" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I702" s="26" t="inlineStr">
+        <is>
+          <t>Tooling for citation management (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="26" t="inlineStr">
+        <is>
+          <t>Academic Writing &amp; Research Skills</t>
+        </is>
+      </c>
+      <c r="B703" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C703" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Nature / Springer Nature</t>
+        </is>
+      </c>
+      <c r="D703" s="26" t="inlineStr">
+        <is>
+          <t>Publishing &amp; Peer Review Explained</t>
+        </is>
+      </c>
+      <c r="E703" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Nature+%2F+Springer+Nature+Publishing+%26+Peer+Review+Explained</t>
+        </is>
+      </c>
+      <c r="F703" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G703" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H703" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I703" s="26" t="inlineStr">
+        <is>
+          <t>Primary source on the publication process (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="26" t="inlineStr">
+        <is>
+          <t>IELTS Preparation</t>
+        </is>
+      </c>
+      <c r="B704" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C704" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Asad Yaqub</t>
+        </is>
+      </c>
+      <c r="D704" s="26" t="inlineStr">
+        <is>
+          <t>IELTS Reading &amp; Listening Techniques</t>
+        </is>
+      </c>
+      <c r="E704" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@AsadYaqub</t>
+        </is>
+      </c>
+      <c r="F704" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G704" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H704" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I704" s="26" t="inlineStr">
+        <is>
+          <t>Very popular with South Asian candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="26" t="inlineStr">
+        <is>
+          <t>IELTS Preparation</t>
+        </is>
+      </c>
+      <c r="B705" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C705" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Fastrack IELTS</t>
+        </is>
+      </c>
+      <c r="D705" s="26" t="inlineStr">
+        <is>
+          <t>Speaking Practice &amp; Mock Tests</t>
+        </is>
+      </c>
+      <c r="E705" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Fastrack+IELTS+Speaking+Practice+%26+Mock+Tests</t>
+        </is>
+      </c>
+      <c r="F705" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G705" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H705" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I705" s="26" t="inlineStr">
+        <is>
+          <t>Speaking-focused practice (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="26" t="inlineStr">
+        <is>
+          <t>IELTS Preparation</t>
+        </is>
+      </c>
+      <c r="B706" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C706" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — AcademicEnglishHelp</t>
+        </is>
+      </c>
+      <c r="D706" s="26" t="inlineStr">
+        <is>
+          <t>Task 2 Essay Structure</t>
+        </is>
+      </c>
+      <c r="E706" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=AcademicEnglishHelp+Task+2+Essay+Structure</t>
+        </is>
+      </c>
+      <c r="F706" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G706" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H706" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I706" s="26" t="inlineStr">
+        <is>
+          <t>Essay-writing depth (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="26" t="inlineStr">
+        <is>
+          <t>TOEFL, PTE &amp; Duolingo English Test</t>
+        </is>
+      </c>
+      <c r="B707" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C707" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — NoteFull</t>
+        </is>
+      </c>
+      <c r="D707" s="26" t="inlineStr">
+        <is>
+          <t>TOEFL Speaking &amp; Writing Templates</t>
+        </is>
+      </c>
+      <c r="E707" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=NoteFull+TOEFL+Speaking+%26+Writing+Templates</t>
+        </is>
+      </c>
+      <c r="F707" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G707" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H707" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I707" s="26" t="inlineStr">
+        <is>
+          <t>Template-driven scoring strategy (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="26" t="inlineStr">
+        <is>
+          <t>TOEFL, PTE &amp; Duolingo English Test</t>
+        </is>
+      </c>
+      <c r="B708" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C708" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — TOEFL Official (ETS)</t>
+        </is>
+      </c>
+      <c r="D708" s="26" t="inlineStr">
+        <is>
+          <t>Official TOEFL Preparation</t>
+        </is>
+      </c>
+      <c r="E708" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=TOEFL+Official+%28ETS%29+Official+TOEFL+Preparation</t>
+        </is>
+      </c>
+      <c r="F708" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G708" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H708" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I708" s="26" t="inlineStr">
+        <is>
+          <t>Primary source (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="26" t="inlineStr">
+        <is>
+          <t>TOEFL, PTE &amp; Duolingo English Test</t>
+        </is>
+      </c>
+      <c r="B709" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C709" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — E2 PTE</t>
+        </is>
+      </c>
+      <c r="D709" s="26" t="inlineStr">
+        <is>
+          <t>PTE Academic Full Course</t>
+        </is>
+      </c>
+      <c r="E709" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=E2+PTE+PTE+Academic+Full+Course</t>
+        </is>
+      </c>
+      <c r="F709" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G709" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H709" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I709" s="26" t="inlineStr">
+        <is>
+          <t>Structured PTE training (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="26" t="inlineStr">
+        <is>
+          <t>TOEFL, PTE &amp; Duolingo English Test</t>
+        </is>
+      </c>
+      <c r="B710" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C710" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Duolingo English Test Official</t>
+        </is>
+      </c>
+      <c r="D710" s="26" t="inlineStr">
+        <is>
+          <t>DET Preparation</t>
+        </is>
+      </c>
+      <c r="E710" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Duolingo+English+Test+Official+DET+Preparation</t>
+        </is>
+      </c>
+      <c r="F710" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G710" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H710" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I710" s="26" t="inlineStr">
+        <is>
+          <t>Primary source for a fast-growing test (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="26" t="inlineStr">
+        <is>
+          <t>SAT &amp; Digital SAT</t>
+        </is>
+      </c>
+      <c r="B711" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C711" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Scalar Learning</t>
+        </is>
+      </c>
+      <c r="D711" s="26" t="inlineStr">
+        <is>
+          <t>SAT Math Problem Solving</t>
+        </is>
+      </c>
+      <c r="E711" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Scalar+Learning+SAT+Math+Problem+Solving</t>
+        </is>
+      </c>
+      <c r="F711" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G711" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H711" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I711" s="26" t="inlineStr">
+        <is>
+          <t>Math-section drilling (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="26" t="inlineStr">
+        <is>
+          <t>SAT &amp; Digital SAT</t>
+        </is>
+      </c>
+      <c r="B712" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C712" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Test Prep Insight / Prep Expert</t>
+        </is>
+      </c>
+      <c r="D712" s="26" t="inlineStr">
+        <is>
+          <t>SAT Strategy Overviews</t>
+        </is>
+      </c>
+      <c r="E712" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Test+Prep+Insight+%2F+Prep+Expert+SAT+Strategy+Overviews</t>
+        </is>
+      </c>
+      <c r="F712" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G712" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H712" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I712" s="26" t="inlineStr">
+        <is>
+          <t>Section-level strategy (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="26" t="inlineStr">
+        <is>
+          <t>GRE, GMAT &amp; Graduate Admissions Tests</t>
+        </is>
+      </c>
+      <c r="B713" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C713" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Manhattan Prep</t>
+        </is>
+      </c>
+      <c r="D713" s="26" t="inlineStr">
+        <is>
+          <t>GMAT Strategy Sessions</t>
+        </is>
+      </c>
+      <c r="E713" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Manhattan+Prep+GMAT+Strategy+Sessions</t>
+        </is>
+      </c>
+      <c r="F713" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G713" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H713" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I713" s="26" t="inlineStr">
+        <is>
+          <t>Long-standing test-prep authority (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="26" t="inlineStr">
+        <is>
+          <t>GRE, GMAT &amp; Graduate Admissions Tests</t>
+        </is>
+      </c>
+      <c r="B714" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C714" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Target Test Prep</t>
+        </is>
+      </c>
+      <c r="D714" s="26" t="inlineStr">
+        <is>
+          <t>GMAT Quant Technique</t>
+        </is>
+      </c>
+      <c r="E714" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Target+Test+Prep+GMAT+Quant+Technique</t>
+        </is>
+      </c>
+      <c r="F714" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G714" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H714" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I714" s="26" t="inlineStr">
+        <is>
+          <t>Quant-heavy methodical training (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="26" t="inlineStr">
+        <is>
+          <t>GRE, GMAT &amp; Graduate Admissions Tests</t>
+        </is>
+      </c>
+      <c r="B715" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C715" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — The Tested Tutor / PrepScholar</t>
+        </is>
+      </c>
+      <c r="D715" s="26" t="inlineStr">
+        <is>
+          <t>Admissions Test Strategy</t>
+        </is>
+      </c>
+      <c r="E715" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=The+Tested+Tutor+%2F+PrepScholar+Admissions+Test+Strategy</t>
+        </is>
+      </c>
+      <c r="F715" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G715" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H715" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I715" s="26" t="inlineStr">
+        <is>
+          <t>Broad admissions test coverage (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="26" t="inlineStr">
+        <is>
+          <t>Competitive Exams (JEE, NEET, Olympiads)</t>
+        </is>
+      </c>
+      <c r="B716" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C716" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Unacademy JEE / NEET</t>
+        </is>
+      </c>
+      <c r="D716" s="26" t="inlineStr">
+        <is>
+          <t>Live Problem Solving Sessions</t>
+        </is>
+      </c>
+      <c r="E716" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Unacademy+JEE+%2F+NEET+Live+Problem+Solving+Sessions</t>
+        </is>
+      </c>
+      <c r="F716" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G716" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H716" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I716" s="26" t="inlineStr">
+        <is>
+          <t>Structured live exam preparation (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="26" t="inlineStr">
+        <is>
+          <t>Competitive Exams (JEE, NEET, Olympiads)</t>
+        </is>
+      </c>
+      <c r="B717" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C717" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Vedantu JEE</t>
+        </is>
+      </c>
+      <c r="D717" s="26" t="inlineStr">
+        <is>
+          <t>Concept &amp; Revision Marathons</t>
+        </is>
+      </c>
+      <c r="E717" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Vedantu+JEE+Concept+%26+Revision+Marathons</t>
+        </is>
+      </c>
+      <c r="F717" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G717" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H717" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I717" s="26" t="inlineStr">
+        <is>
+          <t>Long-format revision sessions (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="26" t="inlineStr">
+        <is>
+          <t>Competitive Exams (JEE, NEET, Olympiads)</t>
+        </is>
+      </c>
+      <c r="B718" s="26" t="inlineStr">
+        <is>
+          <t>Exam Prep</t>
+        </is>
+      </c>
+      <c r="C718" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Khan Academy India</t>
+        </is>
+      </c>
+      <c r="D718" s="26" t="inlineStr">
+        <is>
+          <t>JEE &amp; Board Exam Support</t>
+        </is>
+      </c>
+      <c r="E718" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Khan+Academy+India+JEE+%26+Board+Exam+Support</t>
+        </is>
+      </c>
+      <c r="F718" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G718" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H718" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I718" s="26" t="inlineStr">
+        <is>
+          <t>Free structured support content (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="26" t="inlineStr">
+        <is>
+          <t>Competitive Exams (JEE, NEET, Olympiads)</t>
+        </is>
+      </c>
+      <c r="B719" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C719" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Mathematical Olympiad channels (e.g. Michael Penn)</t>
+        </is>
+      </c>
+      <c r="D719" s="26" t="inlineStr">
+        <is>
+          <t>Olympiad Problem Solving</t>
+        </is>
+      </c>
+      <c r="E719" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Mathematical+Olympiad+channels+%28e.g.+Michael+Penn%29+Olympiad+Problem+Solving</t>
+        </is>
+      </c>
+      <c r="F719" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G719" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H719" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I719" s="26" t="inlineStr">
+        <is>
+          <t>Competition-level problem technique (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="26" t="inlineStr">
+        <is>
+          <t>AI Safety, Ethics &amp; Policy</t>
+        </is>
+      </c>
+      <c r="B720" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C720" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Center for AI Safety / FLI</t>
+        </is>
+      </c>
+      <c r="D720" s="26" t="inlineStr">
+        <is>
+          <t>Policy &amp; Risk Discussions</t>
+        </is>
+      </c>
+      <c r="E720" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Center+for+AI+Safety+%2F+FLI+Policy+%26+Risk+Discussions</t>
+        </is>
+      </c>
+      <c r="F720" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G720" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H720" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I720" s="26" t="inlineStr">
+        <is>
+          <t>Policy-oriented analysis (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="26" t="inlineStr">
+        <is>
+          <t>AI Safety, Ethics &amp; Policy</t>
+        </is>
+      </c>
+      <c r="B721" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C721" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Stanford HAI</t>
+        </is>
+      </c>
+      <c r="D721" s="26" t="inlineStr">
+        <is>
+          <t>Human-Centered AI Talks</t>
+        </is>
+      </c>
+      <c r="E721" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Stanford+HAI+Human-Centered+AI+Talks</t>
+        </is>
+      </c>
+      <c r="F721" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G721" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H721" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I721" s="26" t="inlineStr">
+        <is>
+          <t>Academic AI policy and ethics (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="26" t="inlineStr">
+        <is>
+          <t>Blockchain, Web3 &amp; Quantum Computing</t>
+        </is>
+      </c>
+      <c r="B722" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C722" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Whiteboard Crypto</t>
+        </is>
+      </c>
+      <c r="D722" s="26" t="inlineStr">
+        <is>
+          <t>Blockchain Concepts Explained</t>
+        </is>
+      </c>
+      <c r="E722" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Whiteboard+Crypto+Blockchain+Concepts+Explained</t>
+        </is>
+      </c>
+      <c r="F722" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G722" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H722" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I722" s="26" t="inlineStr">
+        <is>
+          <t>Clear conceptual explanations (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="26" t="inlineStr">
+        <is>
+          <t>Blockchain, Web3 &amp; Quantum Computing</t>
+        </is>
+      </c>
+      <c r="B723" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C723" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Microsoft Quantum</t>
+        </is>
+      </c>
+      <c r="D723" s="26" t="inlineStr">
+        <is>
+          <t>Q# and Quantum Development</t>
+        </is>
+      </c>
+      <c r="E723" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Microsoft+Quantum+Q%23+and+Quantum+Development</t>
+        </is>
+      </c>
+      <c r="F723" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G723" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H723" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I723" s="26" t="inlineStr">
+        <is>
+          <t>Primary source developer training (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="26" t="inlineStr">
+        <is>
+          <t>Design — UI/UX &amp; Graphic Design</t>
+        </is>
+      </c>
+      <c r="B724" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C724" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Flux Academy</t>
+        </is>
+      </c>
+      <c r="D724" s="26" t="inlineStr">
+        <is>
+          <t>Web Design &amp; Freelancing</t>
+        </is>
+      </c>
+      <c r="E724" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Flux+Academy+Web+Design+%26+Freelancing</t>
+        </is>
+      </c>
+      <c r="F724" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G724" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H724" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I724" s="26" t="inlineStr">
+        <is>
+          <t>Design plus client business skills (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="26" t="inlineStr">
+        <is>
+          <t>Design — UI/UX &amp; Graphic Design</t>
+        </is>
+      </c>
+      <c r="B725" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C725" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Satori Graphics</t>
+        </is>
+      </c>
+      <c r="D725" s="26" t="inlineStr">
+        <is>
+          <t>Graphic Design Theory</t>
+        </is>
+      </c>
+      <c r="E725" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Satori+Graphics+Graphic+Design+Theory</t>
+        </is>
+      </c>
+      <c r="F725" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G725" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H725" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I725" s="26" t="inlineStr">
+        <is>
+          <t>Fundamentals of layout and type (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="26" t="inlineStr">
+        <is>
+          <t>Design — UI/UX &amp; Graphic Design</t>
+        </is>
+      </c>
+      <c r="B726" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C726" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Jesse Showalter</t>
+        </is>
+      </c>
+      <c r="D726" s="26" t="inlineStr">
+        <is>
+          <t>UI/UX Workflow &amp; Tools</t>
+        </is>
+      </c>
+      <c r="E726" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Jesse+Showalter+UI%2FUX+Workflow+%26+Tools</t>
+        </is>
+      </c>
+      <c r="F726" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G726" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H726" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I726" s="26" t="inlineStr">
+        <is>
+          <t>Practical designer workflow (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="26" t="inlineStr">
+        <is>
+          <t>Art, Drawing &amp; 3D</t>
+        </is>
+      </c>
+      <c r="B727" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C727" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Marc Brunet</t>
+        </is>
+      </c>
+      <c r="D727" s="26" t="inlineStr">
+        <is>
+          <t>Digital Art &amp; Character Design</t>
+        </is>
+      </c>
+      <c r="E727" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Marc+Brunet+Digital+Art+%26+Character+Design</t>
+        </is>
+      </c>
+      <c r="F727" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G727" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H727" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I727" s="26" t="inlineStr">
+        <is>
+          <t>Ex-Blizzard artist teaching production skills (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="26" t="inlineStr">
+        <is>
+          <t>Art, Drawing &amp; 3D</t>
+        </is>
+      </c>
+      <c r="B728" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C728" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Sinix Design</t>
+        </is>
+      </c>
+      <c r="D728" s="26" t="inlineStr">
+        <is>
+          <t>Painting &amp; Design Theory</t>
+        </is>
+      </c>
+      <c r="E728" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Sinix+Design+Painting+%26+Design+Theory</t>
+        </is>
+      </c>
+      <c r="F728" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G728" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H728" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I728" s="26" t="inlineStr">
+        <is>
+          <t>Deep artistic reasoning (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="26" t="inlineStr">
+        <is>
+          <t>Art, Drawing &amp; 3D</t>
+        </is>
+      </c>
+      <c r="B729" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C729" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — CG Cookie</t>
+        </is>
+      </c>
+      <c r="D729" s="26" t="inlineStr">
+        <is>
+          <t>Blender Modelling &amp; Animation</t>
+        </is>
+      </c>
+      <c r="E729" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=CG+Cookie+Blender+Modelling+%26+Animation</t>
+        </is>
+      </c>
+      <c r="F729" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G729" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H729" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I729" s="26" t="inlineStr">
+        <is>
+          <t>Structured 3D curriculum (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="26" t="inlineStr">
+        <is>
+          <t>Art, Drawing &amp; 3D</t>
+        </is>
+      </c>
+      <c r="B730" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C730" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Ian Hubert</t>
+        </is>
+      </c>
+      <c r="D730" s="26" t="inlineStr">
+        <is>
+          <t>Blender VFX Lazy Tutorials</t>
+        </is>
+      </c>
+      <c r="E730" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Ian+Hubert+Blender+VFX+Lazy+Tutorials</t>
+        </is>
+      </c>
+      <c r="F730" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G730" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H730" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I730" s="26" t="inlineStr">
+        <is>
+          <t>Production VFX technique (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="26" t="inlineStr">
+        <is>
+          <t>Photography, Video &amp; Content Creation</t>
+        </is>
+      </c>
+      <c r="B731" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C731" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Premiere Gal</t>
+        </is>
+      </c>
+      <c r="D731" s="26" t="inlineStr">
+        <is>
+          <t>Video Editing Tutorials</t>
+        </is>
+      </c>
+      <c r="E731" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Premiere+Gal+Video+Editing+Tutorials</t>
+        </is>
+      </c>
+      <c r="F731" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G731" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H731" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I731" s="26" t="inlineStr">
+        <is>
+          <t>Software-focused editing training (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="26" t="inlineStr">
+        <is>
+          <t>Photography, Video &amp; Content Creation</t>
+        </is>
+      </c>
+      <c r="B732" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C732" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Casey Neistat</t>
+        </is>
+      </c>
+      <c r="D732" s="26" t="inlineStr">
+        <is>
+          <t>Storytelling &amp; Creator Craft</t>
+        </is>
+      </c>
+      <c r="E732" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Casey+Neistat+Storytelling+%26+Creator+Craft</t>
+        </is>
+      </c>
+      <c r="F732" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G732" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H732" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I732" s="26" t="inlineStr">
+        <is>
+          <t>Narrative and creator-practice masterclass by example (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="26" t="inlineStr">
+        <is>
+          <t>Music Theory &amp; Instruments</t>
+        </is>
+      </c>
+      <c r="B733" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C733" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — 12tone</t>
+        </is>
+      </c>
+      <c r="D733" s="26" t="inlineStr">
+        <is>
+          <t>Music Theory Analysis</t>
+        </is>
+      </c>
+      <c r="E733" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=12tone+Music+Theory+Analysis</t>
+        </is>
+      </c>
+      <c r="F733" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G733" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H733" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I733" s="26" t="inlineStr">
+        <is>
+          <t>Analytical breakdowns of real songs (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="26" t="inlineStr">
+        <is>
+          <t>Music Theory &amp; Instruments</t>
+        </is>
+      </c>
+      <c r="B734" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C734" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Pianote</t>
+        </is>
+      </c>
+      <c r="D734" s="26" t="inlineStr">
+        <is>
+          <t>Piano Lessons for Beginners</t>
+        </is>
+      </c>
+      <c r="E734" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Pianote+Piano+Lessons+for+Beginners</t>
+        </is>
+      </c>
+      <c r="F734" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G734" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H734" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I734" s="26" t="inlineStr">
+        <is>
+          <t>Structured piano curriculum (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="26" t="inlineStr">
+        <is>
+          <t>Music Theory &amp; Instruments</t>
+        </is>
+      </c>
+      <c r="B735" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C735" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — David Bennett Piano</t>
+        </is>
+      </c>
+      <c r="D735" s="26" t="inlineStr">
+        <is>
+          <t>Theory Concepts Through Pop Music</t>
+        </is>
+      </c>
+      <c r="E735" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=David+Bennett+Piano+Theory+Concepts+Through+Pop+Music</t>
+        </is>
+      </c>
+      <c r="F735" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G735" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H735" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I735" s="26" t="inlineStr">
+        <is>
+          <t>Accessible theory via familiar songs (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="26" t="inlineStr">
+        <is>
+          <t>Languages (Spanish, French, German, Japanese, Arabic)</t>
+        </is>
+      </c>
+      <c r="B736" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C736" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Learn French with Alexa</t>
+        </is>
+      </c>
+      <c r="D736" s="26" t="inlineStr">
+        <is>
+          <t>French Lessons for Beginners</t>
+        </is>
+      </c>
+      <c r="E736" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Learn+French+with+Alexa+French+Lessons+for+Beginners</t>
+        </is>
+      </c>
+      <c r="F736" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G736" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H736" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I736" s="26" t="inlineStr">
+        <is>
+          <t>Long-established French teaching (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="26" t="inlineStr">
+        <is>
+          <t>Languages (Spanish, French, German, Japanese, Arabic)</t>
+        </is>
+      </c>
+      <c r="B737" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C737" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Japanese Ammo with Misa</t>
+        </is>
+      </c>
+      <c r="D737" s="26" t="inlineStr">
+        <is>
+          <t>Japanese Grammar Explained</t>
+        </is>
+      </c>
+      <c r="E737" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Japanese+Ammo+with+Misa+Japanese+Grammar+Explained</t>
+        </is>
+      </c>
+      <c r="F737" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G737" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H737" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I737" s="26" t="inlineStr">
+        <is>
+          <t>Detailed grammar teaching in English (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="26" t="inlineStr">
+        <is>
+          <t>Languages (Spanish, French, German, Japanese, Arabic)</t>
+        </is>
+      </c>
+      <c r="B738" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C738" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Learn Arabic with Maha</t>
+        </is>
+      </c>
+      <c r="D738" s="26" t="inlineStr">
+        <is>
+          <t>Arabic for Beginners</t>
+        </is>
+      </c>
+      <c r="E738" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Learn+Arabic+with+Maha+Arabic+for+Beginners</t>
+        </is>
+      </c>
+      <c r="F738" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G738" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H738" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I738" s="26" t="inlineStr">
+        <is>
+          <t>Structured spoken Arabic (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="26" t="inlineStr">
+        <is>
+          <t>Languages (Spanish, French, German, Japanese, Arabic)</t>
+        </is>
+      </c>
+      <c r="B739" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C739" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Language Simp / Days and Words</t>
+        </is>
+      </c>
+      <c r="D739" s="26" t="inlineStr">
+        <is>
+          <t>Language Learning Method</t>
+        </is>
+      </c>
+      <c r="E739" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Language+Simp+%2F+Days+and+Words+Language+Learning+Method</t>
+        </is>
+      </c>
+      <c r="F739" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G739" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H739" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I739" s="26" t="inlineStr">
+        <is>
+          <t>Method and motivation for self-study (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="26" t="inlineStr">
+        <is>
+          <t>Public Speaking &amp; Communication</t>
+        </is>
+      </c>
+      <c r="B740" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C740" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Communication Coach Alexander Lyon</t>
+        </is>
+      </c>
+      <c r="D740" s="26" t="inlineStr">
+        <is>
+          <t>Professional Communication Skills</t>
+        </is>
+      </c>
+      <c r="E740" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Communication+Coach+Alexander+Lyon+Professional+Communication+Skills</t>
+        </is>
+      </c>
+      <c r="F740" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G740" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H740" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I740" s="26" t="inlineStr">
+        <is>
+          <t>Structured workplace communication training (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="26" t="inlineStr">
+        <is>
+          <t>Public Speaking &amp; Communication</t>
+        </is>
+      </c>
+      <c r="B741" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C741" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Vinh Giang</t>
+        </is>
+      </c>
+      <c r="D741" s="26" t="inlineStr">
+        <is>
+          <t>Voice, Delivery &amp; Stage Presence</t>
+        </is>
+      </c>
+      <c r="E741" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Vinh+Giang+Voice%2C+Delivery+%26+Stage+Presence</t>
+        </is>
+      </c>
+      <c r="F741" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G741" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H741" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I741" s="26" t="inlineStr">
+        <is>
+          <t>Technical vocal coaching (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="26" t="inlineStr">
+        <is>
+          <t>Public Speaking &amp; Communication</t>
+        </is>
+      </c>
+      <c r="B742" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C742" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Toastmasters International</t>
+        </is>
+      </c>
+      <c r="D742" s="26" t="inlineStr">
+        <is>
+          <t>Speech Structure &amp; Practice</t>
+        </is>
+      </c>
+      <c r="E742" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Toastmasters+International+Speech+Structure+%26+Practice</t>
+        </is>
+      </c>
+      <c r="F742" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G742" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H742" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I742" s="26" t="inlineStr">
+        <is>
+          <t>Established speaking methodology (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="26" t="inlineStr">
+        <is>
+          <t>Productivity, Study Skills &amp; Learning How to Learn</t>
+        </is>
+      </c>
+      <c r="B743" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C743" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Barbara Oakley / Learning How to Learn</t>
+        </is>
+      </c>
+      <c r="D743" s="26" t="inlineStr">
+        <is>
+          <t>Learning Science Talks</t>
+        </is>
+      </c>
+      <c r="E743" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Barbara+Oakley+%2F+Learning+How+to+Learn+Learning+Science+Talks</t>
+        </is>
+      </c>
+      <c r="F743" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G743" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H743" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I743" s="26" t="inlineStr">
+        <is>
+          <t>Author of the most-enrolled online course ever (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="26" t="inlineStr">
+        <is>
+          <t>Productivity, Study Skills &amp; Learning How to Learn</t>
+        </is>
+      </c>
+      <c r="B744" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C744" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Odysseas / Python Programmer</t>
+        </is>
+      </c>
+      <c r="D744" s="26" t="inlineStr">
+        <is>
+          <t>Study Strategy for STEM</t>
+        </is>
+      </c>
+      <c r="E744" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Odysseas+%2F+Python+Programmer+Study+Strategy+for+STEM</t>
+        </is>
+      </c>
+      <c r="F744" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G744" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H744" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I744" s="26" t="inlineStr">
+        <is>
+          <t>STEM-specific learning approach (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="26" t="inlineStr">
+        <is>
+          <t>Career, Interviews &amp; Professional Skills</t>
+        </is>
+      </c>
+      <c r="B745" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C745" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Life at Google / Google Careers</t>
+        </is>
+      </c>
+      <c r="D745" s="26" t="inlineStr">
+        <is>
+          <t>Interview Preparation Guidance</t>
+        </is>
+      </c>
+      <c r="E745" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Life+at+Google+%2F+Google+Careers+Interview+Preparation+Guidance</t>
+        </is>
+      </c>
+      <c r="F745" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G745" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H745" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I745" s="26" t="inlineStr">
+        <is>
+          <t>Primary source hiring guidance (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="26" t="inlineStr">
+        <is>
+          <t>Career, Interviews &amp; Professional Skills</t>
+        </is>
+      </c>
+      <c r="B746" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C746" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Self Made Millennial</t>
+        </is>
+      </c>
+      <c r="D746" s="26" t="inlineStr">
+        <is>
+          <t>Resume &amp; Interview Coaching</t>
+        </is>
+      </c>
+      <c r="E746" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Self+Made+Millennial+Resume+%26+Interview+Coaching</t>
+        </is>
+      </c>
+      <c r="F746" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G746" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H746" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I746" s="26" t="inlineStr">
+        <is>
+          <t>Recruiter-perspective job search advice (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="26" t="inlineStr">
+        <is>
+          <t>Career, Interviews &amp; Professional Skills</t>
+        </is>
+      </c>
+      <c r="B747" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C747" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — A Life After Layoff</t>
+        </is>
+      </c>
+      <c r="D747" s="26" t="inlineStr">
+        <is>
+          <t>Hiring Manager Insight</t>
+        </is>
+      </c>
+      <c r="E747" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=A+Life+After+Layoff+Hiring+Manager+Insight</t>
+        </is>
+      </c>
+      <c r="F747" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G747" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H747" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I747" s="26" t="inlineStr">
+        <is>
+          <t>Insider view of recruitment decisions (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="26" t="inlineStr">
+        <is>
+          <t>Health, Fitness &amp; Wellbeing</t>
+        </is>
+      </c>
+      <c r="B748" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C748" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Renaissance Periodization</t>
+        </is>
+      </c>
+      <c r="D748" s="26" t="inlineStr">
+        <is>
+          <t>Hypertrophy &amp; Diet Science</t>
+        </is>
+      </c>
+      <c r="E748" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Renaissance+Periodization+Hypertrophy+%26+Diet+Science</t>
+        </is>
+      </c>
+      <c r="F748" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G748" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H748" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I748" s="26" t="inlineStr">
+        <is>
+          <t>PhD-led training science (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="26" t="inlineStr">
+        <is>
+          <t>Health, Fitness &amp; Wellbeing</t>
+        </is>
+      </c>
+      <c r="B749" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C749" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Andrew Huberman / Huberman Lab</t>
+        </is>
+      </c>
+      <c r="D749" s="26" t="inlineStr">
+        <is>
+          <t>Neuroscience of Sleep, Focus &amp; Health</t>
+        </is>
+      </c>
+      <c r="E749" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Andrew+Huberman+%2F+Huberman+Lab+Neuroscience+of+Sleep%2C+Focus+%26+Health</t>
+        </is>
+      </c>
+      <c r="F749" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G749" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H749" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I749" s="26" t="inlineStr">
+        <is>
+          <t>Popular science of physiology — verify claims independently (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="26" t="inlineStr">
+        <is>
+          <t>Life Skills, Cooking &amp; Practical Knowledge</t>
+        </is>
+      </c>
+      <c r="B750" s="26" t="inlineStr">
+        <is>
+          <t>High School / College</t>
+        </is>
+      </c>
+      <c r="C750" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — J. Kenji López-Alt</t>
+        </is>
+      </c>
+      <c r="D750" s="26" t="inlineStr">
+        <is>
+          <t>First-Person Cooking &amp; Food Science</t>
+        </is>
+      </c>
+      <c r="E750" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=J.+Kenji+L%C3%B3pez-Alt+First-Person+Cooking+%26+Food+Science</t>
+        </is>
+      </c>
+      <c r="F750" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G750" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H750" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I750" s="26" t="inlineStr">
+        <is>
+          <t>Serious food science from a leading author (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="26" t="inlineStr">
+        <is>
+          <t>Life Skills, Cooking &amp; Practical Knowledge</t>
+        </is>
+      </c>
+      <c r="B751" s="26" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C751" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Dad, how do I?</t>
+        </is>
+      </c>
+      <c r="D751" s="26" t="inlineStr">
+        <is>
+          <t>Basic Life &amp; Home Repair Skills</t>
+        </is>
+      </c>
+      <c r="E751" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Dad%2C+how+do+I%3F+Basic+Life+%26+Home+Repair+Skills</t>
+        </is>
+      </c>
+      <c r="F751" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G751" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H751" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I751" s="26" t="inlineStr">
+        <is>
+          <t>Practical household skills (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="26" t="inlineStr">
+        <is>
+          <t>Life Skills, Cooking &amp; Practical Knowledge</t>
+        </is>
+      </c>
+      <c r="B752" s="26" t="inlineStr">
+        <is>
+          <t>All Levels</t>
+        </is>
+      </c>
+      <c r="C752" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Project Farm</t>
+        </is>
+      </c>
+      <c r="D752" s="26" t="inlineStr">
+        <is>
+          <t>Product Testing Methodology</t>
+        </is>
+      </c>
+      <c r="E752" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Project+Farm+Product+Testing+Methodology</t>
+        </is>
+      </c>
+      <c r="F752" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G752" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H752" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I752" s="26" t="inlineStr">
+        <is>
+          <t>Excellent example of controlled testing (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="26" t="inlineStr">
+        <is>
+          <t>Law, Government &amp; Civics</t>
+        </is>
+      </c>
+      <c r="B753" s="26" t="inlineStr">
+        <is>
+          <t>High School Advanced / College</t>
+        </is>
+      </c>
+      <c r="C753" s="26" t="inlineStr">
+        <is>
+          <t>YouTube — Harvard Law School</t>
+        </is>
+      </c>
+      <c r="D753" s="26" t="inlineStr">
+        <is>
+          <t>Public Lectures &amp; Panels</t>
+        </is>
+      </c>
+      <c r="E753" s="26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=Harvard+Law+School+Public+Lectures+%26+Panels</t>
+        </is>
+      </c>
+      <c r="F753" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G753" s="26" t="inlineStr">
+        <is>
+          <t>Not supported by platform</t>
+        </is>
+      </c>
+      <c r="H753" s="26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I753" s="26" t="inlineStr">
+        <is>
+          <t>Primary academic legal source (No specific video resolved yet - the search link always lands on the right channel/playlist; YouTube's search-lookup quota was exhausted before this row could be verified.)</t>
         </is>
       </c>
     </row>

--- a/data/Global_Learning_Resource_Directory.xlsx
+++ b/data/Global_Learning_Resource_Directory.xlsx
@@ -187,7 +187,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -275,6 +275,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8464,19 +8467,19 @@
           <t>Language, Writing &amp; Rhetoric Shorts</t>
         </is>
       </c>
-      <c r="E164" s="23" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@TEDEd</t>
-        </is>
-      </c>
-      <c r="F164" s="22" t="inlineStr">
+      <c r="E164" s="30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2A1IEBFt6Xg</t>
+        </is>
+      </c>
+      <c r="F164" s="30" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G164" s="22" t="inlineStr">
-        <is>
-          <t>Open the channel/playlist, pick the specific video you want, then use: &lt;iframe width="560" height="315" src="https://www.youtube.com/embed/VIDEO_ID" title="TED-Ed" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt; (replace VIDEO_ID with the 11-character code from the video URL).</t>
+      <c r="G164" s="30" t="inlineStr">
+        <is>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/2A1IEBFt6Xg" title="Language, Writing &amp; Rhetoric Shorts" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H164" s="22" t="inlineStr">
@@ -8484,9 +8487,9 @@
           <t>Free</t>
         </is>
       </c>
-      <c r="I164" s="22" t="inlineStr">
-        <is>
-          <t>Short, well-produced explainers on grammar quirks, rhetoric, and writing craft.</t>
+      <c r="I164" s="30" t="inlineStr">
+        <is>
+          <t>Short, well-produced explainers on grammar quirks, rhetoric, and writing craft. Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -17443,17 +17446,17 @@
       </c>
       <c r="E355" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@socratica</t>
+          <t>https://www.youtube.com/watch?v=_P0-mENUv44</t>
         </is>
       </c>
       <c r="F355" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G355" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/_P0-mENUv44" title="SQL Programming Tutorials" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H355" s="26" t="inlineStr">
@@ -17463,7 +17466,7 @@
       </c>
       <c r="I355" s="26" t="inlineStr">
         <is>
-          <t>High-production, concise database and SQL fundamentals</t>
+          <t>High-production, concise database and SQL fundamentals Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -17537,17 +17540,17 @@
       </c>
       <c r="E357" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@GreatScottLab</t>
+          <t>https://www.youtube.com/watch?v=nnZVXshJH4c</t>
         </is>
       </c>
       <c r="F357" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G357" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/nnZVXshJH4c" title="Electronics &amp; Arduino Projects" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H357" s="26" t="inlineStr">
@@ -17557,7 +17560,7 @@
       </c>
       <c r="I357" s="26" t="inlineStr">
         <is>
-          <t>Hands-on electronics and embedded projects with strong production quality</t>
+          <t>Hands-on electronics and embedded projects with strong production quality Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -17584,17 +17587,17 @@
       </c>
       <c r="E358" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ALLABOUTELECTRONICS</t>
+          <t>https://www.youtube.com/watch?v=OgdoRd1Hp3k</t>
         </is>
       </c>
       <c r="F358" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G358" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/OgdoRd1Hp3k" title="Circuit Theory Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H358" s="26" t="inlineStr">
@@ -17604,7 +17607,7 @@
       </c>
       <c r="I358" s="26" t="inlineStr">
         <is>
-          <t>Methodical, exam-oriented electronics theory explanations</t>
+          <t>Methodical, exam-oriented electronics theory explanations Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -17725,17 +17728,17 @@
       </c>
       <c r="E361" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@musictheoryformusicians</t>
+          <t>https://www.youtube.com/watch?v=wsJteEhga34</t>
         </is>
       </c>
       <c r="F361" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G361" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/wsJteEhga34" title="Music Theory Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H361" s="26" t="inlineStr">
@@ -17745,7 +17748,7 @@
       </c>
       <c r="I361" s="26" t="inlineStr">
         <is>
-          <t>Approachable music theory aimed at self-taught musicians</t>
+          <t>Approachable music theory aimed at self-taught musicians Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -17772,17 +17775,17 @@
       </c>
       <c r="E362" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TwoCentsPBS</t>
+          <t>https://www.youtube.com/watch?v=PFi3T_OLtOE</t>
         </is>
       </c>
       <c r="F362" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G362" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/PFi3T_OLtOE" title="Personal Finance Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H362" s="26" t="inlineStr">
@@ -17792,7 +17795,7 @@
       </c>
       <c r="I362" s="26" t="inlineStr">
         <is>
-          <t>PBS Digital Studios production on everyday money decisions</t>
+          <t>PBS Digital Studios production on everyday money decisions Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -17819,17 +17822,17 @@
       </c>
       <c r="E363" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ThePlainBagel</t>
+          <t>https://www.youtube.com/watch?v=CqApXh80HVo</t>
         </is>
       </c>
       <c r="F363" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G363" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/CqApXh80HVo" title="Investing Concepts Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H363" s="26" t="inlineStr">
@@ -17839,7 +17842,7 @@
       </c>
       <c r="I363" s="26" t="inlineStr">
         <is>
-          <t>CFA-charterholder explaining investing and markets without hype</t>
+          <t>CFA-charterholder explaining investing and markets without hype Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -17866,17 +17869,17 @@
       </c>
       <c r="E364" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@GrahamStephan</t>
+          <t>https://www.youtube.com/watch?v=h8dzH_ma8cQ</t>
         </is>
       </c>
       <c r="F364" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G364" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/h8dzH_ma8cQ" title="Personal Finance &amp; Real Estate Investing" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H364" s="26" t="inlineStr">
@@ -17886,7 +17889,7 @@
       </c>
       <c r="I364" s="26" t="inlineStr">
         <is>
-          <t>High-reach independent finance educator with a huge subscriber base</t>
+          <t>High-reach independent finance educator with a huge subscriber base Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18007,17 +18010,17 @@
       </c>
       <c r="E367" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@GothamChess</t>
+          <t>https://www.youtube.com/watch?v=g0W1X63EgKQ</t>
         </is>
       </c>
       <c r="F367" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G367" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/g0W1X63EgKQ" title="Chess Fundamentals &amp; Openings" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H367" s="26" t="inlineStr">
@@ -18027,7 +18030,7 @@
       </c>
       <c r="I367" s="26" t="inlineStr">
         <is>
-          <t>The most-subscribed chess-education channel on YouTube</t>
+          <t>The most-subscribed chess-education channel on YouTube Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18054,17 +18057,17 @@
       </c>
       <c r="E368" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@HangingPawns</t>
+          <t>https://www.youtube.com/watch?v=CyDpcnaRpl8</t>
         </is>
       </c>
       <c r="F368" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G368" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/CyDpcnaRpl8" title="Chess Opening Theory" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H368" s="26" t="inlineStr">
@@ -18074,7 +18077,7 @@
       </c>
       <c r="I368" s="26" t="inlineStr">
         <is>
-          <t>Detailed, well-structured opening and middlegame theory</t>
+          <t>Detailed, well-structured opening and middlegame theory Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18101,17 +18104,17 @@
       </c>
       <c r="E369" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@STLChessClub</t>
+          <t>https://www.youtube.com/watch?v=AbivSjdTZBc</t>
         </is>
       </c>
       <c r="F369" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G369" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/AbivSjdTZBc" title="Chess Lectures by Titled Players" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H369" s="26" t="inlineStr">
@@ -18121,7 +18124,7 @@
       </c>
       <c r="I369" s="26" t="inlineStr">
         <is>
-          <t>Official lecture series from a leading US chess institution</t>
+          <t>Official lecture series from a leading US chess institution Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18148,17 +18151,17 @@
       </c>
       <c r="E370" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@agadmator</t>
+          <t>https://www.youtube.com/watch?v=0W7Xfl8gpEs</t>
         </is>
       </c>
       <c r="F370" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G370" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/0W7Xfl8gpEs" title="Grandmaster Game Analysis" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H370" s="26" t="inlineStr">
@@ -18168,7 +18171,7 @@
       </c>
       <c r="I370" s="26" t="inlineStr">
         <is>
-          <t>One of the highest-reach chess channels; daily annotated grandmaster games</t>
+          <t>One of the highest-reach chess channels; daily annotated grandmaster games Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18195,17 +18198,17 @@
       </c>
       <c r="E371" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ChessNetwork</t>
+          <t>https://www.youtube.com/watch?v=-3-Cn8Y1R84</t>
         </is>
       </c>
       <c r="F371" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G371" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/-3-Cn8Y1R84" title="Chess Tactics &amp; Endgames" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H371" s="26" t="inlineStr">
@@ -18215,7 +18218,7 @@
       </c>
       <c r="I371" s="26" t="inlineStr">
         <is>
-          <t>Long-running channel focused on tactical patterns and endgame technique</t>
+          <t>Long-running channel focused on tactical patterns and endgame technique Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18289,17 +18292,17 @@
       </c>
       <c r="E373" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@tutorialspoint</t>
+          <t>https://www.youtube.com/watch?v=wCaQb-4LYzM</t>
         </is>
       </c>
       <c r="F373" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G373" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/wCaQb-4LYzM" title="Computer Fundamentals for Beginners" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H373" s="26" t="inlineStr">
@@ -18309,7 +18312,7 @@
       </c>
       <c r="I373" s="26" t="inlineStr">
         <is>
-          <t>Straightforward beginner IT-literacy tutorials</t>
+          <t>Straightforward beginner IT-literacy tutorials Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18336,17 +18339,17 @@
       </c>
       <c r="E374" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@gcflearnfree</t>
+          <t>https://www.youtube.com/watch?v=d5LPfzB9nxU</t>
         </is>
       </c>
       <c r="F374" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G374" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/d5LPfzB9nxU" title="Computer Basics &amp; Digital Literacy" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H374" s="26" t="inlineStr">
@@ -18356,7 +18359,7 @@
       </c>
       <c r="I374" s="26" t="inlineStr">
         <is>
-          <t>Nonprofit-run, widely used adult digital-literacy curriculum</t>
+          <t>Nonprofit-run, widely used adult digital-literacy curriculum Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18383,17 +18386,17 @@
       </c>
       <c r="E375" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ajsmart</t>
+          <t>https://www.youtube.com/watch?v=PTbTeySfTJc</t>
         </is>
       </c>
       <c r="F375" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G375" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/PTbTeySfTJc" title="Design Sprint &amp; UX Methods" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H375" s="26" t="inlineStr">
@@ -18403,7 +18406,7 @@
       </c>
       <c r="I375" s="26" t="inlineStr">
         <is>
-          <t>Leading design-sprint agency's own methodology videos</t>
+          <t>Leading design-sprint agency's own methodology videos Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18477,17 +18480,17 @@
       </c>
       <c r="E377" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NNgroup</t>
+          <t>https://www.youtube.com/watch?v=K2msFNTx_k0</t>
         </is>
       </c>
       <c r="F377" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G377" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/K2msFNTx_k0" title="UX Research Methods" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H377" s="26" t="inlineStr">
@@ -18497,7 +18500,7 @@
       </c>
       <c r="I377" s="26" t="inlineStr">
         <is>
-          <t>Nielsen Norman Group; the field's leading UX-research authority</t>
+          <t>Nielsen Norman Group; the field's leading UX-research authority Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18618,17 +18621,17 @@
       </c>
       <c r="E380" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@who</t>
+          <t>https://www.youtube.com/watch?v=VzaNRRoyE2s</t>
         </is>
       </c>
       <c r="F380" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G380" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/VzaNRRoyE2s" title="Epidemiology &amp; Global Health Basics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H380" s="26" t="inlineStr">
@@ -18638,7 +18641,7 @@
       </c>
       <c r="I380" s="26" t="inlineStr">
         <is>
-          <t>Official WHO explainer and training content</t>
+          <t>Official WHO explainer and training content Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18665,17 +18668,17 @@
       </c>
       <c r="E381" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@JustHaveaThink</t>
+          <t>https://www.youtube.com/watch?v=HPU6UDQYkR8</t>
         </is>
       </c>
       <c r="F381" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G381" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/HPU6UDQYkR8" title="Renewable Energy &amp; Climate Tech Explainers" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H381" s="26" t="inlineStr">
@@ -18685,7 +18688,7 @@
       </c>
       <c r="I381" s="26" t="inlineStr">
         <is>
-          <t>Independent, well-researched deep dives into decarbonisation technology</t>
+          <t>Independent, well-researched deep dives into decarbonisation technology Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18759,17 +18762,17 @@
       </c>
       <c r="E383" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@OurChangingClimate</t>
+          <t>https://www.youtube.com/watch?v=6ctwSjEVGwU</t>
         </is>
       </c>
       <c r="F383" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G383" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/6ctwSjEVGwU" title="Renewable Energy Explainers" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H383" s="26" t="inlineStr">
@@ -18779,7 +18782,7 @@
       </c>
       <c r="I383" s="26" t="inlineStr">
         <is>
-          <t>Independent video-essay series on climate solutions</t>
+          <t>Independent video-essay series on climate solutions Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18806,17 +18809,17 @@
       </c>
       <c r="E384" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@zerotothree</t>
+          <t>https://www.youtube.com/watch?v=U0amG4rnc4o</t>
         </is>
       </c>
       <c r="F384" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G384" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/U0amG4rnc4o" title="Early Childhood Development" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H384" s="26" t="inlineStr">
@@ -18826,7 +18829,7 @@
       </c>
       <c r="I384" s="26" t="inlineStr">
         <is>
-          <t>Nonprofit specialising in infant and toddler development research</t>
+          <t>Nonprofit specialising in infant and toddler development research Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18900,17 +18903,17 @@
       </c>
       <c r="E386" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@billvicars</t>
+          <t>https://www.youtube.com/watch?v=CzuQ-1wKLAo</t>
         </is>
       </c>
       <c r="F386" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G386" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/CzuQ-1wKLAo" title="American Sign Language Full Course" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H386" s="26" t="inlineStr">
@@ -18920,7 +18923,7 @@
       </c>
       <c r="I386" s="26" t="inlineStr">
         <is>
-          <t>The most widely used free ASL curriculum on YouTube</t>
+          <t>The most widely used free ASL curriculum on YouTube Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -18994,17 +18997,17 @@
       </c>
       <c r="E388" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Headspace</t>
+          <t>https://www.youtube.com/watch?v=xLrJ9nbgq90</t>
         </is>
       </c>
       <c r="F388" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G388" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/xLrJ9nbgq90" title="Guided Meditation &amp; Mindfulness Basics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H388" s="26" t="inlineStr">
@@ -19014,7 +19017,7 @@
       </c>
       <c r="I388" s="26" t="inlineStr">
         <is>
-          <t>One of the largest, most recognised mindfulness brands, with free guided series</t>
+          <t>One of the largest, most recognised mindfulness brands, with free guided series Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19041,17 +19044,17 @@
       </c>
       <c r="E389" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TherapyinaNutshell</t>
+          <t>https://www.youtube.com/watch?v=ShZKdJF95P8</t>
         </is>
       </c>
       <c r="F389" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G389" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/ShZKdJF95P8" title="Mental Health Skills Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H389" s="26" t="inlineStr">
@@ -19061,7 +19064,7 @@
       </c>
       <c r="I389" s="26" t="inlineStr">
         <is>
-          <t>Licensed therapist explaining coping skills and mental-health concepts</t>
+          <t>Licensed therapist explaining coping skills and mental-health concepts Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19088,17 +19091,17 @@
       </c>
       <c r="E390" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@GreatMeditation</t>
+          <t>https://www.youtube.com/watch?v=Yomsn-nvcx8</t>
         </is>
       </c>
       <c r="F390" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G390" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/Yomsn-nvcx8" title="Guided Meditation Sessions" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H390" s="26" t="inlineStr">
@@ -19108,7 +19111,7 @@
       </c>
       <c r="I390" s="26" t="inlineStr">
         <is>
-          <t>Long, structured guided-meditation sessions for daily practice</t>
+          <t>Long, structured guided-meditation sessions for daily practice Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19135,17 +19138,17 @@
       </c>
       <c r="E391" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@BiggerPockets</t>
+          <t>https://www.youtube.com/watch?v=BILlkXCy8YI</t>
         </is>
       </c>
       <c r="F391" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G391" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/BILlkXCy8YI" title="Real Estate Investing Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H391" s="26" t="inlineStr">
@@ -19155,7 +19158,7 @@
       </c>
       <c r="I391" s="26" t="inlineStr">
         <is>
-          <t>The largest dedicated real-estate-investing education community online</t>
+          <t>The largest dedicated real-estate-investing education community online Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19229,17 +19232,17 @@
       </c>
       <c r="E393" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@JustinRhodes</t>
+          <t>https://www.youtube.com/watch?v=7UjkKBlO-XM</t>
         </is>
       </c>
       <c r="F393" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G393" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/7UjkKBlO-XM" title="Permaculture &amp; Homestead Farming" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H393" s="26" t="inlineStr">
@@ -19249,7 +19252,7 @@
       </c>
       <c r="I393" s="26" t="inlineStr">
         <is>
-          <t>Practical, widely followed sustainable small-farm methods</t>
+          <t>Practical, widely followed sustainable small-farm methods Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19276,17 +19279,17 @@
       </c>
       <c r="E394" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@epicgardening</t>
+          <t>https://www.youtube.com/watch?v=W7H7qkg-pQ0</t>
         </is>
       </c>
       <c r="F394" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G394" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/W7H7qkg-pQ0" title="Sustainable Growing &amp; Gardening Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H394" s="26" t="inlineStr">
@@ -19296,7 +19299,7 @@
       </c>
       <c r="I394" s="26" t="inlineStr">
         <is>
-          <t>One of the largest gardening-education channels, with strong sustainable-practice focus</t>
+          <t>One of the largest gardening-education channels, with strong sustainable-practice focus Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19323,17 +19326,17 @@
       </c>
       <c r="E395" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MentourPilot</t>
+          <t>https://www.youtube.com/watch?v=7O1mVMnY0vc</t>
         </is>
       </c>
       <c r="F395" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G395" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/7O1mVMnY0vc" title="Aviation &amp; Flight Safety Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H395" s="26" t="inlineStr">
@@ -19343,7 +19346,7 @@
       </c>
       <c r="I395" s="26" t="inlineStr">
         <is>
-          <t>Airline pilot explaining aviation systems and incident analysis to a mass audience</t>
+          <t>Airline pilot explaining aviation systems and incident analysis to a mass audience Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19370,17 +19373,17 @@
       </c>
       <c r="E396" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@EverydayAstronaut</t>
+          <t>https://www.youtube.com/watch?v=FQpSAWGgL7k</t>
         </is>
       </c>
       <c r="F396" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G396" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/FQpSAWGgL7k" title="Rockets &amp; Aerospace Engineering Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H396" s="26" t="inlineStr">
@@ -19390,7 +19393,7 @@
       </c>
       <c r="I396" s="26" t="inlineStr">
         <is>
-          <t>Deeply technical yet accessible rocketry and spaceflight engineering</t>
+          <t>Deeply technical yet accessible rocketry and spaceflight engineering Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19417,17 +19420,17 @@
       </c>
       <c r="E397" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ChrisFix</t>
+          <t>https://www.youtube.com/watch?v=m0EiNYvCSpE</t>
         </is>
       </c>
       <c r="F397" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G397" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/m0EiNYvCSpE" title="Car Repair &amp; Maintenance Basics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H397" s="26" t="inlineStr">
@@ -19437,7 +19440,7 @@
       </c>
       <c r="I397" s="26" t="inlineStr">
         <is>
-          <t>One of the most-subscribed DIY car-repair channels in the world</t>
+          <t>One of the most-subscribed DIY car-repair channels in the world Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19464,17 +19467,17 @@
       </c>
       <c r="E398" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@EngineeringExplained</t>
+          <t>https://www.youtube.com/watch?v=UzbrnZ-zWkk</t>
         </is>
       </c>
       <c r="F398" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G398" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/UzbrnZ-zWkk" title="How Cars Work" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H398" s="26" t="inlineStr">
@@ -19484,7 +19487,7 @@
       </c>
       <c r="I398" s="26" t="inlineStr">
         <is>
-          <t>Rigorous automotive engineering explainers with a large following</t>
+          <t>Rigorous automotive engineering explainers with a large following Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19511,17 +19514,17 @@
       </c>
       <c r="E399" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@JeffNippard</t>
+          <t>https://www.youtube.com/watch?v=-jB386MYxbc</t>
         </is>
       </c>
       <c r="F399" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G399" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/-jB386MYxbc" title="Sports Performance &amp; Strength Training Science" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H399" s="26" t="inlineStr">
@@ -19531,7 +19534,7 @@
       </c>
       <c r="I399" s="26" t="inlineStr">
         <is>
-          <t>Evidence-based athletic training and performance concepts</t>
+          <t>Evidence-based athletic training and performance concepts Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19558,17 +19561,17 @@
       </c>
       <c r="E400" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TheCoachingManual</t>
+          <t>https://www.youtube.com/watch?v=lpmosBUr3Ko</t>
         </is>
       </c>
       <c r="F400" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G400" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/lpmosBUr3Ko" title="Coaching Methodology Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H400" s="26" t="inlineStr">
@@ -19578,7 +19581,7 @@
       </c>
       <c r="I400" s="26" t="inlineStr">
         <is>
-          <t>Widely used practical coaching-technique series</t>
+          <t>Widely used practical coaching-technique series Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19605,17 +19608,17 @@
       </c>
       <c r="E401" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@RenaissancePeriodization</t>
+          <t>https://www.youtube.com/watch?v=6x94QcfH_Dw</t>
         </is>
       </c>
       <c r="F401" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G401" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/6x94QcfH_Dw" title="Sports Science &amp; Training Theory" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H401" s="26" t="inlineStr">
@@ -19625,7 +19628,7 @@
       </c>
       <c r="I401" s="26" t="inlineStr">
         <is>
-          <t>PhD-led, research-grounded sports-science and periodization content</t>
+          <t>PhD-led, research-grounded sports-science and periodization content Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19699,17 +19702,17 @@
       </c>
       <c r="E403" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@extracredits</t>
+          <t>https://www.youtube.com/watch?v=FseRp9Y2MR4</t>
         </is>
       </c>
       <c r="F403" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G403" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/FseRp9Y2MR4" title="Game Design &amp; Narrative Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H403" s="26" t="inlineStr">
@@ -19719,7 +19722,7 @@
       </c>
       <c r="I403" s="26" t="inlineStr">
         <is>
-          <t>Long-running series on game design theory and industry practice</t>
+          <t>Long-running series on game design theory and industry practice Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19746,17 +19749,17 @@
       </c>
       <c r="E404" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@AdamCYounis</t>
+          <t>https://www.youtube.com/watch?v=8KM7pOIf0bc</t>
         </is>
       </c>
       <c r="F404" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G404" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/8KM7pOIf0bc" title="Character &amp; Environment Art for Games" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H404" s="26" t="inlineStr">
@@ -19766,7 +19769,7 @@
       </c>
       <c r="I404" s="26" t="inlineStr">
         <is>
-          <t>Practical game-art and asset-creation tutorials</t>
+          <t>Practical game-art and asset-creation tutorials Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19793,17 +19796,17 @@
       </c>
       <c r="E405" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MakersMuse</t>
+          <t>https://www.youtube.com/watch?v=EQGX1mmgyiA</t>
         </is>
       </c>
       <c r="F405" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G405" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/EQGX1mmgyiA" title="3D Printing Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H405" s="26" t="inlineStr">
@@ -19813,7 +19816,7 @@
       </c>
       <c r="I405" s="26" t="inlineStr">
         <is>
-          <t>Practical, widely followed 3D-printing technique and troubleshooting guides</t>
+          <t>Practical, widely followed 3D-printing technique and troubleshooting guides Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19887,17 +19890,17 @@
       </c>
       <c r="E407" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CNCKitchen</t>
+          <t>https://www.youtube.com/watch?v=sHLGrTBLxLg</t>
         </is>
       </c>
       <c r="F407" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G407" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/sHLGrTBLxLg" title="3D Printing Materials &amp; Testing" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H407" s="26" t="inlineStr">
@@ -19907,7 +19910,7 @@
       </c>
       <c r="I407" s="26" t="inlineStr">
         <is>
-          <t>Engineering-rigor testing of 3D-printing materials and settings; huge trusted following</t>
+          <t>Engineering-rigor testing of 3D-printing materials and settings; huge trusted following Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -19934,17 +19937,17 @@
       </c>
       <c r="E408" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Vox</t>
+          <t>https://www.youtube.com/watch?v=QKMLQc_sQEU</t>
         </is>
       </c>
       <c r="F408" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G408" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/QKMLQc_sQEU" title="Media Literacy &amp; Explainer Journalism" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H408" s="26" t="inlineStr">
@@ -19954,7 +19957,7 @@
       </c>
       <c r="I408" s="26" t="inlineStr">
         <is>
-          <t>High-production explainer journalism with enormous reach</t>
+          <t>High-production explainer journalism with enormous reach Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20028,17 +20031,17 @@
       </c>
       <c r="E410" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@johnnyharris</t>
+          <t>https://www.youtube.com/watch?v=XXpqejgnaB0</t>
         </is>
       </c>
       <c r="F410" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G410" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/XXpqejgnaB0" title="Explainer Journalism &amp; Visual Storytelling" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H410" s="26" t="inlineStr">
@@ -20048,7 +20051,7 @@
       </c>
       <c r="I410" s="26" t="inlineStr">
         <is>
-          <t>Former Vox journalist; one of the most-watched independent explainer channels</t>
+          <t>Former Vox journalist; one of the most-watched independent explainer channels Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20169,17 +20172,17 @@
       </c>
       <c r="E413" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@andreaskayy</t>
+          <t>https://www.youtube.com/watch?v=-PHnR-KEHqE</t>
         </is>
       </c>
       <c r="F413" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G413" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/-PHnR-KEHqE" title="Data Engineering Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H413" s="26" t="inlineStr">
@@ -20189,7 +20192,7 @@
       </c>
       <c r="I413" s="26" t="inlineStr">
         <is>
-          <t>Practitioner-run channel focused specifically on data-engineering pipelines</t>
+          <t>Practitioner-run channel focused specifically on data-engineering pipelines Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20216,17 +20219,17 @@
       </c>
       <c r="E414" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SeattleDataGuy</t>
+          <t>https://www.youtube.com/watch?v=TwV9nIAWPso</t>
         </is>
       </c>
       <c r="F414" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G414" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/TwV9nIAWPso" title="Data Engineering &amp; Analytics Careers" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H414" s="26" t="inlineStr">
@@ -20236,7 +20239,7 @@
       </c>
       <c r="I414" s="26" t="inlineStr">
         <is>
-          <t>Practical data-engineering and analytics-career guidance</t>
+          <t>Practical data-engineering and analytics-career guidance Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20263,17 +20266,17 @@
       </c>
       <c r="E415" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@7sagelsat</t>
+          <t>https://www.youtube.com/watch?v=i1I9UPSNbf4</t>
         </is>
       </c>
       <c r="F415" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G415" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/i1I9UPSNbf4" title="LSAT Prep Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H415" s="26" t="inlineStr">
@@ -20283,7 +20286,7 @@
       </c>
       <c r="I415" s="26" t="inlineStr">
         <is>
-          <t>The most widely used free LSAT logic-games and reasoning curriculum</t>
+          <t>The most widely used free LSAT logic-games and reasoning curriculum Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20404,17 +20407,17 @@
       </c>
       <c r="E418" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@thisoldhouse</t>
+          <t>https://www.youtube.com/watch?v=jFIYpz1wirU</t>
         </is>
       </c>
       <c r="F418" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G418" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/jFIYpz1wirU" title="Home Improvement &amp; Carpentry Basics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H418" s="26" t="inlineStr">
@@ -20424,7 +20427,7 @@
       </c>
       <c r="I418" s="26" t="inlineStr">
         <is>
-          <t>Long-running, broadly trusted home-improvement education brand</t>
+          <t>Long-running, broadly trusted home-improvement education brand Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20451,17 +20454,17 @@
       </c>
       <c r="E419" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@FixThisBuildThat</t>
+          <t>https://www.youtube.com/watch?v=DzmPxDDiyFI</t>
         </is>
       </c>
       <c r="F419" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G419" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/DzmPxDDiyFI" title="Beginner Woodworking Projects" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H419" s="26" t="inlineStr">
@@ -20471,7 +20474,7 @@
       </c>
       <c r="I419" s="26" t="inlineStr">
         <is>
-          <t>Project-based woodworking tutorials aimed squarely at beginners</t>
+          <t>Project-based woodworking tutorials aimed squarely at beginners Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20498,17 +20501,17 @@
       </c>
       <c r="E420" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ProfessorPincushion</t>
+          <t>https://www.youtube.com/watch?v=VdrDP3Wuw-Q</t>
         </is>
       </c>
       <c r="F420" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G420" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/VdrDP3Wuw-Q" title="Sewing Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H420" s="26" t="inlineStr">
@@ -20518,7 +20521,7 @@
       </c>
       <c r="I420" s="26" t="inlineStr">
         <is>
-          <t>Clear, methodical beginner sewing tutorials with a large following</t>
+          <t>Clear, methodical beginner sewing tutorials with a large following Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20592,17 +20595,17 @@
       </c>
       <c r="E422" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@BioLayne</t>
+          <t>https://www.youtube.com/watch?v=DFhpqZK4qP4</t>
         </is>
       </c>
       <c r="F422" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G422" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/DFhpqZK4qP4" title="Nutrition Science Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H422" s="26" t="inlineStr">
@@ -20612,7 +20615,7 @@
       </c>
       <c r="I422" s="26" t="inlineStr">
         <is>
-          <t>PhD-in-nutritional-science educator known for evidence-based content</t>
+          <t>PhD-in-nutritional-science educator known for evidence-based content Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20639,17 +20642,17 @@
       </c>
       <c r="E423" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NutritionMadeSimple</t>
+          <t>https://www.youtube.com/watch?v=GpzX3NQzmio</t>
         </is>
       </c>
       <c r="F423" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G423" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/GpzX3NQzmio" title="Evidence-Based Nutrition Basics" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H423" s="26" t="inlineStr">
@@ -20659,7 +20662,7 @@
       </c>
       <c r="I423" s="26" t="inlineStr">
         <is>
-          <t>Research-grounded nutrition explainers aimed at a general audience</t>
+          <t>Research-grounded nutrition explainers aimed at a general audience Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20686,17 +20689,17 @@
       </c>
       <c r="E424" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@physionic</t>
+          <t>https://www.youtube.com/watch?v=STML7Yugs70</t>
         </is>
       </c>
       <c r="F424" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G424" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/STML7Yugs70" title="Nutrition Research Breakdowns" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H424" s="26" t="inlineStr">
@@ -20706,7 +20709,7 @@
       </c>
       <c r="I424" s="26" t="inlineStr">
         <is>
-          <t>PhD physiologist breaking down primary nutrition-science literature</t>
+          <t>PhD physiologist breaking down primary nutrition-science literature Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20780,17 +20783,17 @@
       </c>
       <c r="E426" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@shutupandsitdown</t>
+          <t>https://www.youtube.com/watch?v=8c-L4gLt1jU</t>
         </is>
       </c>
       <c r="F426" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G426" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/8c-L4gLt1jU" title="Board Game Strategy &amp; Design" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H426" s="26" t="inlineStr">
@@ -20800,7 +20803,7 @@
       </c>
       <c r="I426" s="26" t="inlineStr">
         <is>
-          <t>The most-followed independent board-game review and strategy channel</t>
+          <t>The most-followed independent board-game review and strategy channel Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20827,17 +20830,17 @@
       </c>
       <c r="E427" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NotJustBikes</t>
+          <t>https://www.youtube.com/watch?v=E_SJ1NBMrH0</t>
         </is>
       </c>
       <c r="F427" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G427" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/E_SJ1NBMrH0" title="Urban Planning Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H427" s="26" t="inlineStr">
@@ -20847,7 +20850,7 @@
       </c>
       <c r="I427" s="26" t="inlineStr">
         <is>
-          <t>Widely cited urban-design and transportation-planning video essays</t>
+          <t>Widely cited urban-design and transportation-planning video essays Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20874,17 +20877,17 @@
       </c>
       <c r="E428" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CityBeautiful</t>
+          <t>https://www.youtube.com/watch?v=HqHt7VdusAI</t>
         </is>
       </c>
       <c r="F428" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G428" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/HqHt7VdusAI" title="Urban Planning Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H428" s="26" t="inlineStr">
@@ -20894,7 +20897,7 @@
       </c>
       <c r="I428" s="26" t="inlineStr">
         <is>
-          <t>Accessible explainers on how cities are designed and zoned</t>
+          <t>Accessible explainers on how cities are designed and zoned Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20921,17 +20924,17 @@
       </c>
       <c r="E429" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@RMTransit</t>
+          <t>https://www.youtube.com/watch?v=wgAlgu7BCoI</t>
         </is>
       </c>
       <c r="F429" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G429" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/wgAlgu7BCoI" title="Public Transit &amp; City Design" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H429" s="26" t="inlineStr">
@@ -20941,7 +20944,7 @@
       </c>
       <c r="I429" s="26" t="inlineStr">
         <is>
-          <t>Focused explainers on transit systems as an urban-planning discipline</t>
+          <t>Focused explainers on transit systems as an urban-planning discipline Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -20968,17 +20971,17 @@
       </c>
       <c r="E430" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@alanbecker</t>
+          <t>https://www.youtube.com/watch?v=C637UcpHfNY</t>
         </is>
       </c>
       <c r="F430" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G430" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/C637UcpHfNY" title="Animation Principles Explained" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H430" s="26" t="inlineStr">
@@ -20988,7 +20991,7 @@
       </c>
       <c r="I430" s="26" t="inlineStr">
         <is>
-          <t>Animator-run channel breaking down core animation principles</t>
+          <t>Animator-run channel breaking down core animation principles Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -21015,17 +21018,17 @@
       </c>
       <c r="E431" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SchoolofMotion</t>
+          <t>https://www.youtube.com/watch?v=buKzLtYjBiI</t>
         </is>
       </c>
       <c r="F431" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G431" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/buKzLtYjBiI" title="Motion Graphics Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H431" s="26" t="inlineStr">
@@ -21035,7 +21038,7 @@
       </c>
       <c r="I431" s="26" t="inlineStr">
         <is>
-          <t>Industry-run motion-design education with a strong practitioner following</t>
+          <t>Industry-run motion-design education with a strong practitioner following Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -21062,17 +21065,17 @@
       </c>
       <c r="E432" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@BloopAnimation</t>
+          <t>https://www.youtube.com/watch?v=FHnD-m33mMc</t>
         </is>
       </c>
       <c r="F432" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G432" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/FHnD-m33mMc" title="2D Animation Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H432" s="26" t="inlineStr">
@@ -21082,7 +21085,7 @@
       </c>
       <c r="I432" s="26" t="inlineStr">
         <is>
-          <t>Long-running dedicated 2D-animation education channel</t>
+          <t>Long-running dedicated 2D-animation education channel Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -21203,17 +21206,17 @@
       </c>
       <c r="E435" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@BackToBackSWE</t>
+          <t>https://www.youtube.com/watch?v=0K3h5MlIWu0</t>
         </is>
       </c>
       <c r="F435" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G435" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/0K3h5MlIWu0" title="Data Structures Interview Deep Dives" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H435" s="26" t="inlineStr">
@@ -21223,7 +21226,7 @@
       </c>
       <c r="I435" s="26" t="inlineStr">
         <is>
-          <t>Detailed, whiteboard-style breakdowns of classic interview problems</t>
+          <t>Detailed, whiteboard-style breakdowns of classic interview problems Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -21250,17 +21253,17 @@
       </c>
       <c r="E436" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TechWithTim</t>
+          <t>https://www.youtube.com/watch?v=cHlmP4LYdPg</t>
         </is>
       </c>
       <c r="F436" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G436" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/cHlmP4LYdPg" title="Technical Interview Practice" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H436" s="26" t="inlineStr">
@@ -21270,7 +21273,7 @@
       </c>
       <c r="I436" s="26" t="inlineStr">
         <is>
-          <t>Broad, beginner-friendly technical-interview and coding-practice content</t>
+          <t>Broad, beginner-friendly technical-interview and coding-practice content Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -21297,17 +21300,17 @@
       </c>
       <c r="E437" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CSDojo</t>
+          <t>https://www.youtube.com/watch?v=hiISl558JGE</t>
         </is>
       </c>
       <c r="F437" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G437" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/hiISl558JGE" title="Coding Interview &amp; Python Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H437" s="26" t="inlineStr">
@@ -21317,7 +21320,7 @@
       </c>
       <c r="I437" s="26" t="inlineStr">
         <is>
-          <t>Former Google engineer's widely watched interview-prep and Python content</t>
+          <t>Former Google engineer's widely watched interview-prep and Python content Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -21438,17 +21441,17 @@
       </c>
       <c r="E440" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@googlecloudtech</t>
+          <t>https://www.youtube.com/watch?v=FARxSG_EY98</t>
         </is>
       </c>
       <c r="F440" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G440" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/FARxSG_EY98" title="Google Cloud Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H440" s="26" t="inlineStr">
@@ -21458,7 +21461,7 @@
       </c>
       <c r="I440" s="26" t="inlineStr">
         <is>
-          <t>Official Google Cloud training and certification-prep channel</t>
+          <t>Official Google Cloud training and certification-prep channel Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
@@ -21626,17 +21629,17 @@
       </c>
       <c r="E444" s="26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@mruniversity</t>
+          <t>https://www.youtube.com/watch?v=CwPdoCF67Yk</t>
         </is>
       </c>
       <c r="F444" s="26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G444" s="26" t="inlineStr">
         <is>
-          <t>Not supported by platform</t>
+          <t>&lt;iframe width="560" height="315" src="https://www.youtube.com/embed/CwPdoCF67Yk" title="Behavioral Economics Fundamentals" frameborder="0" allowfullscreen&gt;&lt;/iframe&gt;</t>
         </is>
       </c>
       <c r="H444" s="26" t="inlineStr">
@@ -21646,7 +21649,7 @@
       </c>
       <c r="I444" s="26" t="inlineStr">
         <is>
-          <t>George Mason University faculty; standard free behavioral-econ curriculum</t>
+          <t>George Mason University faculty; standard free behavioral-econ curriculum Converted to a real playable video via YouTube Data API v3 on 17 August 2026 (was a bare channel link).</t>
         </is>
       </c>
     </row>
